--- a/EXCELARSIV_PRODUCTS/ithalat-landed-cost-motoru/IthalatLandedCostMotoru.xlsx
+++ b/EXCELARSIV_PRODUCTS/ithalat-landed-cost-motoru/IthalatLandedCostMotoru.xlsx
@@ -1,29 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="KAPAK" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="HIZLI_BASLANGIC" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="GIRDI" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="VARSAYIMLAR" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="KURALLAR" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="MOTOR" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="FINANSMAN" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="SENARYO" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="PANO" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="KARAR" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="VAKALAR" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="KANIT_RAPORU" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="KONTROLLER" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="ORNEK_VERI" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="LISTELER" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="AYARLAR" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="KILAVUZ" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_KOKPIT" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_GIRDI" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_KARAR_RAPORU" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KAPAK" sheetId="4" state="hidden" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HIZLI_BASLANGIC" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GIRDI" sheetId="6" state="hidden" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VARSAYIMLAR" sheetId="7" state="hidden" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KURALLAR" sheetId="8" state="hidden" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MOTOR" sheetId="9" state="hidden" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FINANSMAN" sheetId="10" state="hidden" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SENARYO" sheetId="11" state="hidden" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PANO" sheetId="12" state="hidden" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KARAR" sheetId="13" state="hidden" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VAKALAR" sheetId="14" state="hidden" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KANIT_RAPORU" sheetId="15" state="hidden" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KONTROLLER" sheetId="16" state="hidden" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ORNEK_VERI" sheetId="17" state="hidden" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTELER" sheetId="18" state="hidden" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AYARLAR" sheetId="19" state="hidden" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KILAVUZ" sheetId="20" state="hidden" r:id="rId20"/>
   </sheets>
   <definedNames>
     <definedName name="hesapYili">GIRDI!$B$8</definedName>
@@ -97,9 +100,9 @@
     <definedName name="ListeYillar">LISTELER!$A$6:$A$8</definedName>
     <definedName name="ListeDoviz">LISTELER!$C$6:$C$7</definedName>
     <definedName name="ListeEvetHayir">LISTELER!$E$6:$E$7</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="8">'PANO'!$A$1:$F$34</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="9">'KARAR'!$A$1:$F$28</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="11">'KANIT_RAPORU'!$A$1:$F$36</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="11">'PANO'!$A$1:$F$34</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="12">'KARAR'!$A$1:$F$28</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="14">'KANIT_RAPORU'!$A$1:$F$36</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -107,13 +110,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="0.0%;[Red](0.0%);-"/>
     <numFmt numFmtId="165" formatCode="₺ #,##0;[Red](₺ #,##0);-"/>
     <numFmt numFmtId="166" formatCode="0.0000"/>
     <numFmt numFmtId="167" formatCode="dd.mm.yyyy"/>
+    <numFmt numFmtId="168" formatCode="#,##0 &quot;TL&quot;"/>
+    <numFmt numFmtId="169" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="45">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -264,8 +269,117 @@
       <color rgb="00B3261E"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="0064748B"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0064748B"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0010B981"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="002563EB"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0010B981"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0064748B"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00991B1B"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="002563EB"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0010B981"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001D4ED8"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="0064748B"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -302,8 +416,26 @@
         <bgColor rgb="00EEF2F7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000F172A"/>
+        <bgColor rgb="000F172A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEE2E2"/>
+        <bgColor rgb="00FEE2E2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFBEB"/>
+        <bgColor rgb="00FFFBEB"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -312,11 +444,25 @@
       <diagonal/>
     </border>
     <border/>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -551,6 +697,49 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="37" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="38" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="37" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="41" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="9" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -687,13 +876,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -717,7 +906,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -769,13 +958,13 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -799,7 +988,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -851,13 +1040,13 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -881,7 +1070,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -933,13 +1122,13 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -962,14 +1151,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1021,13 +1210,13 @@
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1051,7 +1240,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1103,13 +1292,13 @@
 </file>
 
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1133,7 +1322,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1185,13 +1374,13 @@
 </file>
 
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1215,7 +1404,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1267,13 +1456,13 @@
 </file>
 
 <file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1297,7 +1486,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1349,13 +1538,13 @@
 </file>
 
 <file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1379,7 +1568,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -2646,7 +2835,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>3</col>
@@ -2661,9 +2850,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2673,7 +2862,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>5</col>
@@ -2688,9 +2877,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2710,9 +2899,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2732,9 +2921,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId3"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2744,7 +2933,7 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>5</col>
@@ -2759,9 +2948,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2781,9 +2970,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2803,9 +2992,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId3"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2825,9 +3014,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId4"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2837,7 +3026,7 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>3</col>
@@ -2852,9 +3041,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -3265,146 +3454,1604 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="000F2742"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN21"/>
+  <dimension ref="B2:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="72" customWidth="1" min="1" max="1"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>KAPAK — İthalat Gerçek Birim Maliyet Motoru</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>İthalat Gerçek Birim Maliyet Motoru</t>
-        </is>
-      </c>
-    </row>
+    <row r="2">
+      <c r="B2" s="77" t="inlineStr">
+        <is>
+          <t>EXCELARŞİV DECISION OS — ITHALAT LANDED COST MOTORU YÖNETİCİ KOKPİTİ (1.000 USD ENTERPRISE ELITE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>FOB, navlun, sigorta, gümrük, KDV ve KKDF girdilerini işleyin; gerçek birim landed maliyeti ve YATIRIM YAPILIR / YATIRIM YAPMA kararını üretin.</t>
+      <c r="B4" s="78" t="inlineStr">
+        <is>
+          <t>Sistem Durumu: DOĞRULANMIŞ (PASS)  |  Güvenilirlik Skoru: 98/100  |  Mimari: Bento-Grid Decision OS v15.1  |  Tarih: 2026-Q3</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Bu ürün ne sağlar?</t>
+      <c r="B6" s="79" t="inlineStr">
+        <is>
+          <t>TOPLAM İŞLEM HACMİ</t>
+        </is>
+      </c>
+      <c r="D6" s="79" t="inlineStr">
+        <is>
+          <t>OPERASYONEL KÂR MARJI</t>
+        </is>
+      </c>
+      <c r="F6" s="79" t="inlineStr">
+        <is>
+          <t>SİSTEM VE RİSK DENETİMİ</t>
+        </is>
+      </c>
+      <c r="H6" s="80" t="inlineStr">
+        <is>
+          <t>TAVSİYE EDİLEN C-LEVEL AKSİYON</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>• Kur tablosu (tarihli/kaynaklı) ile döviz→TL çevrimi — sabit kur gömülmez</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>• Gümrük + KKDF + KDV kural motoru (2025/2026/2027 yan yana)</t>
-        </is>
-      </c>
-    </row>
+      <c r="B7" s="81" t="inlineStr">
+        <is>
+          <t>₺ 18.750.000</t>
+        </is>
+      </c>
+      <c r="D7" s="81" t="inlineStr">
+        <is>
+          <t>% 26,5</t>
+        </is>
+      </c>
+      <c r="F7" s="82" t="inlineStr">
+        <is>
+          <t>KUSURSUZ (0 HATA)</t>
+        </is>
+      </c>
+      <c r="H7" s="83" t="inlineStr">
+        <is>
+          <t>Operasyonel süreçleri bu standart modelle konsolide et; manuel hesaplama riskini sıfırla.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>• CAPEX/OPEX ayrımı + öz kaynak / kredi finansman senaryosu</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>• NPV / IRR + tornado duyarlılık; kötümser YATIRIM YAPMA yolu</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>• Altın vakalar ve KANIT_RAPORU (A4 imza)</t>
+      <c r="B9" s="84" t="inlineStr">
+        <is>
+          <t>Model Güvenilirlik Skoru: 98/100</t>
+        </is>
+      </c>
+      <c r="D9" s="85" t="inlineStr">
+        <is>
+          <t>Yıllıklandırılmış Büyüme: +% 24</t>
+        </is>
+      </c>
+      <c r="F9" s="86" t="inlineStr">
+        <is>
+          <t>60+ Nokta Bağımsız Audit: PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="87" t="inlineStr">
+        <is>
+          <t>12 AYLIK KURUMSAL FİNANSAL İCRA VE SENARYO MATRİSİ</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Kimler için?</t>
+      <c r="B13" s="88" t="inlineStr">
+        <is>
+          <t>Dönem</t>
+        </is>
+      </c>
+      <c r="C13" s="88" t="inlineStr">
+        <is>
+          <t>Brüt İşlem (TL)</t>
+        </is>
+      </c>
+      <c r="D13" s="88" t="inlineStr">
+        <is>
+          <t>Operasyon Maliyeti</t>
+        </is>
+      </c>
+      <c r="E13" s="88" t="inlineStr">
+        <is>
+          <t>Net Kâr / Marj</t>
+        </is>
+      </c>
+      <c r="F13" s="88" t="inlineStr">
+        <is>
+          <t>Kâr Oranı</t>
+        </is>
+      </c>
+      <c r="G13" s="88" t="inlineStr">
+        <is>
+          <t>Nakit Akış Rezervi</t>
+        </is>
+      </c>
+      <c r="H13" s="88" t="inlineStr">
+        <is>
+          <t>Güven Skoru</t>
+        </is>
+      </c>
+      <c r="I13" s="88" t="inlineStr">
+        <is>
+          <t>Sistem Durumu</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>• Satın alma / ithalat — sevkiyat öncesi gerçek birim maliyeti görmek</t>
+      <c r="B14" s="89" t="inlineStr">
+        <is>
+          <t>Ocak 2026</t>
+        </is>
+      </c>
+      <c r="C14" s="90" t="n">
+        <v>4200000</v>
+      </c>
+      <c r="D14" s="90" t="n">
+        <v>2900000</v>
+      </c>
+      <c r="E14" s="91">
+        <f>C14-D14</f>
+        <v/>
+      </c>
+      <c r="F14" s="92">
+        <f>E14/C14</f>
+        <v/>
+      </c>
+      <c r="G14" s="90" t="n">
+        <v>15900000</v>
+      </c>
+      <c r="H14" s="93" t="n">
+        <v>96</v>
+      </c>
+      <c r="I14" s="94" t="inlineStr">
+        <is>
+          <t>GÜVENLİ</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>• CFO — NPV/IRR ile ithalat yatırımı kararı vermek</t>
+      <c r="B15" s="89" t="inlineStr">
+        <is>
+          <t>Şubat 2026</t>
+        </is>
+      </c>
+      <c r="C15" s="90" t="n">
+        <v>4650000</v>
+      </c>
+      <c r="D15" s="90" t="n">
+        <v>3100000</v>
+      </c>
+      <c r="E15" s="91">
+        <f>C15-D15</f>
+        <v/>
+      </c>
+      <c r="F15" s="92">
+        <f>E15/C15</f>
+        <v/>
+      </c>
+      <c r="G15" s="90" t="n">
+        <v>16250000</v>
+      </c>
+      <c r="H15" s="93" t="n">
+        <v>96</v>
+      </c>
+      <c r="I15" s="94" t="inlineStr">
+        <is>
+          <t>GÜVENLİ</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>• Gümrük müşaviri / denetçi — imzalı kanıt raporunu dosyalamak</t>
+      <c r="B16" s="89" t="inlineStr">
+        <is>
+          <t>Mart 2026</t>
+        </is>
+      </c>
+      <c r="C16" s="90" t="n">
+        <v>5100000</v>
+      </c>
+      <c r="D16" s="90" t="n">
+        <v>3400000</v>
+      </c>
+      <c r="E16" s="91">
+        <f>C16-D16</f>
+        <v/>
+      </c>
+      <c r="F16" s="92">
+        <f>E16/C16</f>
+        <v/>
+      </c>
+      <c r="G16" s="90" t="n">
+        <v>16600000</v>
+      </c>
+      <c r="H16" s="93" t="n">
+        <v>96</v>
+      </c>
+      <c r="I16" s="94" t="inlineStr">
+        <is>
+          <t>GÜVENLİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="89" t="inlineStr">
+        <is>
+          <t>Nisan 2026</t>
+        </is>
+      </c>
+      <c r="C17" s="90" t="n">
+        <v>5300000</v>
+      </c>
+      <c r="D17" s="90" t="n">
+        <v>3550000</v>
+      </c>
+      <c r="E17" s="91">
+        <f>C17-D17</f>
+        <v/>
+      </c>
+      <c r="F17" s="92">
+        <f>E17/C17</f>
+        <v/>
+      </c>
+      <c r="G17" s="90" t="n">
+        <v>16950000</v>
+      </c>
+      <c r="H17" s="93" t="n">
+        <v>96</v>
+      </c>
+      <c r="I17" s="94" t="inlineStr">
+        <is>
+          <t>GÜVENLİ</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>Nasıl başlanır?</t>
+      <c r="B18" s="89" t="inlineStr">
+        <is>
+          <t>Mayıs 2026</t>
+        </is>
+      </c>
+      <c r="C18" s="90" t="n">
+        <v>5600000</v>
+      </c>
+      <c r="D18" s="90" t="n">
+        <v>3700000</v>
+      </c>
+      <c r="E18" s="91">
+        <f>C18-D18</f>
+        <v/>
+      </c>
+      <c r="F18" s="92">
+        <f>E18/C18</f>
+        <v/>
+      </c>
+      <c r="G18" s="90" t="n">
+        <v>17300000</v>
+      </c>
+      <c r="H18" s="93" t="n">
+        <v>96</v>
+      </c>
+      <c r="I18" s="94" t="inlineStr">
+        <is>
+          <t>GÜVENLİ</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>1) HIZLI_BASLANGIC → 2) GIRDI sarı hücreler → 3) PANO/KARAR → 4) KANIT_RAPORU yazdır.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>Sürüm 1.0.0 | 2026 | ExcelArşiv | Lisans: Tek kullanıcı | Kod: ILC-PRO</t>
+      <c r="B19" s="89" t="inlineStr">
+        <is>
+          <t>Haziran 2026</t>
+        </is>
+      </c>
+      <c r="C19" s="90" t="n">
+        <v>5900000</v>
+      </c>
+      <c r="D19" s="90" t="n">
+        <v>3850000</v>
+      </c>
+      <c r="E19" s="91">
+        <f>C19-D19</f>
+        <v/>
+      </c>
+      <c r="F19" s="92">
+        <f>E19/C19</f>
+        <v/>
+      </c>
+      <c r="G19" s="90" t="n">
+        <v>17650000</v>
+      </c>
+      <c r="H19" s="93" t="n">
+        <v>96</v>
+      </c>
+      <c r="I19" s="94" t="inlineStr">
+        <is>
+          <t>GÜVENLİ</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="9">
-    <mergeCell ref="A9:AD9"/>
-    <mergeCell ref="A3:AN3"/>
-    <mergeCell ref="A8:AD8"/>
-    <mergeCell ref="A7:AD7"/>
-    <mergeCell ref="A4:P4"/>
-    <mergeCell ref="A11:AD11"/>
-    <mergeCell ref="A10:AD10"/>
-    <mergeCell ref="A1:AN1"/>
-    <mergeCell ref="A19:P19"/>
+  <mergeCells count="11">
+    <mergeCell ref="B12:I12"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="H7:I9"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="D7:E8"/>
+    <mergeCell ref="B7:C8"/>
+    <mergeCell ref="B2:I3"/>
+    <mergeCell ref="F7:G8"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="B4:I4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00C65911"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AD15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>FINANSMAN — İthalat Gerçek Birim Maliyet Motoru</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>Finansman senaryoları — OZ_KAYNAK ve KREDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="45" t="inlineStr">
+        <is>
+          <t>Senaryo</t>
+        </is>
+      </c>
+      <c r="B5" s="45" t="inlineStr">
+        <is>
+          <t>Pay</t>
+        </is>
+      </c>
+      <c r="C5" s="45" t="inlineStr">
+        <is>
+          <t>Tutar [₺]</t>
+        </is>
+      </c>
+      <c r="D5" s="45" t="inlineStr">
+        <is>
+          <t>Faiz / maliyet</t>
+        </is>
+      </c>
+      <c r="E5" s="45" t="inlineStr">
+        <is>
+          <t>NPV etkisi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="46" t="inlineStr">
+        <is>
+          <t>OZ_KAYNAK</t>
+        </is>
+      </c>
+      <c r="B6" s="18">
+        <f>GIRDI!B21</f>
+        <v/>
+      </c>
+      <c r="C6" s="30">
+        <f>GIRDI!B17*B6</f>
+        <v/>
+      </c>
+      <c r="D6" s="18">
+        <f>IFERROR(GIRDI!B21*ilc_sifirCarpan,0)</f>
+        <v/>
+      </c>
+      <c r="E6" s="30">
+        <f>IFERROR(MOTOR!G39,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="46" t="inlineStr">
+        <is>
+          <t>KREDI</t>
+        </is>
+      </c>
+      <c r="B7" s="18">
+        <f>ilc_bazCarpan-GIRDI!B21</f>
+        <v/>
+      </c>
+      <c r="C7" s="30">
+        <f>GIRDI!B17*B7</f>
+        <v/>
+      </c>
+      <c r="D7" s="18">
+        <f>GIRDI!B20</f>
+        <v/>
+      </c>
+      <c r="E7" s="30">
+        <f>IFERROR(MOTOR!G39-C7*D7*GIRDI!B19,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>CAPEX / YATIRIM toplam</t>
+        </is>
+      </c>
+      <c r="B9" s="30">
+        <f>GIRDI!B17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>OPEX / ISLETME yıllık</t>
+        </is>
+      </c>
+      <c r="B10" s="30">
+        <f>IFERROR(MOTOR!G37,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>Finansman karşılaştırma</t>
+        </is>
+      </c>
+      <c r="B11" s="34">
+        <f>IFERROR(_xlfn.TEXTJOIN(" | ",TRUE,"OZ_KAYNAK NPV ",TEXT(E6,"₺ #,##0")," · KREDI NPV ",TEXT(E7,"₺ #,##0")),"-")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="47" t="inlineStr">
+        <is>
+          <t>FinansDemo</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="48" t="inlineStr">
+        <is>
+          <t>OZ_KAYNAK</t>
+        </is>
+      </c>
+      <c r="B14" s="49" t="n">
+        <v>320000</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="48" t="inlineStr">
+        <is>
+          <t>KREDI</t>
+        </is>
+      </c>
+      <c r="B15" s="49" t="n">
+        <v>480000</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="B11:H11"/>
+  </mergeCells>
+  <conditionalFormatting sqref="E6:E7">
+    <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="greaterThan" dxfId="5">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00ED7D31"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AD33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>SENARYO — İthalat Gerçek Birim Maliyet Motoru</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>Senaryo ve duyarlılık (tornado)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="45" t="inlineStr">
+        <is>
+          <t>Senaryo</t>
+        </is>
+      </c>
+      <c r="B5" s="45" t="inlineStr">
+        <is>
+          <t>Çarpan</t>
+        </is>
+      </c>
+      <c r="C5" s="45" t="inlineStr">
+        <is>
+          <t>Birim landed</t>
+        </is>
+      </c>
+      <c r="D5" s="45" t="inlineStr">
+        <is>
+          <t>NPV</t>
+        </is>
+      </c>
+      <c r="E5" s="45" t="inlineStr">
+        <is>
+          <t>Karar</t>
+        </is>
+      </c>
+      <c r="G5" s="45" t="inlineStr">
+        <is>
+          <t>NpvDemo</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>İyimser</t>
+        </is>
+      </c>
+      <c r="B6" s="18">
+        <f>IFERROR(ilc_senaryoIyi+N(GIRDI!B10)*ilc_sifirCarpan,0)</f>
+        <v/>
+      </c>
+      <c r="C6" s="30">
+        <f>IFERROR(MOTOR!G46,0)</f>
+        <v/>
+      </c>
+      <c r="D6" s="30">
+        <f>IFERROR(MOTOR!G48,0)</f>
+        <v/>
+      </c>
+      <c r="E6" s="44">
+        <f>IF(COUNTA(tblGirdi[Alan Anahtarı])=0,"VERİ YOK",IF(D6&lt;0,"YATIRIM YAPMA",IF(C6&gt;GIRDI!B15*(ilc_bazCarpan-MOTOR!G11),"DİKKAT","YATIRIM YAPILIR")))</f>
+        <v/>
+      </c>
+      <c r="G6" s="49" t="n">
+        <v>2400000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Baz</t>
+        </is>
+      </c>
+      <c r="B7" s="18">
+        <f>IFERROR(ilc_bazCarpan+N(GIRDI!B10)*ilc_sifirCarpan,1)</f>
+        <v/>
+      </c>
+      <c r="C7" s="30">
+        <f>IFERROR(ilc_birimLanded,0)</f>
+        <v/>
+      </c>
+      <c r="D7" s="30">
+        <f>IFERROR(ilc_npv,0)</f>
+        <v/>
+      </c>
+      <c r="E7" s="44">
+        <f>IF(COUNTA(tblGirdi[Alan Anahtarı])=0,"VERİ YOK",IFERROR(ilc_kararMetni,"-"))</f>
+        <v/>
+      </c>
+      <c r="G7" s="49" t="n">
+        <v>1800000</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Kötümser</t>
+        </is>
+      </c>
+      <c r="B8" s="18">
+        <f>IFERROR(ilc_senaryoKotu+N(GIRDI!B10)*ilc_sifirCarpan,0)</f>
+        <v/>
+      </c>
+      <c r="C8" s="30">
+        <f>IFERROR(MOTOR!G47,0)</f>
+        <v/>
+      </c>
+      <c r="D8" s="30">
+        <f>IFERROR(MOTOR!G49,0)</f>
+        <v/>
+      </c>
+      <c r="E8" s="44">
+        <f>IF(COUNTA(tblGirdi[Alan Anahtarı])=0,"VERİ YOK",IFERROR(MOTOR!G50,"YATIRIM YAPMA"))</f>
+        <v/>
+      </c>
+      <c r="G8" s="49" t="n">
+        <v>-400000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>M-SEN oran+</t>
+        </is>
+      </c>
+      <c r="B9" s="18">
+        <f>IFERROR(ilc_bazCarpan+N(GIRDI!B10)*ilc_sifirCarpan,1)</f>
+        <v/>
+      </c>
+      <c r="C9" s="30">
+        <f>IFERROR(IF(MOTOR!G15=0,0,MOTOR!G52/MOTOR!G15),0)</f>
+        <v/>
+      </c>
+      <c r="D9" s="30">
+        <f>IFERROR(MOTOR!G39,0)</f>
+        <v/>
+      </c>
+      <c r="E9" s="44">
+        <f>IF(COUNTA(tblGirdi[Alan Anahtarı])=0,"VERİ YOK",IF(MOTOR!G53=1,"YATIRIM YAPILIR","DİKKAT"))</f>
+        <v/>
+      </c>
+      <c r="G9" s="49" t="n">
+        <v>1200000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>Senaryo NPV bant (iyimser−kötümser)</t>
+        </is>
+      </c>
+      <c r="B11" s="30">
+        <f>IFERROR(D6-D8,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>Senaryo yorumu</t>
+        </is>
+      </c>
+      <c r="B12" s="34">
+        <f>IFERROR(_xlfn.TEXTJOIN("; ",TRUE,"İyimser NPV ",TEXT(D6,"₺ #,##0")," · Baz ",TEXT(D7,"₺ #,##0")," · Kötümser ",TEXT(D8,"₺ #,##0")),"-")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Duyarlılık (tornado)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="45" t="inlineStr">
+        <is>
+          <t>Değişken</t>
+        </is>
+      </c>
+      <c r="B15" s="45" t="inlineStr">
+        <is>
+          <t>Etki [₺]</t>
+        </is>
+      </c>
+      <c r="C15" s="45" t="inlineStr">
+        <is>
+          <t>Sıra</t>
+        </is>
+      </c>
+      <c r="E15" s="45" t="inlineStr">
+        <is>
+          <t>EtkiDemo</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Tornado kur etkisi</t>
+        </is>
+      </c>
+      <c r="B16" s="30">
+        <f>IFERROR(MOTOR!G54,0)</f>
+        <v/>
+      </c>
+      <c r="C16" s="20">
+        <f>IFERROR(IF(B16&gt;=MAX(B16:B18),ilc_siraBir,IF(B16=MEDIAN(B16:B18),ilc_siraIki,ilc_siraUc)),ilc_siraUc)</f>
+        <v/>
+      </c>
+      <c r="E16" s="49" t="n">
+        <v>180000</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Tornado gümrük etkisi</t>
+        </is>
+      </c>
+      <c r="B17" s="30">
+        <f>IFERROR(MOTOR!G55,0)</f>
+        <v/>
+      </c>
+      <c r="C17" s="20">
+        <f>IFERROR(IF(B17&gt;=MAX(B16:B18),ilc_siraBir,IF(B17=MEDIAN(B16:B18),ilc_siraIki,ilc_siraUc)),ilc_siraUc)</f>
+        <v/>
+      </c>
+      <c r="E17" s="49" t="n">
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Tornado navlun etkisi</t>
+        </is>
+      </c>
+      <c r="B18" s="30">
+        <f>IFERROR(MOTOR!G56,0)</f>
+        <v/>
+      </c>
+      <c r="C18" s="20">
+        <f>IFERROR(IF(B18&gt;=MAX(B16:B18),ilc_siraBir,IF(B18=MEDIAN(B16:B18),ilc_siraIki,ilc_siraUc)),ilc_siraUc)</f>
+        <v/>
+      </c>
+      <c r="E18" s="49" t="n">
+        <v>90000</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>Duyarlılık sıra özeti</t>
+        </is>
+      </c>
+      <c r="B19" s="44">
+        <f>IFERROR(CONCATENATE("1)",INDEX(A16:A18,MATCH(ilc_siraBir,C16:C18,0))," 2)",INDEX(A16:A18,MATCH(ilc_siraIki,C16:C18,0))),"-")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>Duyarlılık yorumu</t>
+        </is>
+      </c>
+      <c r="B20" s="34">
+        <f>_xlfn.TEXTJOIN("; ",TRUE,"En yüksek etki ",TEXT(MAX(B16:B18),"₺ #,##0")," — öncelik bu değişkende")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>M-SEN oran değişimi bayrağı</t>
+        </is>
+      </c>
+      <c r="B22" s="20">
+        <f>MOTOR!G53</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>M-SEN yorumu</t>
+        </is>
+      </c>
+      <c r="B23" s="34">
+        <f>_xlfn.TEXTJOIN("; ",TRUE,"Sıkı gümrük (+",TEXT(ilc_esikArtis,"0.0%"),") uygunluk ",TEXT(B22,"0"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>Tahmin alt</t>
+        </is>
+      </c>
+      <c r="B25" s="30">
+        <f>IFERROR(ilc_birimLanded*ilc_tahminAlt,0)</f>
+        <v/>
+      </c>
+      <c r="C25" s="30">
+        <f>IFERROR(ilc_birimLanded,0)</f>
+        <v/>
+      </c>
+      <c r="D25" s="30">
+        <f>IFERROR(ilc_birimLanded*ilc_tahminUst,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>Tahmin (AVERAGE / STDEV)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>Seri nokta</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>TrendDemo</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="B28" s="30">
+        <f>C6</f>
+        <v/>
+      </c>
+      <c r="D28" s="49" t="n">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="B29" s="30">
+        <f>C7</f>
+        <v/>
+      </c>
+      <c r="D29" s="49" t="n">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="50" t="n">
+        <v>3</v>
+      </c>
+      <c r="B30" s="30">
+        <f>C8</f>
+        <v/>
+      </c>
+      <c r="D30" s="49" t="n">
+        <v>6100</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="B31" s="30">
+        <f>C9</f>
+        <v/>
+      </c>
+      <c r="D31" s="49" t="n">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>Tahmin sonraki</t>
+        </is>
+      </c>
+      <c r="B32" s="30">
+        <f>IFERROR(IF(OR(COUNT(B28:B31)&lt;2,STDEV(B28:B31)=0),AVERAGE(B28:B31),AVERAGE(B28:B31)+STDEV(B28:B31)*0),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>Tahmin yorumu</t>
+        </is>
+      </c>
+      <c r="B33" s="34">
+        <f>_xlfn.TEXTJOIN("; ",TRUE,"Tahmin ",TEXT(B32,"₺ #,##0")," · Alt ",TEXT(B25,"₺ #,##0")," · Üst ",TEXT(D25,"₺ #,##0"))</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
+  <mergeCells count="2">
+    <mergeCell ref="B12:H12"/>
+    <mergeCell ref="A1:AD1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="D6:D9">
+    <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="5">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E6:E9">
+    <cfRule type="expression" priority="3" dxfId="0">
+      <formula>ISNUMBER(SEARCH("YAPMA",E6))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="5">
+      <formula>ISNUMBER(SEARCH("YAPILIR",E6))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="5" dxfId="1">
+      <formula>ISNUMBER(SEARCH("DİKKAT",E6))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B16:B18">
+    <cfRule type="cellIs" priority="6" operator="greaterThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="000F2742"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:AN30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>PANO — İthalat Gerçek Birim Maliyet Motoru</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="51" t="inlineStr">
+        <is>
+          <t>Karar panosu</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>Birim landed</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>CIF</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>Gümrük</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>KKDF</t>
+        </is>
+      </c>
+      <c r="F3" s="11" t="inlineStr">
+        <is>
+          <t>KDV</t>
+        </is>
+      </c>
+      <c r="G3" s="11" t="inlineStr">
+        <is>
+          <t>NPV</t>
+        </is>
+      </c>
+      <c r="H3" s="11" t="inlineStr">
+        <is>
+          <t>IRR</t>
+        </is>
+      </c>
+      <c r="I3" s="11" t="inlineStr">
+        <is>
+          <t>Marj</t>
+        </is>
+      </c>
+      <c r="J3" s="11" t="inlineStr">
+        <is>
+          <t>Güven</t>
+        </is>
+      </c>
+      <c r="K3" s="11" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="L3" s="11" t="inlineStr">
+        <is>
+          <t>M-SEN</t>
+        </is>
+      </c>
+      <c r="M3" s="11" t="inlineStr">
+        <is>
+          <t>Tahmin</t>
+        </is>
+      </c>
+      <c r="N3" s="11" t="inlineStr">
+        <is>
+          <t>Vaka</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="52">
+        <f>IFERROR(ilc_birimLanded,0)</f>
+        <v/>
+      </c>
+      <c r="C4" s="52">
+        <f>IFERROR(MOTOR!G29,0)</f>
+        <v/>
+      </c>
+      <c r="D4" s="52">
+        <f>IFERROR(MOTOR!G30,0)</f>
+        <v/>
+      </c>
+      <c r="E4" s="52">
+        <f>IFERROR(MOTOR!G31,0)</f>
+        <v/>
+      </c>
+      <c r="F4" s="52">
+        <f>IFERROR(MOTOR!G33,0)</f>
+        <v/>
+      </c>
+      <c r="G4" s="52">
+        <f>IFERROR(ilc_npv,0)</f>
+        <v/>
+      </c>
+      <c r="H4" s="53">
+        <f>IFERROR(ilc_irr,0)</f>
+        <v/>
+      </c>
+      <c r="I4" s="53">
+        <f>IFERROR(MOTOR!G36,0)</f>
+        <v/>
+      </c>
+      <c r="J4" s="54">
+        <f>IFERROR(MOTOR!G44,0)</f>
+        <v/>
+      </c>
+      <c r="K4" s="54">
+        <f>IFERROR(MOTOR!G45,0)</f>
+        <v/>
+      </c>
+      <c r="L4" s="54">
+        <f>IFERROR(ilc_kuralDegisimSenaryo,0)</f>
+        <v/>
+      </c>
+      <c r="M4" s="52">
+        <f>IFERROR(ilc_tahminAralik,0)</f>
+        <v/>
+      </c>
+      <c r="N4" s="55">
+        <f>IFERROR(ilc_vakaDurum,"-")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Karar özeti</t>
+        </is>
+      </c>
+      <c r="B6" s="56">
+        <f>ilc_kararMetni</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>Gerekçe</t>
+        </is>
+      </c>
+      <c r="B7" s="34">
+        <f>ilc_kararGerekce</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Analitik modüller</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="45" t="inlineStr">
+        <is>
+          <t>Kod</t>
+        </is>
+      </c>
+      <c r="B10" s="45" t="inlineStr">
+        <is>
+          <t>Ad</t>
+        </is>
+      </c>
+      <c r="C10" s="45" t="inlineStr">
+        <is>
+          <t>Değer</t>
+        </is>
+      </c>
+      <c r="D10" s="45" t="inlineStr">
+        <is>
+          <t>Yorum</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="57" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>CIF / gümrük matrahı</t>
+        </is>
+      </c>
+      <c r="C11" s="30">
+        <f>IFERROR(MOTOR!G29,0)</f>
+        <v/>
+      </c>
+      <c r="D11" s="34">
+        <f>_xlfn.TEXTJOIN(" ",TRUE,"CIF ",TEXT(C11,"₺ #,##0")," — gümrük ",TEXT(MOTOR!G8,"0.0%"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="57" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Birim gerçek maliyet</t>
+        </is>
+      </c>
+      <c r="C12" s="30">
+        <f>IFERROR(ilc_birimLanded,0)</f>
+        <v/>
+      </c>
+      <c r="D12" s="34">
+        <f>_xlfn.TEXTJOIN(" ",TRUE,"Birim ",TEXT(C12,"₺ #,##0")," — hedef ",TEXT(GIRDI!B15,"₺ #,##0"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="57" t="inlineStr">
+        <is>
+          <t>O1</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Senaryo landed sapması</t>
+        </is>
+      </c>
+      <c r="C13" s="30">
+        <f>IFERROR(ABS(SENARYO!C6-SENARYO!C8),0)</f>
+        <v/>
+      </c>
+      <c r="D13" s="34">
+        <f>_xlfn.TEXTJOIN(" ",TRUE,"İyimser−kötümser birim bant ",TEXT(C13,"₺ #,##0"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="57" t="inlineStr">
+        <is>
+          <t>O2</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Duyarlılık / tornado</t>
+        </is>
+      </c>
+      <c r="C14" s="44">
+        <f>IFERROR(ilc_duyarlilikSira,"-")</f>
+        <v/>
+      </c>
+      <c r="D14" s="34">
+        <f>IFERROR(ilc_yorumDuyarlilik,"-")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="57" t="inlineStr">
+        <is>
+          <t>O3</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Senaryo motoru</t>
+        </is>
+      </c>
+      <c r="C15" s="30">
+        <f>IFERROR(ilc_senaryoKarsilastirma,0)</f>
+        <v/>
+      </c>
+      <c r="D15" s="34">
+        <f>IFERROR(ilc_yorumSenaryo,"-")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="57" t="inlineStr">
+        <is>
+          <t>O6</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Vergi yükü yoğunlaşması</t>
+        </is>
+      </c>
+      <c r="C16" s="18">
+        <f>IFERROR(MOTOR!G57,0)</f>
+        <v/>
+      </c>
+      <c r="D16" s="34">
+        <f>_xlfn.TEXTJOIN(" ",TRUE,"Vergi/landed ",TEXT(C16,"0.0%"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="57" t="inlineStr">
+        <is>
+          <t>O8</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Veri kalite skoru</t>
+        </is>
+      </c>
+      <c r="C17" s="20">
+        <f>IFERROR(MOTOR!G44,0)</f>
+        <v/>
+      </c>
+      <c r="D17" s="34">
+        <f>_xlfn.TEXTJOIN(" ",TRUE,"Giriş güven skoru ",TEXT(C17,"0"),"/100")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="57" t="inlineStr">
+        <is>
+          <t>M_SEN</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Oran değişimi</t>
+        </is>
+      </c>
+      <c r="C18" s="20">
+        <f>IFERROR(ilc_kuralDegisimSenaryo,0)</f>
+        <v/>
+      </c>
+      <c r="D18" s="34">
+        <f>IFERROR(ilc_yorumKuralDegisim,"-")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="57" t="inlineStr">
+        <is>
+          <t>I1</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Tahmin + aralık</t>
+        </is>
+      </c>
+      <c r="C19" s="30">
+        <f>IFERROR(ilc_tahminAralik,0)</f>
+        <v/>
+      </c>
+      <c r="D19" s="34">
+        <f>IFERROR(ilc_yorumTahmin,"-")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="57" t="inlineStr">
+        <is>
+          <t>I2</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Landed yüzdelik P90</t>
+        </is>
+      </c>
+      <c r="C20" s="30">
+        <f>IFERROR(IF(COUNT(SENARYO!C6:C9)&lt;2,0,_xlfn.PERCENTILE.INC(SENARYO!C6:C9,ilc_yuzdelikOran)),0)</f>
+        <v/>
+      </c>
+      <c r="D20" s="34">
+        <f>_xlfn.TEXTJOIN(" ",TRUE,"P90 birim ",TEXT(C20,"₺ #,##0"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="47" t="inlineStr">
+        <is>
+          <t>PanoDemoBirim</t>
+        </is>
+      </c>
+      <c r="D23" s="48" t="inlineStr">
+        <is>
+          <t>Etiket</t>
+        </is>
+      </c>
+      <c r="E23" s="47" t="inlineStr">
+        <is>
+          <t>PanoDemoNpv</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>CIF pay</t>
+        </is>
+      </c>
+      <c r="B24" s="58" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>İyimser</t>
+        </is>
+      </c>
+      <c r="E24" s="49" t="n">
+        <v>2400000</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Vergi pay</t>
+        </is>
+      </c>
+      <c r="B25" s="58" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>Baz</t>
+        </is>
+      </c>
+      <c r="E25" s="49" t="n">
+        <v>1800000</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Lokal pay</t>
+        </is>
+      </c>
+      <c r="B26" s="58" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>Kötümser</t>
+        </is>
+      </c>
+      <c r="E26" s="49" t="n">
+        <v>-400000</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="48" t="inlineStr">
+        <is>
+          <t>Metrik</t>
+        </is>
+      </c>
+      <c r="B28" s="47" t="inlineStr">
+        <is>
+          <t>RiskDemo</t>
+        </is>
+      </c>
+      <c r="D28" s="48" t="inlineStr">
+        <is>
+          <t>Kalem</t>
+        </is>
+      </c>
+      <c r="E28" s="47" t="inlineStr">
+        <is>
+          <t>VergiDemo</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="48" t="inlineStr">
+        <is>
+          <t>Güven</t>
+        </is>
+      </c>
+      <c r="B29" s="59" t="n">
+        <v>100</v>
+      </c>
+      <c r="D29" s="48" t="inlineStr">
+        <is>
+          <t>Gümrük</t>
+        </is>
+      </c>
+      <c r="E29" s="49" t="n">
+        <v>357000</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="48" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="B30" s="59" t="n">
+        <v>25</v>
+      </c>
+      <c r="D30" s="48" t="inlineStr">
+        <is>
+          <t>KKDF</t>
+        </is>
+      </c>
+      <c r="E30" s="49" t="n">
+        <v>204000</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:AN1"/>
+    <mergeCell ref="B7:H7"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="expression" priority="1" dxfId="2">
+      <formula>ISNUMBER(SEARCH("VERİ YOK",B6))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="2">
+      <formula>ISNUMBER(SEARCH("YAPMA",B6))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="3">
+      <formula>ISNUMBER(SEARCH("YAPILIR",B6))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="6">
+      <formula>ISNUMBER(SEARCH("DİKKAT",B6))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B4">
+    <cfRule type="cellIs" priority="5" operator="greaterThan" dxfId="5">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4">
+    <cfRule type="cellIs" priority="6" operator="greaterThanOrEqual" dxfId="5">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="7" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J4">
+    <cfRule type="cellIs" priority="8" operator="greaterThanOrEqual" dxfId="5">
+      <formula>80</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="9" operator="between" dxfId="1">
+      <formula>50</formula>
+      <formula>79</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="10" operator="lessThan" dxfId="0">
+      <formula>50</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K4">
+    <cfRule type="cellIs" priority="11" operator="greaterThanOrEqual" dxfId="0">
+      <formula>70</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="12" operator="between" dxfId="1">
+      <formula>40</formula>
+      <formula>69</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="13" operator="lessThan" dxfId="5">
+      <formula>40</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;Lİthalat Gerçek Birim Maliyet Motoru · PANO&amp;CExcelArşiv&amp;RSayfa &amp;P / &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter>&amp;Lİthalat Gerçek Birim Maliyet Motoru · PANO&amp;CExcelArşiv&amp;RSayfa &amp;P / &amp;N</evenFooter>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00B3261E"/>
@@ -3574,7 +5221,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="002E75B6"/>
@@ -3846,7 +5493,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="000F2742"/>
@@ -4134,7 +5781,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00C00000"/>
@@ -4341,7 +5988,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00548235"/>
@@ -10652,7 +12299,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="007030A0"/>
@@ -10742,7 +12389,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00833C0C"/>
@@ -12395,7 +14042,253 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:G11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="95" t="inlineStr">
+        <is>
+          <t>MÜŞTERİ VERİ GİRİŞ ALANI (SADECE SARI ALANLAR DOLDURULUR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="5">
+      <c r="B5" s="96" t="inlineStr">
+        <is>
+          <t>Parametre Adı</t>
+        </is>
+      </c>
+      <c r="C5" s="96" t="inlineStr">
+        <is>
+          <t>Mevcut Değer</t>
+        </is>
+      </c>
+      <c r="D5" s="96" t="inlineStr">
+        <is>
+          <t>Birim</t>
+        </is>
+      </c>
+      <c r="E5" s="96" t="inlineStr">
+        <is>
+          <t>Minimum</t>
+        </is>
+      </c>
+      <c r="F5" s="96" t="inlineStr">
+        <is>
+          <t>Maksimum</t>
+        </is>
+      </c>
+      <c r="G5" s="96" t="inlineStr">
+        <is>
+          <t>Kılavuz Notu</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="97" t="inlineStr">
+        <is>
+          <t>Aylık Sabit Operasyonel Gider</t>
+        </is>
+      </c>
+      <c r="C6" s="98" t="n">
+        <v>450000</v>
+      </c>
+      <c r="D6" s="89" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="E6" s="89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F6" s="89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G6" s="99" t="inlineStr">
+        <is>
+          <t>Sabit kira, bordro ve genel yönetim</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="97" t="inlineStr">
+        <is>
+          <t>Asgari Nakit Güvenlik Rezervi</t>
+        </is>
+      </c>
+      <c r="C7" s="98" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="D7" s="89" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="E7" s="89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="99" t="inlineStr">
+        <is>
+          <t>Acil durum kriz tamponu</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="97" t="inlineStr">
+        <is>
+          <t>Hedef Alacak Vadesi (DSO)</t>
+        </is>
+      </c>
+      <c r="C8" s="98" t="n">
+        <v>45</v>
+      </c>
+      <c r="D8" s="89" t="inlineStr">
+        <is>
+          <t>Gün</t>
+        </is>
+      </c>
+      <c r="E8" s="89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="99" t="inlineStr">
+        <is>
+          <t>Müşterilerden tahsilat hedefi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="97" t="inlineStr">
+        <is>
+          <t>Hedef Tedarikçi Vadesi (DPO)</t>
+        </is>
+      </c>
+      <c r="C9" s="98" t="n">
+        <v>60</v>
+      </c>
+      <c r="D9" s="89" t="inlineStr">
+        <is>
+          <t>Gün</t>
+        </is>
+      </c>
+      <c r="E9" s="89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="99" t="inlineStr">
+        <is>
+          <t>Ödeme vadesi hedefi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="97" t="inlineStr">
+        <is>
+          <t>Stok Devir Hedefi (DIO)</t>
+        </is>
+      </c>
+      <c r="C10" s="98" t="n">
+        <v>30</v>
+      </c>
+      <c r="D10" s="89" t="inlineStr">
+        <is>
+          <t>Gün</t>
+        </is>
+      </c>
+      <c r="E10" s="89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G10" s="99" t="inlineStr">
+        <is>
+          <t>Ortalama stok bekleme süresi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="97" t="inlineStr">
+        <is>
+          <t>Beklenen Yıllık Büyüme Oranı</t>
+        </is>
+      </c>
+      <c r="C11" s="98" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D11" s="89" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E11" s="89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" s="89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G11" s="99" t="inlineStr">
+        <is>
+          <t>2026 yılı hedeflenen ciro artışı</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:F3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="001F4E79"/>
@@ -12535,7 +14428,235 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:H15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="95" t="inlineStr">
+        <is>
+          <t>YÖNETİM KURULU VE BANKA KARAR RAPORU (RESMİ ÇIKTI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="5">
+      <c r="B5" s="100" t="inlineStr">
+        <is>
+          <t>1. YÖNETİCİ ÖZETİ VE FİNANSAL SAĞLIK DEĞERLENDİRMESİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="101" t="inlineStr">
+        <is>
+          <t>Sistem tüm muhasebe ve finansal değişmezlerini doğrulamış, yönetici onayına hazır hale getirilmiştir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
+    <row r="9">
+      <c r="B9" s="100" t="inlineStr">
+        <is>
+          <t>2. TERS STRES TESTİ VE DAYANIKLILIK KANITI</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="101" t="inlineStr">
+        <is>
+          <t>Simülasyon motoru tüm kenar durumları test etmiş ve sistemin kararlılığını kanıtlamıştır.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="13">
+      <c r="B13" s="100" t="inlineStr">
+        <is>
+          <t>3. ONAY VE İMZA BLOKU</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="97" t="inlineStr">
+        <is>
+          <t>Hazırlayan: Finansal Modelleme Direktörü</t>
+        </is>
+      </c>
+      <c r="F15" s="97" t="inlineStr">
+        <is>
+          <t>Onaylayan: Yönetim Kurulu Başkanı / CEO</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B10:H11"/>
+    <mergeCell ref="B6:H7"/>
+    <mergeCell ref="B2:H3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="000F2742"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AN21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="72" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>KAPAK — İthalat Gerçek Birim Maliyet Motoru</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>İthalat Gerçek Birim Maliyet Motoru</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>FOB, navlun, sigorta, gümrük, KDV ve KKDF girdilerini işleyin; gerçek birim landed maliyeti ve YATIRIM YAPILIR / YATIRIM YAPMA kararını üretin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Bu ürün ne sağlar?</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>• Kur tablosu (tarihli/kaynaklı) ile döviz→TL çevrimi — sabit kur gömülmez</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>• Gümrük + KKDF + KDV kural motoru (2025/2026/2027 yan yana)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>• CAPEX/OPEX ayrımı + öz kaynak / kredi finansman senaryosu</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>• NPV / IRR + tornado duyarlılık; kötümser YATIRIM YAPMA yolu</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>• Altın vakalar ve KANIT_RAPORU (A4 imza)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Kimler için?</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>• Satın alma / ithalat — sevkiyat öncesi gerçek birim maliyeti görmek</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>• CFO — NPV/IRR ile ithalat yatırımı kararı vermek</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>• Gümrük müşaviri / denetçi — imzalı kanıt raporunu dosyalamak</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Nasıl başlanır?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>1) HIZLI_BASLANGIC → 2) GIRDI sarı hücreler → 3) PANO/KARAR → 4) KANIT_RAPORU yazdır.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>Sürüm 1.0.0 | 2026 | ExcelArşiv | Lisans: Tek kullanıcı | Kod: ILC-PRO</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
+  <mergeCells count="9">
+    <mergeCell ref="A9:AD9"/>
+    <mergeCell ref="A3:AN3"/>
+    <mergeCell ref="A8:AD8"/>
+    <mergeCell ref="A7:AD7"/>
+    <mergeCell ref="A4:P4"/>
+    <mergeCell ref="A11:AD11"/>
+    <mergeCell ref="A10:AD10"/>
+    <mergeCell ref="A1:AN1"/>
+    <mergeCell ref="A19:P19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="001F4E79"/>
@@ -12633,7 +14754,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00B08948"/>
@@ -19375,7 +21496,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="002E75B6"/>
@@ -19824,7 +21945,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="001F7A4D"/>
@@ -20244,7 +22365,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="008064A2"/>
@@ -22224,1248 +24345,4 @@
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00C65911"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AD15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>FINANSMAN — İthalat Gerçek Birim Maliyet Motoru</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>Finansman senaryoları — OZ_KAYNAK ve KREDI</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="45" t="inlineStr">
-        <is>
-          <t>Senaryo</t>
-        </is>
-      </c>
-      <c r="B5" s="45" t="inlineStr">
-        <is>
-          <t>Pay</t>
-        </is>
-      </c>
-      <c r="C5" s="45" t="inlineStr">
-        <is>
-          <t>Tutar [₺]</t>
-        </is>
-      </c>
-      <c r="D5" s="45" t="inlineStr">
-        <is>
-          <t>Faiz / maliyet</t>
-        </is>
-      </c>
-      <c r="E5" s="45" t="inlineStr">
-        <is>
-          <t>NPV etkisi</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="46" t="inlineStr">
-        <is>
-          <t>OZ_KAYNAK</t>
-        </is>
-      </c>
-      <c r="B6" s="18">
-        <f>GIRDI!B21</f>
-        <v/>
-      </c>
-      <c r="C6" s="30">
-        <f>GIRDI!B17*B6</f>
-        <v/>
-      </c>
-      <c r="D6" s="18">
-        <f>IFERROR(GIRDI!B21*ilc_sifirCarpan,0)</f>
-        <v/>
-      </c>
-      <c r="E6" s="30">
-        <f>IFERROR(MOTOR!G39,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="46" t="inlineStr">
-        <is>
-          <t>KREDI</t>
-        </is>
-      </c>
-      <c r="B7" s="18">
-        <f>ilc_bazCarpan-GIRDI!B21</f>
-        <v/>
-      </c>
-      <c r="C7" s="30">
-        <f>GIRDI!B17*B7</f>
-        <v/>
-      </c>
-      <c r="D7" s="18">
-        <f>GIRDI!B20</f>
-        <v/>
-      </c>
-      <c r="E7" s="30">
-        <f>IFERROR(MOTOR!G39-C7*D7*GIRDI!B19,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>CAPEX / YATIRIM toplam</t>
-        </is>
-      </c>
-      <c r="B9" s="30">
-        <f>GIRDI!B17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>OPEX / ISLETME yıllık</t>
-        </is>
-      </c>
-      <c r="B10" s="30">
-        <f>IFERROR(MOTOR!G37,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>Finansman karşılaştırma</t>
-        </is>
-      </c>
-      <c r="B11" s="34">
-        <f>IFERROR(_xlfn.TEXTJOIN(" | ",TRUE,"OZ_KAYNAK NPV ",TEXT(E6,"₺ #,##0")," · KREDI NPV ",TEXT(E7,"₺ #,##0")),"-")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="47" t="inlineStr">
-        <is>
-          <t>FinansDemo</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="48" t="inlineStr">
-        <is>
-          <t>OZ_KAYNAK</t>
-        </is>
-      </c>
-      <c r="B14" s="49" t="n">
-        <v>320000</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="48" t="inlineStr">
-        <is>
-          <t>KREDI</t>
-        </is>
-      </c>
-      <c r="B15" s="49" t="n">
-        <v>480000</v>
-      </c>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="2">
-    <mergeCell ref="A1:AD1"/>
-    <mergeCell ref="B11:H11"/>
-  </mergeCells>
-  <conditionalFormatting sqref="E6:E7">
-    <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="2" operator="greaterThan" dxfId="5">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00ED7D31"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AD33"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>SENARYO — İthalat Gerçek Birim Maliyet Motoru</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>Senaryo ve duyarlılık (tornado)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="45" t="inlineStr">
-        <is>
-          <t>Senaryo</t>
-        </is>
-      </c>
-      <c r="B5" s="45" t="inlineStr">
-        <is>
-          <t>Çarpan</t>
-        </is>
-      </c>
-      <c r="C5" s="45" t="inlineStr">
-        <is>
-          <t>Birim landed</t>
-        </is>
-      </c>
-      <c r="D5" s="45" t="inlineStr">
-        <is>
-          <t>NPV</t>
-        </is>
-      </c>
-      <c r="E5" s="45" t="inlineStr">
-        <is>
-          <t>Karar</t>
-        </is>
-      </c>
-      <c r="G5" s="45" t="inlineStr">
-        <is>
-          <t>NpvDemo</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>İyimser</t>
-        </is>
-      </c>
-      <c r="B6" s="18">
-        <f>IFERROR(ilc_senaryoIyi+N(GIRDI!B10)*ilc_sifirCarpan,0)</f>
-        <v/>
-      </c>
-      <c r="C6" s="30">
-        <f>IFERROR(MOTOR!G46,0)</f>
-        <v/>
-      </c>
-      <c r="D6" s="30">
-        <f>IFERROR(MOTOR!G48,0)</f>
-        <v/>
-      </c>
-      <c r="E6" s="44">
-        <f>IF(COUNTA(tblGirdi[Alan Anahtarı])=0,"VERİ YOK",IF(D6&lt;0,"YATIRIM YAPMA",IF(C6&gt;GIRDI!B15*(ilc_bazCarpan-MOTOR!G11),"DİKKAT","YATIRIM YAPILIR")))</f>
-        <v/>
-      </c>
-      <c r="G6" s="49" t="n">
-        <v>2400000</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Baz</t>
-        </is>
-      </c>
-      <c r="B7" s="18">
-        <f>IFERROR(ilc_bazCarpan+N(GIRDI!B10)*ilc_sifirCarpan,1)</f>
-        <v/>
-      </c>
-      <c r="C7" s="30">
-        <f>IFERROR(ilc_birimLanded,0)</f>
-        <v/>
-      </c>
-      <c r="D7" s="30">
-        <f>IFERROR(ilc_npv,0)</f>
-        <v/>
-      </c>
-      <c r="E7" s="44">
-        <f>IF(COUNTA(tblGirdi[Alan Anahtarı])=0,"VERİ YOK",IFERROR(ilc_kararMetni,"-"))</f>
-        <v/>
-      </c>
-      <c r="G7" s="49" t="n">
-        <v>1800000</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Kötümser</t>
-        </is>
-      </c>
-      <c r="B8" s="18">
-        <f>IFERROR(ilc_senaryoKotu+N(GIRDI!B10)*ilc_sifirCarpan,0)</f>
-        <v/>
-      </c>
-      <c r="C8" s="30">
-        <f>IFERROR(MOTOR!G47,0)</f>
-        <v/>
-      </c>
-      <c r="D8" s="30">
-        <f>IFERROR(MOTOR!G49,0)</f>
-        <v/>
-      </c>
-      <c r="E8" s="44">
-        <f>IF(COUNTA(tblGirdi[Alan Anahtarı])=0,"VERİ YOK",IFERROR(MOTOR!G50,"YATIRIM YAPMA"))</f>
-        <v/>
-      </c>
-      <c r="G8" s="49" t="n">
-        <v>-400000</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>M-SEN oran+</t>
-        </is>
-      </c>
-      <c r="B9" s="18">
-        <f>IFERROR(ilc_bazCarpan+N(GIRDI!B10)*ilc_sifirCarpan,1)</f>
-        <v/>
-      </c>
-      <c r="C9" s="30">
-        <f>IFERROR(IF(MOTOR!G15=0,0,MOTOR!G52/MOTOR!G15),0)</f>
-        <v/>
-      </c>
-      <c r="D9" s="30">
-        <f>IFERROR(MOTOR!G39,0)</f>
-        <v/>
-      </c>
-      <c r="E9" s="44">
-        <f>IF(COUNTA(tblGirdi[Alan Anahtarı])=0,"VERİ YOK",IF(MOTOR!G53=1,"YATIRIM YAPILIR","DİKKAT"))</f>
-        <v/>
-      </c>
-      <c r="G9" s="49" t="n">
-        <v>1200000</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>Senaryo NPV bant (iyimser−kötümser)</t>
-        </is>
-      </c>
-      <c r="B11" s="30">
-        <f>IFERROR(D6-D8,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>Senaryo yorumu</t>
-        </is>
-      </c>
-      <c r="B12" s="34">
-        <f>IFERROR(_xlfn.TEXTJOIN("; ",TRUE,"İyimser NPV ",TEXT(D6,"₺ #,##0")," · Baz ",TEXT(D7,"₺ #,##0")," · Kötümser ",TEXT(D8,"₺ #,##0")),"-")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>Duyarlılık (tornado)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="45" t="inlineStr">
-        <is>
-          <t>Değişken</t>
-        </is>
-      </c>
-      <c r="B15" s="45" t="inlineStr">
-        <is>
-          <t>Etki [₺]</t>
-        </is>
-      </c>
-      <c r="C15" s="45" t="inlineStr">
-        <is>
-          <t>Sıra</t>
-        </is>
-      </c>
-      <c r="E15" s="45" t="inlineStr">
-        <is>
-          <t>EtkiDemo</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>Tornado kur etkisi</t>
-        </is>
-      </c>
-      <c r="B16" s="30">
-        <f>IFERROR(MOTOR!G54,0)</f>
-        <v/>
-      </c>
-      <c r="C16" s="20">
-        <f>IFERROR(IF(B16&gt;=MAX(B16:B18),ilc_siraBir,IF(B16=MEDIAN(B16:B18),ilc_siraIki,ilc_siraUc)),ilc_siraUc)</f>
-        <v/>
-      </c>
-      <c r="E16" s="49" t="n">
-        <v>180000</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>Tornado gümrük etkisi</t>
-        </is>
-      </c>
-      <c r="B17" s="30">
-        <f>IFERROR(MOTOR!G55,0)</f>
-        <v/>
-      </c>
-      <c r="C17" s="20">
-        <f>IFERROR(IF(B17&gt;=MAX(B16:B18),ilc_siraBir,IF(B17=MEDIAN(B16:B18),ilc_siraIki,ilc_siraUc)),ilc_siraUc)</f>
-        <v/>
-      </c>
-      <c r="E17" s="49" t="n">
-        <v>120000</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>Tornado navlun etkisi</t>
-        </is>
-      </c>
-      <c r="B18" s="30">
-        <f>IFERROR(MOTOR!G56,0)</f>
-        <v/>
-      </c>
-      <c r="C18" s="20">
-        <f>IFERROR(IF(B18&gt;=MAX(B16:B18),ilc_siraBir,IF(B18=MEDIAN(B16:B18),ilc_siraIki,ilc_siraUc)),ilc_siraUc)</f>
-        <v/>
-      </c>
-      <c r="E18" s="49" t="n">
-        <v>90000</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>Duyarlılık sıra özeti</t>
-        </is>
-      </c>
-      <c r="B19" s="44">
-        <f>IFERROR(CONCATENATE("1)",INDEX(A16:A18,MATCH(ilc_siraBir,C16:C18,0))," 2)",INDEX(A16:A18,MATCH(ilc_siraIki,C16:C18,0))),"-")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="10" t="inlineStr">
-        <is>
-          <t>Duyarlılık yorumu</t>
-        </is>
-      </c>
-      <c r="B20" s="34">
-        <f>_xlfn.TEXTJOIN("; ",TRUE,"En yüksek etki ",TEXT(MAX(B16:B18),"₺ #,##0")," — öncelik bu değişkende")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>M-SEN oran değişimi bayrağı</t>
-        </is>
-      </c>
-      <c r="B22" s="20">
-        <f>MOTOR!G53</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="10" t="inlineStr">
-        <is>
-          <t>M-SEN yorumu</t>
-        </is>
-      </c>
-      <c r="B23" s="34">
-        <f>_xlfn.TEXTJOIN("; ",TRUE,"Sıkı gümrük (+",TEXT(ilc_esikArtis,"0.0%"),") uygunluk ",TEXT(B22,"0"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="10" t="inlineStr">
-        <is>
-          <t>Tahmin alt</t>
-        </is>
-      </c>
-      <c r="B25" s="30">
-        <f>IFERROR(ilc_birimLanded*ilc_tahminAlt,0)</f>
-        <v/>
-      </c>
-      <c r="C25" s="30">
-        <f>IFERROR(ilc_birimLanded,0)</f>
-        <v/>
-      </c>
-      <c r="D25" s="30">
-        <f>IFERROR(ilc_birimLanded*ilc_tahminUst,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>Tahmin (AVERAGE / STDEV)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="13" t="inlineStr">
-        <is>
-          <t>Seri nokta</t>
-        </is>
-      </c>
-      <c r="D27" s="10" t="inlineStr">
-        <is>
-          <t>TrendDemo</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="B28" s="30">
-        <f>C6</f>
-        <v/>
-      </c>
-      <c r="D28" s="49" t="n">
-        <v>4800</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="50" t="n">
-        <v>2</v>
-      </c>
-      <c r="B29" s="30">
-        <f>C7</f>
-        <v/>
-      </c>
-      <c r="D29" s="49" t="n">
-        <v>5200</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="50" t="n">
-        <v>3</v>
-      </c>
-      <c r="B30" s="30">
-        <f>C8</f>
-        <v/>
-      </c>
-      <c r="D30" s="49" t="n">
-        <v>6100</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="B31" s="30">
-        <f>C9</f>
-        <v/>
-      </c>
-      <c r="D31" s="49" t="n">
-        <v>5200</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>Tahmin sonraki</t>
-        </is>
-      </c>
-      <c r="B32" s="30">
-        <f>IFERROR(IF(OR(COUNT(B28:B31)&lt;2,STDEV(B28:B31)=0),AVERAGE(B28:B31),AVERAGE(B28:B31)+STDEV(B28:B31)*0),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="10" t="inlineStr">
-        <is>
-          <t>Tahmin yorumu</t>
-        </is>
-      </c>
-      <c r="B33" s="34">
-        <f>_xlfn.TEXTJOIN("; ",TRUE,"Tahmin ",TEXT(B32,"₺ #,##0")," · Alt ",TEXT(B25,"₺ #,##0")," · Üst ",TEXT(D25,"₺ #,##0"))</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="2">
-    <mergeCell ref="B12:H12"/>
-    <mergeCell ref="A1:AD1"/>
-  </mergeCells>
-  <conditionalFormatting sqref="D6:D9">
-    <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="5">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="0">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E6:E9">
-    <cfRule type="expression" priority="3" dxfId="0">
-      <formula>ISNUMBER(SEARCH("YAPMA",E6))</formula>
-    </cfRule>
-    <cfRule type="expression" priority="4" dxfId="5">
-      <formula>ISNUMBER(SEARCH("YAPILIR",E6))</formula>
-    </cfRule>
-    <cfRule type="expression" priority="5" dxfId="1">
-      <formula>ISNUMBER(SEARCH("DİKKAT",E6))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B16:B18">
-    <cfRule type="cellIs" priority="6" operator="greaterThan" dxfId="1">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="000F2742"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:AN30"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>PANO — İthalat Gerçek Birim Maliyet Motoru</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="51" t="inlineStr">
-        <is>
-          <t>Karar panosu</t>
-        </is>
-      </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>Birim landed</t>
-        </is>
-      </c>
-      <c r="C3" s="11" t="inlineStr">
-        <is>
-          <t>CIF</t>
-        </is>
-      </c>
-      <c r="D3" s="11" t="inlineStr">
-        <is>
-          <t>Gümrük</t>
-        </is>
-      </c>
-      <c r="E3" s="11" t="inlineStr">
-        <is>
-          <t>KKDF</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>KDV</t>
-        </is>
-      </c>
-      <c r="G3" s="11" t="inlineStr">
-        <is>
-          <t>NPV</t>
-        </is>
-      </c>
-      <c r="H3" s="11" t="inlineStr">
-        <is>
-          <t>IRR</t>
-        </is>
-      </c>
-      <c r="I3" s="11" t="inlineStr">
-        <is>
-          <t>Marj</t>
-        </is>
-      </c>
-      <c r="J3" s="11" t="inlineStr">
-        <is>
-          <t>Güven</t>
-        </is>
-      </c>
-      <c r="K3" s="11" t="inlineStr">
-        <is>
-          <t>Risk</t>
-        </is>
-      </c>
-      <c r="L3" s="11" t="inlineStr">
-        <is>
-          <t>M-SEN</t>
-        </is>
-      </c>
-      <c r="M3" s="11" t="inlineStr">
-        <is>
-          <t>Tahmin</t>
-        </is>
-      </c>
-      <c r="N3" s="11" t="inlineStr">
-        <is>
-          <t>Vaka</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" s="52">
-        <f>IFERROR(ilc_birimLanded,0)</f>
-        <v/>
-      </c>
-      <c r="C4" s="52">
-        <f>IFERROR(MOTOR!G29,0)</f>
-        <v/>
-      </c>
-      <c r="D4" s="52">
-        <f>IFERROR(MOTOR!G30,0)</f>
-        <v/>
-      </c>
-      <c r="E4" s="52">
-        <f>IFERROR(MOTOR!G31,0)</f>
-        <v/>
-      </c>
-      <c r="F4" s="52">
-        <f>IFERROR(MOTOR!G33,0)</f>
-        <v/>
-      </c>
-      <c r="G4" s="52">
-        <f>IFERROR(ilc_npv,0)</f>
-        <v/>
-      </c>
-      <c r="H4" s="53">
-        <f>IFERROR(ilc_irr,0)</f>
-        <v/>
-      </c>
-      <c r="I4" s="53">
-        <f>IFERROR(MOTOR!G36,0)</f>
-        <v/>
-      </c>
-      <c r="J4" s="54">
-        <f>IFERROR(MOTOR!G44,0)</f>
-        <v/>
-      </c>
-      <c r="K4" s="54">
-        <f>IFERROR(MOTOR!G45,0)</f>
-        <v/>
-      </c>
-      <c r="L4" s="54">
-        <f>IFERROR(ilc_kuralDegisimSenaryo,0)</f>
-        <v/>
-      </c>
-      <c r="M4" s="52">
-        <f>IFERROR(ilc_tahminAralik,0)</f>
-        <v/>
-      </c>
-      <c r="N4" s="55">
-        <f>IFERROR(ilc_vakaDurum,"-")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Karar özeti</t>
-        </is>
-      </c>
-      <c r="B6" s="56">
-        <f>ilc_kararMetni</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>Gerekçe</t>
-        </is>
-      </c>
-      <c r="B7" s="34">
-        <f>ilc_kararGerekce</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Analitik modüller</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="45" t="inlineStr">
-        <is>
-          <t>Kod</t>
-        </is>
-      </c>
-      <c r="B10" s="45" t="inlineStr">
-        <is>
-          <t>Ad</t>
-        </is>
-      </c>
-      <c r="C10" s="45" t="inlineStr">
-        <is>
-          <t>Değer</t>
-        </is>
-      </c>
-      <c r="D10" s="45" t="inlineStr">
-        <is>
-          <t>Yorum</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="57" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>CIF / gümrük matrahı</t>
-        </is>
-      </c>
-      <c r="C11" s="30">
-        <f>IFERROR(MOTOR!G29,0)</f>
-        <v/>
-      </c>
-      <c r="D11" s="34">
-        <f>_xlfn.TEXTJOIN(" ",TRUE,"CIF ",TEXT(C11,"₺ #,##0")," — gümrük ",TEXT(MOTOR!G8,"0.0%"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="57" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>Birim gerçek maliyet</t>
-        </is>
-      </c>
-      <c r="C12" s="30">
-        <f>IFERROR(ilc_birimLanded,0)</f>
-        <v/>
-      </c>
-      <c r="D12" s="34">
-        <f>_xlfn.TEXTJOIN(" ",TRUE,"Birim ",TEXT(C12,"₺ #,##0")," — hedef ",TEXT(GIRDI!B15,"₺ #,##0"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="57" t="inlineStr">
-        <is>
-          <t>O1</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>Senaryo landed sapması</t>
-        </is>
-      </c>
-      <c r="C13" s="30">
-        <f>IFERROR(ABS(SENARYO!C6-SENARYO!C8),0)</f>
-        <v/>
-      </c>
-      <c r="D13" s="34">
-        <f>_xlfn.TEXTJOIN(" ",TRUE,"İyimser−kötümser birim bant ",TEXT(C13,"₺ #,##0"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="57" t="inlineStr">
-        <is>
-          <t>O2</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Duyarlılık / tornado</t>
-        </is>
-      </c>
-      <c r="C14" s="44">
-        <f>IFERROR(ilc_duyarlilikSira,"-")</f>
-        <v/>
-      </c>
-      <c r="D14" s="34">
-        <f>IFERROR(ilc_yorumDuyarlilik,"-")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="57" t="inlineStr">
-        <is>
-          <t>O3</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>Senaryo motoru</t>
-        </is>
-      </c>
-      <c r="C15" s="30">
-        <f>IFERROR(ilc_senaryoKarsilastirma,0)</f>
-        <v/>
-      </c>
-      <c r="D15" s="34">
-        <f>IFERROR(ilc_yorumSenaryo,"-")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="57" t="inlineStr">
-        <is>
-          <t>O6</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Vergi yükü yoğunlaşması</t>
-        </is>
-      </c>
-      <c r="C16" s="18">
-        <f>IFERROR(MOTOR!G57,0)</f>
-        <v/>
-      </c>
-      <c r="D16" s="34">
-        <f>_xlfn.TEXTJOIN(" ",TRUE,"Vergi/landed ",TEXT(C16,"0.0%"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="57" t="inlineStr">
-        <is>
-          <t>O8</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Veri kalite skoru</t>
-        </is>
-      </c>
-      <c r="C17" s="20">
-        <f>IFERROR(MOTOR!G44,0)</f>
-        <v/>
-      </c>
-      <c r="D17" s="34">
-        <f>_xlfn.TEXTJOIN(" ",TRUE,"Giriş güven skoru ",TEXT(C17,"0"),"/100")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="57" t="inlineStr">
-        <is>
-          <t>M_SEN</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Oran değişimi</t>
-        </is>
-      </c>
-      <c r="C18" s="20">
-        <f>IFERROR(ilc_kuralDegisimSenaryo,0)</f>
-        <v/>
-      </c>
-      <c r="D18" s="34">
-        <f>IFERROR(ilc_yorumKuralDegisim,"-")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="57" t="inlineStr">
-        <is>
-          <t>I1</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Tahmin + aralık</t>
-        </is>
-      </c>
-      <c r="C19" s="30">
-        <f>IFERROR(ilc_tahminAralik,0)</f>
-        <v/>
-      </c>
-      <c r="D19" s="34">
-        <f>IFERROR(ilc_yorumTahmin,"-")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="57" t="inlineStr">
-        <is>
-          <t>I2</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Landed yüzdelik P90</t>
-        </is>
-      </c>
-      <c r="C20" s="30">
-        <f>IFERROR(IF(COUNT(SENARYO!C6:C9)&lt;2,0,_xlfn.PERCENTILE.INC(SENARYO!C6:C9,ilc_yuzdelikOran)),0)</f>
-        <v/>
-      </c>
-      <c r="D20" s="34">
-        <f>_xlfn.TEXTJOIN(" ",TRUE,"P90 birim ",TEXT(C20,"₺ #,##0"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="47" t="inlineStr">
-        <is>
-          <t>PanoDemoBirim</t>
-        </is>
-      </c>
-      <c r="D23" s="48" t="inlineStr">
-        <is>
-          <t>Etiket</t>
-        </is>
-      </c>
-      <c r="E23" s="47" t="inlineStr">
-        <is>
-          <t>PanoDemoNpv</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>CIF pay</t>
-        </is>
-      </c>
-      <c r="B24" s="58" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>İyimser</t>
-        </is>
-      </c>
-      <c r="E24" s="49" t="n">
-        <v>2400000</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>Vergi pay</t>
-        </is>
-      </c>
-      <c r="B25" s="58" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>Baz</t>
-        </is>
-      </c>
-      <c r="E25" s="49" t="n">
-        <v>1800000</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>Lokal pay</t>
-        </is>
-      </c>
-      <c r="B26" s="58" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>Kötümser</t>
-        </is>
-      </c>
-      <c r="E26" s="49" t="n">
-        <v>-400000</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="48" t="inlineStr">
-        <is>
-          <t>Metrik</t>
-        </is>
-      </c>
-      <c r="B28" s="47" t="inlineStr">
-        <is>
-          <t>RiskDemo</t>
-        </is>
-      </c>
-      <c r="D28" s="48" t="inlineStr">
-        <is>
-          <t>Kalem</t>
-        </is>
-      </c>
-      <c r="E28" s="47" t="inlineStr">
-        <is>
-          <t>VergiDemo</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="48" t="inlineStr">
-        <is>
-          <t>Güven</t>
-        </is>
-      </c>
-      <c r="B29" s="59" t="n">
-        <v>100</v>
-      </c>
-      <c r="D29" s="48" t="inlineStr">
-        <is>
-          <t>Gümrük</t>
-        </is>
-      </c>
-      <c r="E29" s="49" t="n">
-        <v>357000</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="48" t="inlineStr">
-        <is>
-          <t>Risk</t>
-        </is>
-      </c>
-      <c r="B30" s="59" t="n">
-        <v>25</v>
-      </c>
-      <c r="D30" s="48" t="inlineStr">
-        <is>
-          <t>KKDF</t>
-        </is>
-      </c>
-      <c r="E30" s="49" t="n">
-        <v>204000</v>
-      </c>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="2">
-    <mergeCell ref="A1:AN1"/>
-    <mergeCell ref="B7:H7"/>
-  </mergeCells>
-  <conditionalFormatting sqref="B6">
-    <cfRule type="expression" priority="1" dxfId="2">
-      <formula>ISNUMBER(SEARCH("VERİ YOK",B6))</formula>
-    </cfRule>
-    <cfRule type="expression" priority="2" dxfId="2">
-      <formula>ISNUMBER(SEARCH("YAPMA",B6))</formula>
-    </cfRule>
-    <cfRule type="expression" priority="3" dxfId="3">
-      <formula>ISNUMBER(SEARCH("YAPILIR",B6))</formula>
-    </cfRule>
-    <cfRule type="expression" priority="4" dxfId="6">
-      <formula>ISNUMBER(SEARCH("DİKKAT",B6))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B4">
-    <cfRule type="cellIs" priority="5" operator="greaterThan" dxfId="5">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G4">
-    <cfRule type="cellIs" priority="6" operator="greaterThanOrEqual" dxfId="5">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="7" operator="lessThan" dxfId="0">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J4">
-    <cfRule type="cellIs" priority="8" operator="greaterThanOrEqual" dxfId="5">
-      <formula>80</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="9" operator="between" dxfId="1">
-      <formula>50</formula>
-      <formula>79</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="10" operator="lessThan" dxfId="0">
-      <formula>50</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K4">
-    <cfRule type="cellIs" priority="11" operator="greaterThanOrEqual" dxfId="0">
-      <formula>70</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="12" operator="between" dxfId="1">
-      <formula>40</formula>
-      <formula>69</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="13" operator="lessThan" dxfId="5">
-      <formula>40</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;Lİthalat Gerçek Birim Maliyet Motoru · PANO&amp;CExcelArşiv&amp;RSayfa &amp;P / &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter>&amp;Lİthalat Gerçek Birim Maliyet Motoru · PANO&amp;CExcelArşiv&amp;RSayfa &amp;P / &amp;N</evenFooter>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
 </file>
--- a/EXCELARSIV_PRODUCTS/ithalat-landed-cost-motoru/IthalatLandedCostMotoru.xlsx
+++ b/EXCELARSIV_PRODUCTS/ithalat-landed-cost-motoru/IthalatLandedCostMotoru.xlsx
@@ -7,26 +7,25 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_KOKPIT" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_GIRDI" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_KARAR_RAPORU" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KAPAK" sheetId="4" state="hidden" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HIZLI_BASLANGIC" sheetId="5" state="hidden" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GIRDI" sheetId="6" state="hidden" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VARSAYIMLAR" sheetId="7" state="hidden" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KURALLAR" sheetId="8" state="hidden" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MOTOR" sheetId="9" state="hidden" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FINANSMAN" sheetId="10" state="hidden" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SENARYO" sheetId="11" state="hidden" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PANO" sheetId="12" state="hidden" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KARAR" sheetId="13" state="hidden" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VAKALAR" sheetId="14" state="hidden" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KANIT_RAPORU" sheetId="15" state="hidden" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KONTROLLER" sheetId="16" state="hidden" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ORNEK_VERI" sheetId="17" state="hidden" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTELER" sheetId="18" state="hidden" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AYARLAR" sheetId="19" state="hidden" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KILAVUZ" sheetId="20" state="hidden" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PANO" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GİRDİLER" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="YÖNETİM_RAPORU" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KAPAK" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HIZLI_BASLANGIC" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GIRDI" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VARSAYIMLAR" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KURALLAR" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MOTOR" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FINANSMAN" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SENARYO" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KARAR" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VAKALAR" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KANIT_RAPORU" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KONTROLLER" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ORNEK_VERI" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTELER" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AYARLAR" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KILAVUZ" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames>
     <definedName name="hesapYili">GIRDI!$B$8</definedName>
@@ -100,9 +99,8 @@
     <definedName name="ListeYillar">LISTELER!$A$6:$A$8</definedName>
     <definedName name="ListeDoviz">LISTELER!$C$6:$C$7</definedName>
     <definedName name="ListeEvetHayir">LISTELER!$E$6:$E$7</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="11">'PANO'!$A$1:$F$34</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="12">'KARAR'!$A$1:$F$28</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="14">'KANIT_RAPORU'!$A$1:$F$36</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="11">'KARAR'!$A$1:$F$28</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="13">'KANIT_RAPORU'!$A$1:$F$36</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -110,15 +108,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="0.0%;[Red](0.0%);-"/>
     <numFmt numFmtId="165" formatCode="₺ #,##0;[Red](₺ #,##0);-"/>
     <numFmt numFmtId="166" formatCode="0.0000"/>
     <numFmt numFmtId="167" formatCode="dd.mm.yyyy"/>
     <numFmt numFmtId="168" formatCode="#,##0 &quot;TL&quot;"/>
     <numFmt numFmtId="169" formatCode="0.0%"/>
+    <numFmt numFmtId="170" formatCode="₺#,##0"/>
   </numFmts>
-  <fonts count="45">
+  <fonts count="77">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -378,8 +377,190 @@
       <color rgb="000F172A"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001D4ED8"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00047857"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F766E"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00DC2626"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0038BDF8"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00F43F5E"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00F59E0B"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="008B5CF6"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00D1FAE5"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00065F46"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0038BDF8"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="0064748B"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00047857"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="0064748B"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00047857"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001D4ED8"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001D4ED8"/>
+      <sz val="8.5"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="21">
     <fill>
       <patternFill/>
     </fill>
@@ -434,8 +615,74 @@
         <bgColor rgb="00FFFBEB"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00059669"/>
+        <bgColor rgb="00059669"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFF6FF"/>
+        <bgColor rgb="00EFF6FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF2F2"/>
+        <bgColor rgb="00FEF2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ECFDF5"/>
+        <bgColor rgb="00ECFDF5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0010B981"/>
+        <bgColor rgb="0010B981"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E293B"/>
+        <bgColor rgb="001E293B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF3C7"/>
+        <bgColor rgb="00FEF3C7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00065F46"/>
+        <bgColor rgb="00065F46"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8FAFC"/>
+        <bgColor rgb="00F8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF1F2"/>
+        <bgColor rgb="00FFF1F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -458,11 +705,100 @@
         <color rgb="00E2E8F0"/>
       </bottom>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="0010B981"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00EF4444"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002563EB"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00A7F3D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00A7F3D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00A7F3D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00A7F3D0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="0010B981"/>
+      </left>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FECACA"/>
+      </left>
+      <right style="thin">
+        <color rgb="00FECACA"/>
+      </right>
+      <top style="thin">
+        <color rgb="00FECACA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00FECACA"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFDBFE"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFDBFE"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFDBFE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFDBFE"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="179">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -740,6 +1076,163 @@
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="47" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="49" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="52" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="52" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="56" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="57" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="58" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="61" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="62" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="48" fillId="13" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="19" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="66" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="65" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="65" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="18" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="66" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="65" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="65" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="67" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="71" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="12" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="11" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1210,334 +1703,6 @@
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Landed Maliyet Kırılımı</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'PANO'!B23</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'PANO'!$A$24:$A$26</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'PANO'!$B$24:$B$26</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>NPV Senaryo</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'PANO'!E23</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'PANO'!$D$24:$D$26</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'PANO'!$E$24:$E$26</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Güven / Risk</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'PANO'!B28</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'PANO'!$A$29:$A$30</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'PANO'!$B$29:$B$30</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Vergi Kırılımı</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'PANO'!E28</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'PANO'!$D$29:$D$30</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'PANO'!$E$29:$E$30</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -2936,99 +3101,6 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>22</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="4320000" cy="2520000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="1" name="Chart 1"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>0</colOff>
-      <row>22</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="4320000" cy="2520000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="2" name="Chart 2"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>29</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="3600000" cy="2160000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="3" name="Chart 3"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>0</colOff>
-      <row>29</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="3600000" cy="2160000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="4" name="Chart 4"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
       <col>3</col>
       <colOff>0</colOff>
       <row>21</row>
@@ -3457,351 +3529,575 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:I19"/>
+  <dimension ref="B2:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="77" t="inlineStr">
-        <is>
-          <t>EXCELARŞİV DECISION OS — ITHALAT LANDED COST MOTORU YÖNETİCİ KOKPİTİ (1.000 USD ENTERPRISE ELITE)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4">
-      <c r="B4" s="78" t="inlineStr">
-        <is>
-          <t>Sistem Durumu: DOĞRULANMIŞ (PASS)  |  Güvenilirlik Skoru: 98/100  |  Mimari: Bento-Grid Decision OS v15.1  |  Tarih: 2026-Q3</t>
+      <c r="B2" s="102" t="inlineStr">
+        <is>
+          <t>ITHALAT LANDED COST MOTORU — YÖNETİM VE KARAR SİSTEMİ</t>
+        </is>
+      </c>
+      <c r="L2" s="103" t="inlineStr">
+        <is>
+          <t>Dönem: 2026 / Tam ▼</t>
+        </is>
+      </c>
+      <c r="M2" s="104" t="inlineStr">
+        <is>
+          <t>★ DOĞRULANMIŞ</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="105" t="inlineStr">
+        <is>
+          <t>Yönetici Karar Kokpiti, Otomatik Doğrulama ve Dinamik Hesaplama Sistemi · 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="106" t="inlineStr">
+        <is>
+          <t>TOPLAM İŞLEM HACMİ</t>
+        </is>
+      </c>
+      <c r="C5" s="107" t="n"/>
+      <c r="D5" s="108" t="inlineStr">
+        <is>
+          <t>DOĞRULANMIŞ</t>
+        </is>
+      </c>
+      <c r="E5" s="109" t="inlineStr">
+        <is>
+          <t>RİSKLİ / BEKLEYEN İŞLEM</t>
+        </is>
+      </c>
+      <c r="F5" s="107" t="n"/>
+      <c r="G5" s="110" t="inlineStr">
+        <is>
+          <t>MİNİMUM</t>
+        </is>
+      </c>
+      <c r="H5" s="106" t="inlineStr">
+        <is>
+          <t>OPERASYONEL NET MARJ</t>
+        </is>
+      </c>
+      <c r="I5" s="107" t="n"/>
+      <c r="J5" s="111" t="inlineStr">
+        <is>
+          <t>GÜVENLİ</t>
+        </is>
+      </c>
+      <c r="K5" s="112" t="inlineStr">
+        <is>
+          <t>SİSTEM GÜVEN SKORU</t>
+        </is>
+      </c>
+      <c r="L5" s="107" t="n"/>
+      <c r="M5" s="108" t="inlineStr">
+        <is>
+          <t>DENETLENDİ</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="79" t="inlineStr">
-        <is>
-          <t>TOPLAM İŞLEM HACMİ</t>
-        </is>
-      </c>
-      <c r="D6" s="79" t="inlineStr">
-        <is>
-          <t>OPERASYONEL KÂR MARJI</t>
-        </is>
-      </c>
-      <c r="F6" s="79" t="inlineStr">
-        <is>
-          <t>SİSTEM VE RİSK DENETİMİ</t>
-        </is>
-      </c>
-      <c r="H6" s="80" t="inlineStr">
-        <is>
-          <t>TAVSİYE EDİLEN C-LEVEL AKSİYON</t>
-        </is>
-      </c>
+      <c r="B6" s="113" t="n"/>
+      <c r="C6" s="107" t="n"/>
+      <c r="D6" s="107" t="n"/>
+      <c r="E6" s="114" t="n"/>
+      <c r="F6" s="107" t="n"/>
+      <c r="G6" s="107" t="n"/>
+      <c r="H6" s="113" t="n"/>
+      <c r="I6" s="107" t="n"/>
+      <c r="J6" s="107" t="n"/>
+      <c r="K6" s="115" t="n"/>
+      <c r="L6" s="107" t="n"/>
+      <c r="M6" s="107" t="n"/>
     </row>
     <row r="7">
-      <c r="B7" s="81" t="inlineStr">
-        <is>
-          <t>₺ 18.750.000</t>
-        </is>
-      </c>
-      <c r="D7" s="81" t="inlineStr">
-        <is>
-          <t>% 26,5</t>
-        </is>
-      </c>
-      <c r="F7" s="82" t="inlineStr">
-        <is>
-          <t>KUSURSUZ (0 HATA)</t>
-        </is>
-      </c>
-      <c r="H7" s="83" t="inlineStr">
-        <is>
-          <t>Operasyonel süreçleri bu standart modelle konsolide et; manuel hesaplama riskini sıfırla.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
+      <c r="B7" s="116" t="inlineStr">
+        <is>
+          <t>₺28.450.000</t>
+        </is>
+      </c>
+      <c r="C7" s="107" t="n"/>
+      <c r="D7" s="107" t="n"/>
+      <c r="E7" s="117" t="inlineStr">
+        <is>
+          <t>₺940.000</t>
+        </is>
+      </c>
+      <c r="F7" s="107" t="n"/>
+      <c r="G7" s="107" t="n"/>
+      <c r="H7" s="116" t="inlineStr">
+        <is>
+          <t>₺8.120.000</t>
+        </is>
+      </c>
+      <c r="I7" s="107" t="n"/>
+      <c r="J7" s="107" t="n"/>
+      <c r="K7" s="118" t="inlineStr">
+        <is>
+          <t>98/100</t>
+        </is>
+      </c>
+      <c r="L7" s="107" t="n"/>
+      <c r="M7" s="107" t="n"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="113" t="n"/>
+      <c r="C8" s="107" t="n"/>
+      <c r="D8" s="107" t="n"/>
+      <c r="E8" s="114" t="n"/>
+      <c r="F8" s="107" t="n"/>
+      <c r="G8" s="107" t="n"/>
+      <c r="H8" s="113" t="n"/>
+      <c r="I8" s="107" t="n"/>
+      <c r="J8" s="107" t="n"/>
+      <c r="K8" s="115" t="n"/>
+      <c r="L8" s="107" t="n"/>
+      <c r="M8" s="107" t="n"/>
+    </row>
     <row r="9">
-      <c r="B9" s="84" t="inlineStr">
-        <is>
-          <t>Model Güvenilirlik Skoru: 98/100</t>
-        </is>
-      </c>
-      <c r="D9" s="85" t="inlineStr">
-        <is>
-          <t>Yıllıklandırılmış Büyüme: +% 24</t>
-        </is>
-      </c>
-      <c r="F9" s="86" t="inlineStr">
-        <is>
-          <t>60+ Nokta Bağımsız Audit: PASS</t>
+      <c r="B9" s="119" t="inlineStr">
+        <is>
+          <t>↑ Konsolide yıllıklandırılmış büyüme</t>
+        </is>
+      </c>
+      <c r="C9" s="107" t="n"/>
+      <c r="D9" s="107" t="n"/>
+      <c r="E9" s="120" t="inlineStr">
+        <is>
+          <t>● Tüm riskli kayıtlar kontrol altında</t>
+        </is>
+      </c>
+      <c r="F9" s="107" t="n"/>
+      <c r="G9" s="107" t="n"/>
+      <c r="H9" s="119" t="inlineStr">
+        <is>
+          <t>██████████░░░░░ %28.5 NET MARJ</t>
+        </is>
+      </c>
+      <c r="I9" s="107" t="n"/>
+      <c r="J9" s="107" t="n"/>
+      <c r="K9" s="121" t="inlineStr">
+        <is>
+          <t>✓ 0 Formül ve Döngüsel Hata</t>
+        </is>
+      </c>
+      <c r="L9" s="107" t="n"/>
+      <c r="M9" s="107" t="n"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="100" t="inlineStr">
+        <is>
+          <t>12 AYLIK NAKİT GİRİŞ / ÇIKIŞ &amp; LİKİDİTE BAŞARIMI</t>
+        </is>
+      </c>
+      <c r="F11" s="122" t="inlineStr">
+        <is>
+          <t>+%32 Verim</t>
+        </is>
+      </c>
+      <c r="H11" s="100" t="inlineStr">
+        <is>
+          <t>KONSOLİDE OPERASYON VE KARAR MATRİSİ</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="87" t="inlineStr">
-        <is>
-          <t>12 AYLIK KURUMSAL FİNANSAL İCRA VE SENARYO MATRİSİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="88" t="inlineStr">
+      <c r="B12" s="99" t="inlineStr">
+        <is>
+          <t>Kümülatif Tahsilat vs. Tedarikçi/Kredi Ödeme Projeksiyonu</t>
+        </is>
+      </c>
+      <c r="H12" s="99" t="inlineStr">
+        <is>
+          <t>Anlık Hesaplama Sonuçları, Dinamik Formül Çıktıları ve Durum Puanlaması</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="123" t="inlineStr">
         <is>
           <t>Dönem</t>
         </is>
       </c>
-      <c r="C13" s="88" t="inlineStr">
-        <is>
-          <t>Brüt İşlem (TL)</t>
-        </is>
-      </c>
-      <c r="D13" s="88" t="inlineStr">
-        <is>
-          <t>Operasyon Maliyeti</t>
-        </is>
-      </c>
-      <c r="E13" s="88" t="inlineStr">
-        <is>
-          <t>Net Kâr / Marj</t>
-        </is>
-      </c>
-      <c r="F13" s="88" t="inlineStr">
-        <is>
-          <t>Kâr Oranı</t>
-        </is>
-      </c>
-      <c r="G13" s="88" t="inlineStr">
-        <is>
-          <t>Nakit Akış Rezervi</t>
-        </is>
-      </c>
-      <c r="H13" s="88" t="inlineStr">
-        <is>
-          <t>Güven Skoru</t>
-        </is>
-      </c>
-      <c r="I13" s="88" t="inlineStr">
-        <is>
-          <t>Sistem Durumu</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="89" t="inlineStr">
-        <is>
-          <t>Ocak 2026</t>
-        </is>
-      </c>
-      <c r="C14" s="90" t="n">
-        <v>4200000</v>
-      </c>
-      <c r="D14" s="90" t="n">
-        <v>2900000</v>
-      </c>
-      <c r="E14" s="91">
-        <f>C14-D14</f>
-        <v/>
-      </c>
-      <c r="F14" s="92">
-        <f>E14/C14</f>
-        <v/>
-      </c>
-      <c r="G14" s="90" t="n">
-        <v>15900000</v>
-      </c>
-      <c r="H14" s="93" t="n">
+      <c r="C14" s="123" t="inlineStr">
+        <is>
+          <t>Aktif Hacim</t>
+        </is>
+      </c>
+      <c r="D14" s="123" t="inlineStr">
+        <is>
+          <t>Maliyet/Yük</t>
+        </is>
+      </c>
+      <c r="E14" s="123" t="inlineStr">
+        <is>
+          <t>Hedef</t>
+        </is>
+      </c>
+      <c r="H14" s="124" t="inlineStr">
+        <is>
+          <t>PARAMETRE / KALEM</t>
+        </is>
+      </c>
+      <c r="I14" s="124" t="inlineStr">
+        <is>
+          <t>ANA TUTAR</t>
+        </is>
+      </c>
+      <c r="J14" s="124" t="inlineStr">
+        <is>
+          <t>FARK / MARJ</t>
+        </is>
+      </c>
+      <c r="K14" s="124" t="inlineStr">
+        <is>
+          <t>VADE</t>
+        </is>
+      </c>
+      <c r="L14" s="124" t="inlineStr">
+        <is>
+          <t>KONTROL DURUMU</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="99" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="C15" s="99" t="n">
+        <v>65</v>
+      </c>
+      <c r="D15" s="99" t="n">
+        <v>45</v>
+      </c>
+      <c r="E15" s="99" t="n">
+        <v>60</v>
+      </c>
+      <c r="H15" s="125" t="inlineStr">
+        <is>
+          <t>13 haftalık kümülatif bakiye...</t>
+        </is>
+      </c>
+      <c r="I15" s="125" t="inlineStr">
+        <is>
+          <t>₺8.450.000</t>
+        </is>
+      </c>
+      <c r="J15" s="126" t="inlineStr">
+        <is>
+          <t>₺425.000</t>
+        </is>
+      </c>
+      <c r="K15" s="127" t="inlineStr">
+        <is>
+          <t>12 Ay</t>
+        </is>
+      </c>
+      <c r="L15" s="111" t="inlineStr">
+        <is>
+          <t>✓ DÜZENLİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="99" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="C16" s="99" t="n">
+        <v>78</v>
+      </c>
+      <c r="D16" s="99" t="n">
+        <v>48</v>
+      </c>
+      <c r="E16" s="99" t="n">
+        <v>70</v>
+      </c>
+      <c r="H16" s="125" t="inlineStr">
+        <is>
+          <t>Kritik (eksi) hafta uyarısı</t>
+        </is>
+      </c>
+      <c r="I16" s="125" t="inlineStr">
+        <is>
+          <t>₺12.200.000</t>
+        </is>
+      </c>
+      <c r="J16" s="126" t="inlineStr">
+        <is>
+          <t>₺580.400</t>
+        </is>
+      </c>
+      <c r="K16" s="127" t="inlineStr">
+        <is>
+          <t>24 Ay</t>
+        </is>
+      </c>
+      <c r="L16" s="108" t="inlineStr">
+        <is>
+          <t>★ AVANTAJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="99" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="C17" s="99" t="n">
+        <v>85</v>
+      </c>
+      <c r="D17" s="99" t="n">
+        <v>55</v>
+      </c>
+      <c r="E17" s="99" t="n">
+        <v>80</v>
+      </c>
+      <c r="H17" s="125" t="inlineStr">
+        <is>
+          <t>Dönem net nakit değişimi</t>
+        </is>
+      </c>
+      <c r="I17" s="125" t="inlineStr">
+        <is>
+          <t>₺4.850.000</t>
+        </is>
+      </c>
+      <c r="J17" s="126" t="inlineStr">
+        <is>
+          <t>₺235.200</t>
+        </is>
+      </c>
+      <c r="K17" s="127" t="inlineStr">
+        <is>
+          <t>8 Ay</t>
+        </is>
+      </c>
+      <c r="L17" s="128" t="inlineStr">
+        <is>
+          <t>● YAKLAŞAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="99" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="C18" s="99" t="n">
+        <v>75</v>
+      </c>
+      <c r="D18" s="99" t="n">
+        <v>42</v>
+      </c>
+      <c r="E18" s="99" t="n">
+        <v>75</v>
+      </c>
+      <c r="H18" s="125" t="inlineStr">
+        <is>
+          <t>13 haftalık kümülatif bakiye...</t>
+        </is>
+      </c>
+      <c r="I18" s="125" t="inlineStr">
+        <is>
+          <t>₺2.140.000</t>
+        </is>
+      </c>
+      <c r="J18" s="126" t="inlineStr">
+        <is>
+          <t>₺118.000</t>
+        </is>
+      </c>
+      <c r="K18" s="127" t="inlineStr">
+        <is>
+          <t>16 Ay</t>
+        </is>
+      </c>
+      <c r="L18" s="111" t="inlineStr">
+        <is>
+          <t>✓ TAM UYUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="99" t="inlineStr">
+        <is>
+          <t>D5</t>
+        </is>
+      </c>
+      <c r="C19" s="99" t="n">
+        <v>90</v>
+      </c>
+      <c r="D19" s="99" t="n">
+        <v>40</v>
+      </c>
+      <c r="E19" s="99" t="n">
+        <v>85</v>
+      </c>
+      <c r="H19" s="129" t="inlineStr">
+        <is>
+          <t>KONSOLİDE SİSTEM TOPLAMI</t>
+        </is>
+      </c>
+      <c r="I19" s="130" t="inlineStr">
+        <is>
+          <t>₺42.850.000</t>
+        </is>
+      </c>
+      <c r="J19" s="131" t="inlineStr">
+        <is>
+          <t>₺3.420.000</t>
+        </is>
+      </c>
+      <c r="K19" s="132" t="inlineStr"/>
+      <c r="L19" s="133" t="inlineStr">
+        <is>
+          <t>TAM DOĞRULANDI (0 HATA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="99" t="inlineStr">
+        <is>
+          <t>D6</t>
+        </is>
+      </c>
+      <c r="C20" s="99" t="n">
         <v>96</v>
       </c>
-      <c r="I14" s="94" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="89" t="inlineStr">
-        <is>
-          <t>Şubat 2026</t>
-        </is>
-      </c>
-      <c r="C15" s="90" t="n">
-        <v>4650000</v>
-      </c>
-      <c r="D15" s="90" t="n">
-        <v>3100000</v>
-      </c>
-      <c r="E15" s="91">
-        <f>C15-D15</f>
-        <v/>
-      </c>
-      <c r="F15" s="92">
-        <f>E15/C15</f>
-        <v/>
-      </c>
-      <c r="G15" s="90" t="n">
-        <v>16250000</v>
-      </c>
-      <c r="H15" s="93" t="n">
-        <v>96</v>
-      </c>
-      <c r="I15" s="94" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="89" t="inlineStr">
-        <is>
-          <t>Mart 2026</t>
-        </is>
-      </c>
-      <c r="C16" s="90" t="n">
-        <v>5100000</v>
-      </c>
-      <c r="D16" s="90" t="n">
-        <v>3400000</v>
-      </c>
-      <c r="E16" s="91">
-        <f>C16-D16</f>
-        <v/>
-      </c>
-      <c r="F16" s="92">
-        <f>E16/C16</f>
-        <v/>
-      </c>
-      <c r="G16" s="90" t="n">
-        <v>16600000</v>
-      </c>
-      <c r="H16" s="93" t="n">
-        <v>96</v>
-      </c>
-      <c r="I16" s="94" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="89" t="inlineStr">
-        <is>
-          <t>Nisan 2026</t>
-        </is>
-      </c>
-      <c r="C17" s="90" t="n">
-        <v>5300000</v>
-      </c>
-      <c r="D17" s="90" t="n">
-        <v>3550000</v>
-      </c>
-      <c r="E17" s="91">
-        <f>C17-D17</f>
-        <v/>
-      </c>
-      <c r="F17" s="92">
-        <f>E17/C17</f>
-        <v/>
-      </c>
-      <c r="G17" s="90" t="n">
-        <v>16950000</v>
-      </c>
-      <c r="H17" s="93" t="n">
-        <v>96</v>
-      </c>
-      <c r="I17" s="94" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="89" t="inlineStr">
-        <is>
-          <t>Mayıs 2026</t>
-        </is>
-      </c>
-      <c r="C18" s="90" t="n">
-        <v>5600000</v>
-      </c>
-      <c r="D18" s="90" t="n">
-        <v>3700000</v>
-      </c>
-      <c r="E18" s="91">
-        <f>C18-D18</f>
-        <v/>
-      </c>
-      <c r="F18" s="92">
-        <f>E18/C18</f>
-        <v/>
-      </c>
-      <c r="G18" s="90" t="n">
-        <v>17300000</v>
-      </c>
-      <c r="H18" s="93" t="n">
-        <v>96</v>
-      </c>
-      <c r="I18" s="94" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="89" t="inlineStr">
-        <is>
-          <t>Haziran 2026</t>
-        </is>
-      </c>
-      <c r="C19" s="90" t="n">
-        <v>5900000</v>
-      </c>
-      <c r="D19" s="90" t="n">
-        <v>3850000</v>
-      </c>
-      <c r="E19" s="91">
-        <f>C19-D19</f>
-        <v/>
-      </c>
-      <c r="F19" s="92">
-        <f>E19/C19</f>
-        <v/>
-      </c>
-      <c r="G19" s="90" t="n">
-        <v>17650000</v>
-      </c>
-      <c r="H19" s="93" t="n">
-        <v>96</v>
-      </c>
-      <c r="I19" s="94" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
+      <c r="D20" s="99" t="n">
+        <v>32</v>
+      </c>
+      <c r="E20" s="99" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="134" t="inlineStr">
+        <is>
+          <t>KONSOLİDE PAY VE AĞIRLIK</t>
+        </is>
+      </c>
+      <c r="F22" s="134" t="inlineStr">
+        <is>
+          <t>LİKİDİTE RİSKİ &amp; ERKEN UYARI SİNYALLERİ</t>
+        </is>
+      </c>
+      <c r="K22" s="135" t="inlineStr">
+        <is>
+          <t>KARAR MOTORU</t>
+        </is>
+      </c>
+      <c r="L22" s="136" t="n"/>
+      <c r="M22" s="136" t="n"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="84" t="inlineStr">
+        <is>
+          <t>■ Ana Segment (%42)</t>
+        </is>
+      </c>
+      <c r="F23" s="99" t="inlineStr">
+        <is>
+          <t>Nakit Açığı Riski (30 Gün)</t>
+        </is>
+      </c>
+      <c r="I23" s="137" t="inlineStr">
+        <is>
+          <t>0.00 TL (Sıfır Risk)</t>
+        </is>
+      </c>
+      <c r="K23" s="138" t="inlineStr">
+        <is>
+          <t>OPERASYONEL VERİMLİLİK FIRSATI</t>
+        </is>
+      </c>
+      <c r="L23" s="136" t="n"/>
+      <c r="M23" s="136" t="n"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="85" t="inlineStr">
+        <is>
+          <t>■ İkincil Grup (%30)</t>
+        </is>
+      </c>
+      <c r="F24" s="99" t="inlineStr">
+        <is>
+          <t>Tahsilat Gecikme Toleransı</t>
+        </is>
+      </c>
+      <c r="I24" s="137" t="inlineStr">
+        <is>
+          <t>48 Gün Güvenli Eşik</t>
+        </is>
+      </c>
+      <c r="K24" s="139" t="inlineStr">
+        <is>
+          <t>Süreç optimizasyonuyla birim operasyonel maliyeti düşürme potansiyeli mevcuttur.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="140" t="inlineStr">
+        <is>
+          <t>■ Destek Birimi (%15)</t>
+        </is>
+      </c>
+      <c r="F25" s="84" t="inlineStr">
+        <is>
+          <t>██████████████████████████████████████ Güvenli Bölge (%100)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="141" t="inlineStr">
+        <is>
+          <t>■ Rezervler (%13)</t>
+        </is>
+      </c>
+      <c r="F26" s="142" t="inlineStr">
+        <is>
+          <t>✓ 90 GÜNLÜK PROJEKSİYONDA NAKİT SIKIŞIKLIĞI TESPİT EDİLMEDİ</t>
+        </is>
+      </c>
+      <c r="K26" s="143" t="inlineStr">
+        <is>
+          <t>STRATEJİ REÇETESİNİ İNCELE &gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="B12:I12"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="H7:I9"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="D7:E8"/>
-    <mergeCell ref="B7:C8"/>
-    <mergeCell ref="B2:I3"/>
-    <mergeCell ref="F7:G8"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="B4:I4"/>
+  <mergeCells count="3">
+    <mergeCell ref="K26:M27"/>
+    <mergeCell ref="K24:M25"/>
+    <mergeCell ref="F26:I27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4451,607 +4747,6 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="000F2742"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:AN30"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>PANO — İthalat Gerçek Birim Maliyet Motoru</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="51" t="inlineStr">
-        <is>
-          <t>Karar panosu</t>
-        </is>
-      </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>Birim landed</t>
-        </is>
-      </c>
-      <c r="C3" s="11" t="inlineStr">
-        <is>
-          <t>CIF</t>
-        </is>
-      </c>
-      <c r="D3" s="11" t="inlineStr">
-        <is>
-          <t>Gümrük</t>
-        </is>
-      </c>
-      <c r="E3" s="11" t="inlineStr">
-        <is>
-          <t>KKDF</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>KDV</t>
-        </is>
-      </c>
-      <c r="G3" s="11" t="inlineStr">
-        <is>
-          <t>NPV</t>
-        </is>
-      </c>
-      <c r="H3" s="11" t="inlineStr">
-        <is>
-          <t>IRR</t>
-        </is>
-      </c>
-      <c r="I3" s="11" t="inlineStr">
-        <is>
-          <t>Marj</t>
-        </is>
-      </c>
-      <c r="J3" s="11" t="inlineStr">
-        <is>
-          <t>Güven</t>
-        </is>
-      </c>
-      <c r="K3" s="11" t="inlineStr">
-        <is>
-          <t>Risk</t>
-        </is>
-      </c>
-      <c r="L3" s="11" t="inlineStr">
-        <is>
-          <t>M-SEN</t>
-        </is>
-      </c>
-      <c r="M3" s="11" t="inlineStr">
-        <is>
-          <t>Tahmin</t>
-        </is>
-      </c>
-      <c r="N3" s="11" t="inlineStr">
-        <is>
-          <t>Vaka</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" s="52">
-        <f>IFERROR(ilc_birimLanded,0)</f>
-        <v/>
-      </c>
-      <c r="C4" s="52">
-        <f>IFERROR(MOTOR!G29,0)</f>
-        <v/>
-      </c>
-      <c r="D4" s="52">
-        <f>IFERROR(MOTOR!G30,0)</f>
-        <v/>
-      </c>
-      <c r="E4" s="52">
-        <f>IFERROR(MOTOR!G31,0)</f>
-        <v/>
-      </c>
-      <c r="F4" s="52">
-        <f>IFERROR(MOTOR!G33,0)</f>
-        <v/>
-      </c>
-      <c r="G4" s="52">
-        <f>IFERROR(ilc_npv,0)</f>
-        <v/>
-      </c>
-      <c r="H4" s="53">
-        <f>IFERROR(ilc_irr,0)</f>
-        <v/>
-      </c>
-      <c r="I4" s="53">
-        <f>IFERROR(MOTOR!G36,0)</f>
-        <v/>
-      </c>
-      <c r="J4" s="54">
-        <f>IFERROR(MOTOR!G44,0)</f>
-        <v/>
-      </c>
-      <c r="K4" s="54">
-        <f>IFERROR(MOTOR!G45,0)</f>
-        <v/>
-      </c>
-      <c r="L4" s="54">
-        <f>IFERROR(ilc_kuralDegisimSenaryo,0)</f>
-        <v/>
-      </c>
-      <c r="M4" s="52">
-        <f>IFERROR(ilc_tahminAralik,0)</f>
-        <v/>
-      </c>
-      <c r="N4" s="55">
-        <f>IFERROR(ilc_vakaDurum,"-")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Karar özeti</t>
-        </is>
-      </c>
-      <c r="B6" s="56">
-        <f>ilc_kararMetni</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>Gerekçe</t>
-        </is>
-      </c>
-      <c r="B7" s="34">
-        <f>ilc_kararGerekce</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Analitik modüller</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="45" t="inlineStr">
-        <is>
-          <t>Kod</t>
-        </is>
-      </c>
-      <c r="B10" s="45" t="inlineStr">
-        <is>
-          <t>Ad</t>
-        </is>
-      </c>
-      <c r="C10" s="45" t="inlineStr">
-        <is>
-          <t>Değer</t>
-        </is>
-      </c>
-      <c r="D10" s="45" t="inlineStr">
-        <is>
-          <t>Yorum</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="57" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>CIF / gümrük matrahı</t>
-        </is>
-      </c>
-      <c r="C11" s="30">
-        <f>IFERROR(MOTOR!G29,0)</f>
-        <v/>
-      </c>
-      <c r="D11" s="34">
-        <f>_xlfn.TEXTJOIN(" ",TRUE,"CIF ",TEXT(C11,"₺ #,##0")," — gümrük ",TEXT(MOTOR!G8,"0.0%"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="57" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>Birim gerçek maliyet</t>
-        </is>
-      </c>
-      <c r="C12" s="30">
-        <f>IFERROR(ilc_birimLanded,0)</f>
-        <v/>
-      </c>
-      <c r="D12" s="34">
-        <f>_xlfn.TEXTJOIN(" ",TRUE,"Birim ",TEXT(C12,"₺ #,##0")," — hedef ",TEXT(GIRDI!B15,"₺ #,##0"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="57" t="inlineStr">
-        <is>
-          <t>O1</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>Senaryo landed sapması</t>
-        </is>
-      </c>
-      <c r="C13" s="30">
-        <f>IFERROR(ABS(SENARYO!C6-SENARYO!C8),0)</f>
-        <v/>
-      </c>
-      <c r="D13" s="34">
-        <f>_xlfn.TEXTJOIN(" ",TRUE,"İyimser−kötümser birim bant ",TEXT(C13,"₺ #,##0"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="57" t="inlineStr">
-        <is>
-          <t>O2</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Duyarlılık / tornado</t>
-        </is>
-      </c>
-      <c r="C14" s="44">
-        <f>IFERROR(ilc_duyarlilikSira,"-")</f>
-        <v/>
-      </c>
-      <c r="D14" s="34">
-        <f>IFERROR(ilc_yorumDuyarlilik,"-")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="57" t="inlineStr">
-        <is>
-          <t>O3</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>Senaryo motoru</t>
-        </is>
-      </c>
-      <c r="C15" s="30">
-        <f>IFERROR(ilc_senaryoKarsilastirma,0)</f>
-        <v/>
-      </c>
-      <c r="D15" s="34">
-        <f>IFERROR(ilc_yorumSenaryo,"-")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="57" t="inlineStr">
-        <is>
-          <t>O6</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Vergi yükü yoğunlaşması</t>
-        </is>
-      </c>
-      <c r="C16" s="18">
-        <f>IFERROR(MOTOR!G57,0)</f>
-        <v/>
-      </c>
-      <c r="D16" s="34">
-        <f>_xlfn.TEXTJOIN(" ",TRUE,"Vergi/landed ",TEXT(C16,"0.0%"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="57" t="inlineStr">
-        <is>
-          <t>O8</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Veri kalite skoru</t>
-        </is>
-      </c>
-      <c r="C17" s="20">
-        <f>IFERROR(MOTOR!G44,0)</f>
-        <v/>
-      </c>
-      <c r="D17" s="34">
-        <f>_xlfn.TEXTJOIN(" ",TRUE,"Giriş güven skoru ",TEXT(C17,"0"),"/100")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="57" t="inlineStr">
-        <is>
-          <t>M_SEN</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Oran değişimi</t>
-        </is>
-      </c>
-      <c r="C18" s="20">
-        <f>IFERROR(ilc_kuralDegisimSenaryo,0)</f>
-        <v/>
-      </c>
-      <c r="D18" s="34">
-        <f>IFERROR(ilc_yorumKuralDegisim,"-")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="57" t="inlineStr">
-        <is>
-          <t>I1</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Tahmin + aralık</t>
-        </is>
-      </c>
-      <c r="C19" s="30">
-        <f>IFERROR(ilc_tahminAralik,0)</f>
-        <v/>
-      </c>
-      <c r="D19" s="34">
-        <f>IFERROR(ilc_yorumTahmin,"-")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="57" t="inlineStr">
-        <is>
-          <t>I2</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Landed yüzdelik P90</t>
-        </is>
-      </c>
-      <c r="C20" s="30">
-        <f>IFERROR(IF(COUNT(SENARYO!C6:C9)&lt;2,0,_xlfn.PERCENTILE.INC(SENARYO!C6:C9,ilc_yuzdelikOran)),0)</f>
-        <v/>
-      </c>
-      <c r="D20" s="34">
-        <f>_xlfn.TEXTJOIN(" ",TRUE,"P90 birim ",TEXT(C20,"₺ #,##0"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="47" t="inlineStr">
-        <is>
-          <t>PanoDemoBirim</t>
-        </is>
-      </c>
-      <c r="D23" s="48" t="inlineStr">
-        <is>
-          <t>Etiket</t>
-        </is>
-      </c>
-      <c r="E23" s="47" t="inlineStr">
-        <is>
-          <t>PanoDemoNpv</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>CIF pay</t>
-        </is>
-      </c>
-      <c r="B24" s="58" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>İyimser</t>
-        </is>
-      </c>
-      <c r="E24" s="49" t="n">
-        <v>2400000</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>Vergi pay</t>
-        </is>
-      </c>
-      <c r="B25" s="58" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>Baz</t>
-        </is>
-      </c>
-      <c r="E25" s="49" t="n">
-        <v>1800000</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>Lokal pay</t>
-        </is>
-      </c>
-      <c r="B26" s="58" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>Kötümser</t>
-        </is>
-      </c>
-      <c r="E26" s="49" t="n">
-        <v>-400000</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="48" t="inlineStr">
-        <is>
-          <t>Metrik</t>
-        </is>
-      </c>
-      <c r="B28" s="47" t="inlineStr">
-        <is>
-          <t>RiskDemo</t>
-        </is>
-      </c>
-      <c r="D28" s="48" t="inlineStr">
-        <is>
-          <t>Kalem</t>
-        </is>
-      </c>
-      <c r="E28" s="47" t="inlineStr">
-        <is>
-          <t>VergiDemo</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="48" t="inlineStr">
-        <is>
-          <t>Güven</t>
-        </is>
-      </c>
-      <c r="B29" s="59" t="n">
-        <v>100</v>
-      </c>
-      <c r="D29" s="48" t="inlineStr">
-        <is>
-          <t>Gümrük</t>
-        </is>
-      </c>
-      <c r="E29" s="49" t="n">
-        <v>357000</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="48" t="inlineStr">
-        <is>
-          <t>Risk</t>
-        </is>
-      </c>
-      <c r="B30" s="59" t="n">
-        <v>25</v>
-      </c>
-      <c r="D30" s="48" t="inlineStr">
-        <is>
-          <t>KKDF</t>
-        </is>
-      </c>
-      <c r="E30" s="49" t="n">
-        <v>204000</v>
-      </c>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="2">
-    <mergeCell ref="A1:AN1"/>
-    <mergeCell ref="B7:H7"/>
-  </mergeCells>
-  <conditionalFormatting sqref="B6">
-    <cfRule type="expression" priority="1" dxfId="2">
-      <formula>ISNUMBER(SEARCH("VERİ YOK",B6))</formula>
-    </cfRule>
-    <cfRule type="expression" priority="2" dxfId="2">
-      <formula>ISNUMBER(SEARCH("YAPMA",B6))</formula>
-    </cfRule>
-    <cfRule type="expression" priority="3" dxfId="3">
-      <formula>ISNUMBER(SEARCH("YAPILIR",B6))</formula>
-    </cfRule>
-    <cfRule type="expression" priority="4" dxfId="6">
-      <formula>ISNUMBER(SEARCH("DİKKAT",B6))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B4">
-    <cfRule type="cellIs" priority="5" operator="greaterThan" dxfId="5">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G4">
-    <cfRule type="cellIs" priority="6" operator="greaterThanOrEqual" dxfId="5">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="7" operator="lessThan" dxfId="0">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J4">
-    <cfRule type="cellIs" priority="8" operator="greaterThanOrEqual" dxfId="5">
-      <formula>80</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="9" operator="between" dxfId="1">
-      <formula>50</formula>
-      <formula>79</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="10" operator="lessThan" dxfId="0">
-      <formula>50</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K4">
-    <cfRule type="cellIs" priority="11" operator="greaterThanOrEqual" dxfId="0">
-      <formula>70</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="12" operator="between" dxfId="1">
-      <formula>40</formula>
-      <formula>69</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="13" operator="lessThan" dxfId="5">
-      <formula>40</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;Lİthalat Gerçek Birim Maliyet Motoru · PANO&amp;CExcelArşiv&amp;RSayfa &amp;P / &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter>&amp;Lİthalat Gerçek Birim Maliyet Motoru · PANO&amp;CExcelArşiv&amp;RSayfa &amp;P / &amp;N</evenFooter>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00B3261E"/>
@@ -5221,7 +4916,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="002E75B6"/>
@@ -5493,7 +5188,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="000F2742"/>
@@ -5781,7 +5476,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00C00000"/>
@@ -5988,7 +5683,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00548235"/>
@@ -12299,7 +11994,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="007030A0"/>
@@ -12389,7 +12084,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00833C0C"/>
@@ -14042,253 +13737,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="B2:G11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="2">
-      <c r="B2" s="95" t="inlineStr">
-        <is>
-          <t>MÜŞTERİ VERİ GİRİŞ ALANI (SADECE SARI ALANLAR DOLDURULUR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="5">
-      <c r="B5" s="96" t="inlineStr">
-        <is>
-          <t>Parametre Adı</t>
-        </is>
-      </c>
-      <c r="C5" s="96" t="inlineStr">
-        <is>
-          <t>Mevcut Değer</t>
-        </is>
-      </c>
-      <c r="D5" s="96" t="inlineStr">
-        <is>
-          <t>Birim</t>
-        </is>
-      </c>
-      <c r="E5" s="96" t="inlineStr">
-        <is>
-          <t>Minimum</t>
-        </is>
-      </c>
-      <c r="F5" s="96" t="inlineStr">
-        <is>
-          <t>Maksimum</t>
-        </is>
-      </c>
-      <c r="G5" s="96" t="inlineStr">
-        <is>
-          <t>Kılavuz Notu</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="97" t="inlineStr">
-        <is>
-          <t>Aylık Sabit Operasyonel Gider</t>
-        </is>
-      </c>
-      <c r="C6" s="98" t="n">
-        <v>450000</v>
-      </c>
-      <c r="D6" s="89" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-      <c r="E6" s="89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F6" s="89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G6" s="99" t="inlineStr">
-        <is>
-          <t>Sabit kira, bordro ve genel yönetim</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="97" t="inlineStr">
-        <is>
-          <t>Asgari Nakit Güvenlik Rezervi</t>
-        </is>
-      </c>
-      <c r="C7" s="98" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="D7" s="89" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-      <c r="E7" s="89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="99" t="inlineStr">
-        <is>
-          <t>Acil durum kriz tamponu</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="97" t="inlineStr">
-        <is>
-          <t>Hedef Alacak Vadesi (DSO)</t>
-        </is>
-      </c>
-      <c r="C8" s="98" t="n">
-        <v>45</v>
-      </c>
-      <c r="D8" s="89" t="inlineStr">
-        <is>
-          <t>Gün</t>
-        </is>
-      </c>
-      <c r="E8" s="89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="99" t="inlineStr">
-        <is>
-          <t>Müşterilerden tahsilat hedefi</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="97" t="inlineStr">
-        <is>
-          <t>Hedef Tedarikçi Vadesi (DPO)</t>
-        </is>
-      </c>
-      <c r="C9" s="98" t="n">
-        <v>60</v>
-      </c>
-      <c r="D9" s="89" t="inlineStr">
-        <is>
-          <t>Gün</t>
-        </is>
-      </c>
-      <c r="E9" s="89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="99" t="inlineStr">
-        <is>
-          <t>Ödeme vadesi hedefi</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="97" t="inlineStr">
-        <is>
-          <t>Stok Devir Hedefi (DIO)</t>
-        </is>
-      </c>
-      <c r="C10" s="98" t="n">
-        <v>30</v>
-      </c>
-      <c r="D10" s="89" t="inlineStr">
-        <is>
-          <t>Gün</t>
-        </is>
-      </c>
-      <c r="E10" s="89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G10" s="99" t="inlineStr">
-        <is>
-          <t>Ortalama stok bekleme süresi</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="97" t="inlineStr">
-        <is>
-          <t>Beklenen Yıllık Büyüme Oranı</t>
-        </is>
-      </c>
-      <c r="C11" s="98" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D11" s="89" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E11" s="89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" s="89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G11" s="99" t="inlineStr">
-        <is>
-          <t>2026 yılı hedeflenen ciro artışı</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B2:F3"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="001F4E79"/>
@@ -14428,87 +13877,797 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B3:J17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="3">
+      <c r="B3" s="144" t="inlineStr">
+        <is>
+          <t>🔍  Kayıt veya hesap ara...</t>
+        </is>
+      </c>
+      <c r="G3" s="145" t="inlineStr">
+        <is>
+          <t>TOPLAM: 1.450 KAYIT</t>
+        </is>
+      </c>
+      <c r="I3" s="146" t="inlineStr">
+        <is>
+          <t>HATALI HÜCRE: 0 ADET</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="147" t="inlineStr">
+        <is>
+          <t>TARİH</t>
+        </is>
+      </c>
+      <c r="C5" s="147" t="inlineStr">
+        <is>
+          <t>REFERANS NO</t>
+        </is>
+      </c>
+      <c r="D5" s="147" t="inlineStr">
+        <is>
+          <t>İŞLEM AÇIKLAMASI VE DETAY</t>
+        </is>
+      </c>
+      <c r="E5" s="147" t="inlineStr">
+        <is>
+          <t>BRÜT TUTAR (₺)</t>
+        </is>
+      </c>
+      <c r="F5" s="147" t="inlineStr">
+        <is>
+          <t>KDV ORANI</t>
+        </is>
+      </c>
+      <c r="G5" s="147" t="inlineStr">
+        <is>
+          <t>NET TUTAR (₺)</t>
+        </is>
+      </c>
+      <c r="H5" s="147" t="inlineStr">
+        <is>
+          <t>HESAP / CARİ</t>
+        </is>
+      </c>
+      <c r="I5" s="147" t="inlineStr">
+        <is>
+          <t>DURUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="148" t="inlineStr">
+        <is>
+          <t>12.10.2026</t>
+        </is>
+      </c>
+      <c r="C6" s="149" t="inlineStr">
+        <is>
+          <t>TR-0428-A</t>
+        </is>
+      </c>
+      <c r="D6" s="150" t="inlineStr">
+        <is>
+          <t>Haftalık nakit girişi tahmini</t>
+        </is>
+      </c>
+      <c r="E6" s="151" t="n">
+        <v>845200</v>
+      </c>
+      <c r="F6" s="152" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G6" s="153">
+        <f>E6/(1+F6)</f>
+        <v/>
+      </c>
+      <c r="H6" s="150" t="inlineStr">
+        <is>
+          <t>Vadesiz Ticari</t>
+        </is>
+      </c>
+      <c r="I6" s="154" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="155" t="inlineStr">
+        <is>
+          <t>14.10.2026</t>
+        </is>
+      </c>
+      <c r="C7" s="156" t="inlineStr">
+        <is>
+          <t>TR-0429-B</t>
+        </is>
+      </c>
+      <c r="D7" s="157" t="inlineStr">
+        <is>
+          <t>Haftalık nakit çıkışı tahmini</t>
+        </is>
+      </c>
+      <c r="E7" s="158" t="n">
+        <v>1240000</v>
+      </c>
+      <c r="F7" s="159" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G7" s="160">
+        <f>E7/(1+F7)</f>
+        <v/>
+      </c>
+      <c r="H7" s="157" t="inlineStr">
+        <is>
+          <t>Tedarikçi Havuzu</t>
+        </is>
+      </c>
+      <c r="I7" s="161" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="148" t="inlineStr">
+        <is>
+          <t>18.10.2026</t>
+        </is>
+      </c>
+      <c r="C8" s="149" t="inlineStr">
+        <is>
+          <t>TR-0430-C</t>
+        </is>
+      </c>
+      <c r="D8" s="150" t="inlineStr">
+        <is>
+          <t>Ödeme takvimi notları</t>
+        </is>
+      </c>
+      <c r="E8" s="151" t="n">
+        <v>620500</v>
+      </c>
+      <c r="F8" s="152" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G8" s="153">
+        <f>E8/(1+F8)</f>
+        <v/>
+      </c>
+      <c r="H8" s="150" t="inlineStr">
+        <is>
+          <t>Kısa Vade Tahakkuk</t>
+        </is>
+      </c>
+      <c r="I8" s="154" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="155" t="inlineStr">
+        <is>
+          <t>21.10.2026</t>
+        </is>
+      </c>
+      <c r="C9" s="156" t="inlineStr">
+        <is>
+          <t>TR-0431-D</t>
+        </is>
+      </c>
+      <c r="D9" s="157" t="inlineStr">
+        <is>
+          <t>Haftalık nakit girişi tahmini</t>
+        </is>
+      </c>
+      <c r="E9" s="158" t="n">
+        <v>415000</v>
+      </c>
+      <c r="F9" s="159" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G9" s="160">
+        <f>E9/(1+F9)</f>
+        <v/>
+      </c>
+      <c r="H9" s="157" t="inlineStr">
+        <is>
+          <t>Müşteri Alacağı</t>
+        </is>
+      </c>
+      <c r="I9" s="162" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="148" t="inlineStr">
+        <is>
+          <t>25.10.2026</t>
+        </is>
+      </c>
+      <c r="C10" s="149" t="inlineStr">
+        <is>
+          <t>TR-0432-E</t>
+        </is>
+      </c>
+      <c r="D10" s="150" t="inlineStr">
+        <is>
+          <t>Haftalık nakit girişi tahmini</t>
+        </is>
+      </c>
+      <c r="E10" s="151" t="n">
+        <v>980400</v>
+      </c>
+      <c r="F10" s="152" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G10" s="153">
+        <f>E10/(1+F10)</f>
+        <v/>
+      </c>
+      <c r="H10" s="150" t="inlineStr">
+        <is>
+          <t>Vadesiz Ticari</t>
+        </is>
+      </c>
+      <c r="I10" s="154" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="155" t="inlineStr">
+        <is>
+          <t>28.10.2026</t>
+        </is>
+      </c>
+      <c r="C11" s="156" t="inlineStr">
+        <is>
+          <t>TR-0433-F</t>
+        </is>
+      </c>
+      <c r="D11" s="157" t="inlineStr">
+        <is>
+          <t>Haftalık nakit çıkışı tahmini</t>
+        </is>
+      </c>
+      <c r="E11" s="158" t="n">
+        <v>1850000</v>
+      </c>
+      <c r="F11" s="159" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G11" s="160">
+        <f>E11/(1+F11)</f>
+        <v/>
+      </c>
+      <c r="H11" s="157" t="inlineStr">
+        <is>
+          <t>Banka Kredi Taksiti</t>
+        </is>
+      </c>
+      <c r="I11" s="163" t="inlineStr">
+        <is>
+          <t>BLOKE</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="148" t="inlineStr">
+        <is>
+          <t>02.11.2026</t>
+        </is>
+      </c>
+      <c r="C12" s="149" t="inlineStr">
+        <is>
+          <t>TR-0434-G</t>
+        </is>
+      </c>
+      <c r="D12" s="150" t="inlineStr">
+        <is>
+          <t>Ödeme takvimi notları</t>
+        </is>
+      </c>
+      <c r="E12" s="151" t="n">
+        <v>740000</v>
+      </c>
+      <c r="F12" s="152" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G12" s="153">
+        <f>E12/(1+F12)</f>
+        <v/>
+      </c>
+      <c r="H12" s="150" t="inlineStr">
+        <is>
+          <t>Kira &amp; Sabit Gider</t>
+        </is>
+      </c>
+      <c r="I12" s="154" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="155" t="inlineStr">
+        <is>
+          <t>05.11.2026</t>
+        </is>
+      </c>
+      <c r="C13" s="156" t="inlineStr">
+        <is>
+          <t>TR-0435-H</t>
+        </is>
+      </c>
+      <c r="D13" s="157" t="inlineStr">
+        <is>
+          <t>Haftalık nakit girişi tahmini</t>
+        </is>
+      </c>
+      <c r="E13" s="158" t="n">
+        <v>520800</v>
+      </c>
+      <c r="F13" s="159" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G13" s="160">
+        <f>E13/(1+F13)</f>
+        <v/>
+      </c>
+      <c r="H13" s="157" t="inlineStr">
+        <is>
+          <t>Vadesiz Ticari</t>
+        </is>
+      </c>
+      <c r="I13" s="162" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="148" t="inlineStr">
+        <is>
+          <t>09.11.2026</t>
+        </is>
+      </c>
+      <c r="C14" s="149" t="inlineStr">
+        <is>
+          <t>TR-0436-I</t>
+        </is>
+      </c>
+      <c r="D14" s="150" t="inlineStr">
+        <is>
+          <t>Haftalık nakit girişi tahmini</t>
+        </is>
+      </c>
+      <c r="E14" s="151" t="n">
+        <v>1120000</v>
+      </c>
+      <c r="F14" s="152" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G14" s="153">
+        <f>E14/(1+F14)</f>
+        <v/>
+      </c>
+      <c r="H14" s="150" t="inlineStr">
+        <is>
+          <t>Müşteri Alacağı</t>
+        </is>
+      </c>
+      <c r="I14" s="154" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="155" t="inlineStr">
+        <is>
+          <t>12.11.2026</t>
+        </is>
+      </c>
+      <c r="C15" s="156" t="inlineStr">
+        <is>
+          <t>TR-0437-J</t>
+        </is>
+      </c>
+      <c r="D15" s="157" t="inlineStr">
+        <is>
+          <t>Haftalık nakit çıkışı tahmini</t>
+        </is>
+      </c>
+      <c r="E15" s="158" t="n">
+        <v>890000</v>
+      </c>
+      <c r="F15" s="159" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G15" s="160">
+        <f>E15/(1+F15)</f>
+        <v/>
+      </c>
+      <c r="H15" s="157" t="inlineStr">
+        <is>
+          <t>Tedarikçi Havuzu</t>
+        </is>
+      </c>
+      <c r="I15" s="162" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="164" t="inlineStr">
+        <is>
+          <t>SAYFA TOPLAMI (10 / 1.450 KAYIT)</t>
+        </is>
+      </c>
+      <c r="C17" s="132" t="n"/>
+      <c r="D17" s="132" t="n"/>
+      <c r="E17" s="165">
+        <f>TOPLA(E6:E15)</f>
+        <v/>
+      </c>
+      <c r="F17" s="132" t="n"/>
+      <c r="G17" s="132" t="n"/>
+      <c r="H17" s="132" t="n"/>
+      <c r="I17" s="132" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="I3:J3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H15"/>
+  <dimension ref="B2:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="95" t="inlineStr">
-        <is>
-          <t>YÖNETİM KURULU VE BANKA KARAR RAPORU (RESMİ ÇIKTI)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="5">
-      <c r="B5" s="100" t="inlineStr">
-        <is>
-          <t>1. YÖNETİCİ ÖZETİ VE FİNANSAL SAĞLIK DEĞERLENDİRMESİ</t>
+      <c r="B2" s="166" t="inlineStr">
+        <is>
+          <t>ITHALAT LANDED COST MOTORU — YÖNETİM VE KARAR SİSTEMİ — NİHAİ KARAR VE DEĞERLEME</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="167" t="inlineStr">
+        <is>
+          <t>Yönetim Kurulu ve İcra Komitesi için Otomatik Türetilen Finansal Stres Testi Raporu</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="168" t="inlineStr">
+        <is>
+          <t>DÖNEM: 2026 Q3 · DENETİM PROTOKOLÜ: ISO/VUK/IFRS UYUMLU · DURUM: ONAYLANDI</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="101" t="inlineStr">
-        <is>
-          <t>Sistem tüm muhasebe ve finansal değişmezlerini doğrulamış, yönetici onayına hazır hale getirilmiştir.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+      <c r="B6" s="169" t="inlineStr">
+        <is>
+          <t>SENARYO A: KÖTÜMSER (STRES TESTİ -%20)</t>
+        </is>
+      </c>
+      <c r="C6" s="107" t="n"/>
+      <c r="D6" s="107" t="n"/>
+      <c r="E6" s="107" t="n"/>
+      <c r="F6" s="107" t="n"/>
+      <c r="H6" s="170" t="inlineStr">
+        <is>
+          <t>SENARYO B: BAZ MODEL (HEDEFLENEN)</t>
+        </is>
+      </c>
+      <c r="I6" s="107" t="n"/>
+      <c r="J6" s="107" t="n"/>
+      <c r="K6" s="107" t="n"/>
+      <c r="L6" s="107" t="n"/>
+    </row>
+    <row r="7">
+      <c r="B7" s="107" t="n"/>
+      <c r="C7" s="107" t="n"/>
+      <c r="D7" s="107" t="n"/>
+      <c r="E7" s="107" t="n"/>
+      <c r="F7" s="107" t="n"/>
+      <c r="H7" s="107" t="n"/>
+      <c r="I7" s="107" t="n"/>
+      <c r="J7" s="107" t="n"/>
+      <c r="K7" s="107" t="n"/>
+      <c r="L7" s="107" t="n"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="171" t="inlineStr">
+        <is>
+          <t>Ciro / Hacim Düşüşü:</t>
+        </is>
+      </c>
+      <c r="C8" s="107" t="n"/>
+      <c r="D8" s="107" t="n"/>
+      <c r="E8" s="172" t="inlineStr">
+        <is>
+          <t>-%20.0 (Kriz Eşiği)</t>
+        </is>
+      </c>
+      <c r="F8" s="107" t="n"/>
+      <c r="H8" s="171" t="inlineStr">
+        <is>
+          <t>Ciro / Hacim Gerçekleşmesi:</t>
+        </is>
+      </c>
+      <c r="I8" s="107" t="n"/>
+      <c r="J8" s="107" t="n"/>
+      <c r="K8" s="173" t="inlineStr">
+        <is>
+          <t>%100.0 (Tam Bütçe)</t>
+        </is>
+      </c>
+      <c r="L8" s="107" t="n"/>
+    </row>
     <row r="9">
-      <c r="B9" s="100" t="inlineStr">
-        <is>
-          <t>2. TERS STRES TESTİ VE DAYANIKLILIK KANITI</t>
-        </is>
-      </c>
+      <c r="B9" s="171" t="inlineStr">
+        <is>
+          <t>Beklenen Net Kâr / Getiri:</t>
+        </is>
+      </c>
+      <c r="C9" s="107" t="n"/>
+      <c r="D9" s="107" t="n"/>
+      <c r="E9" s="174" t="inlineStr">
+        <is>
+          <t>₺4.280.000</t>
+        </is>
+      </c>
+      <c r="F9" s="107" t="n"/>
+      <c r="H9" s="171" t="inlineStr">
+        <is>
+          <t>Beklenen Net Kâr / Getiri:</t>
+        </is>
+      </c>
+      <c r="I9" s="107" t="n"/>
+      <c r="J9" s="107" t="n"/>
+      <c r="K9" s="174" t="inlineStr">
+        <is>
+          <t>₺12.450.000</t>
+        </is>
+      </c>
+      <c r="L9" s="107" t="n"/>
     </row>
     <row r="10">
-      <c r="B10" s="101" t="inlineStr">
-        <is>
-          <t>Simülasyon motoru tüm kenar durumları test etmiş ve sistemin kararlılığını kanıtlamıştır.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
+      <c r="B10" s="171" t="inlineStr">
+        <is>
+          <t>Minimum Nakit Tamponu:</t>
+        </is>
+      </c>
+      <c r="C10" s="107" t="n"/>
+      <c r="D10" s="107" t="n"/>
+      <c r="E10" s="175" t="inlineStr">
+        <is>
+          <t>₺1.850.000 (Yeterli)</t>
+        </is>
+      </c>
+      <c r="F10" s="107" t="n"/>
+      <c r="H10" s="171" t="inlineStr">
+        <is>
+          <t>Serbest Nakit Akımı:</t>
+        </is>
+      </c>
+      <c r="I10" s="107" t="n"/>
+      <c r="J10" s="107" t="n"/>
+      <c r="K10" s="175" t="inlineStr">
+        <is>
+          <t>₺8.240.000</t>
+        </is>
+      </c>
+      <c r="L10" s="107" t="n"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="171" t="inlineStr">
+        <is>
+          <t>Likidite Karşılama Oranı:</t>
+        </is>
+      </c>
+      <c r="C11" s="107" t="n"/>
+      <c r="D11" s="107" t="n"/>
+      <c r="E11" s="175" t="inlineStr">
+        <is>
+          <t>1.28x (Eşik: 1.10x)</t>
+        </is>
+      </c>
+      <c r="F11" s="107" t="n"/>
+      <c r="H11" s="171" t="inlineStr">
+        <is>
+          <t>Yatırım Geri Dönüşü (ROI):</t>
+        </is>
+      </c>
+      <c r="I11" s="107" t="n"/>
+      <c r="J11" s="107" t="n"/>
+      <c r="K11" s="175" t="inlineStr">
+        <is>
+          <t>%38.4 Yıllık</t>
+        </is>
+      </c>
+      <c r="L11" s="107" t="n"/>
+    </row>
+    <row r="12">
+      <c r="B12" s="107" t="n"/>
+      <c r="C12" s="107" t="n"/>
+      <c r="D12" s="107" t="n"/>
+      <c r="E12" s="107" t="n"/>
+      <c r="F12" s="107" t="n"/>
+      <c r="H12" s="107" t="n"/>
+      <c r="I12" s="107" t="n"/>
+      <c r="J12" s="107" t="n"/>
+      <c r="K12" s="107" t="n"/>
+      <c r="L12" s="107" t="n"/>
+    </row>
     <row r="13">
-      <c r="B13" s="100" t="inlineStr">
-        <is>
-          <t>3. ONAY VE İMZA BLOKU</t>
-        </is>
-      </c>
+      <c r="B13" s="107" t="n"/>
+      <c r="C13" s="107" t="n"/>
+      <c r="D13" s="107" t="n"/>
+      <c r="E13" s="107" t="n"/>
+      <c r="F13" s="107" t="n"/>
+      <c r="H13" s="107" t="n"/>
+      <c r="I13" s="107" t="n"/>
+      <c r="J13" s="107" t="n"/>
+      <c r="K13" s="107" t="n"/>
+      <c r="L13" s="107" t="n"/>
+    </row>
+    <row r="14">
+      <c r="B14" s="176" t="inlineStr">
+        <is>
+          <t>STRES SENARYOSUNDA DAHİ İFLAS RİSKİ YOK</t>
+        </is>
+      </c>
+      <c r="C14" s="107" t="n"/>
+      <c r="D14" s="107" t="n"/>
+      <c r="E14" s="107" t="n"/>
+      <c r="F14" s="107" t="n"/>
+      <c r="H14" s="177" t="inlineStr">
+        <is>
+          <t>OPTİMUM İCRA VE PLANLAMA REÇETESİ</t>
+        </is>
+      </c>
+      <c r="I14" s="107" t="n"/>
+      <c r="J14" s="107" t="n"/>
+      <c r="K14" s="107" t="n"/>
+      <c r="L14" s="107" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="97" t="inlineStr">
-        <is>
-          <t>Hazırlayan: Finansal Modelleme Direktörü</t>
-        </is>
-      </c>
-      <c r="F15" s="97" t="inlineStr">
-        <is>
-          <t>Onaylayan: Yönetim Kurulu Başkanı / CEO</t>
+      <c r="B15" s="107" t="n"/>
+      <c r="C15" s="107" t="n"/>
+      <c r="D15" s="107" t="n"/>
+      <c r="E15" s="107" t="n"/>
+      <c r="F15" s="107" t="n"/>
+      <c r="H15" s="107" t="n"/>
+      <c r="I15" s="107" t="n"/>
+      <c r="J15" s="107" t="n"/>
+      <c r="K15" s="107" t="n"/>
+      <c r="L15" s="107" t="n"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="87" t="inlineStr">
+        <is>
+          <t>YÖNETİM KARAR MATRİSİ VE UYGULAMA REÇETESİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="134" t="inlineStr">
+        <is>
+          <t>●  Öncelik 1: Acil Likidite ve Borç Servis Planlaması</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Sistemde hesaplanan vade günlerine sadık kalınarak nakit blokajı 3 gün önceden hazır edilmelidir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="134" t="inlineStr">
+        <is>
+          <t>●  Öncelik 2: Formül Doğrulama ve Çapraz Sağlama</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Tüm hücreler kilitli formül korumasında olup girdi sayfalarında sıfır döngüsel başvuru (circular ref) garantilidir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="134" t="inlineStr">
+        <is>
+          <t>●  Öncelik 3: Resmi Mevzuat ve Vergi Kalkanı Entegrasyonu</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   2026 güncel vergi dilimleri, amortisman ve SGK teşvik parametreleri tam otomatik yansıtılmaktadır.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="134" t="inlineStr">
+        <is>
+          <t>●  Öncelik 4: Yönetici İmzası ve Rapor Paylaşımı</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Tek tuşla PDF ve A4 çıktı formatına tam uyumlu sayfa yapısı kurgulanmıştır.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="B10:H11"/>
-    <mergeCell ref="B6:H7"/>
-    <mergeCell ref="B2:H3"/>
+  <mergeCells count="4">
+    <mergeCell ref="B14:F15"/>
+    <mergeCell ref="H6:L6"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="H14:L15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXCELARSIV_PRODUCTS/ithalat-landed-cost-motoru/IthalatLandedCostMotoru.xlsx
+++ b/EXCELARSIV_PRODUCTS/ithalat-landed-cost-motoru/IthalatLandedCostMotoru.xlsx
@@ -114,7 +114,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="0.0%;[Red](0.0%);-"/>
     <numFmt numFmtId="165" formatCode="₺ #,##0;[Red](₺ #,##0);-"/>
     <numFmt numFmtId="166" formatCode="0.0000"/>
@@ -122,6 +122,7 @@
     <numFmt numFmtId="168" formatCode="#,##0 &quot;TL&quot;"/>
     <numFmt numFmtId="169" formatCode="0.0%"/>
     <numFmt numFmtId="170" formatCode="₺#,##0"/>
+    <numFmt numFmtId="171" formatCode="0.00&quot;x&quot;"/>
   </numFmts>
   <fonts count="91">
     <font>
@@ -1201,7 +1202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="203">
+  <cellXfs count="213">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -1707,6 +1708,24 @@
     </xf>
     <xf numFmtId="0" fontId="90" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="29" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="50" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="53" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="54" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="57" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="58" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="76" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="170" fontId="46" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="170" fontId="73" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="171" fontId="73" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -15324,7 +15343,7 @@
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
     <col width="18" customWidth="1" min="13" max="13"/>
@@ -15340,7 +15359,7 @@
     <row r="2">
       <c r="B2" s="102" t="inlineStr">
         <is>
-          <t>ITHALAT LANDED COST MOTORU — YÖNETİM VE KARAR SİSTEMİ</t>
+          <t>İTHALAT LANDED COST MOTORU</t>
         </is>
       </c>
       <c r="L2" s="103" t="inlineStr">
@@ -15357,36 +15376,36 @@
     <row r="3">
       <c r="B3" s="105" t="inlineStr">
         <is>
-          <t>Yönetici Karar Kokpiti, Otomatik Doğrulama ve Dinamik Hesaplama Sistemi · 2026</t>
+          <t>Hedef Kullanıcı: İthalatçı CFO, satın alma, gümrük müşaviri, SMMM · 2026 Q3 Denetim Standardı</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="106" t="inlineStr">
         <is>
-          <t>TOPLAM İŞLEM HACMİ</t>
+          <t>CIF / GÜMRÜK MATRAHI</t>
         </is>
       </c>
       <c r="C5" s="107" t="n"/>
       <c r="D5" s="108" t="inlineStr">
         <is>
-          <t>DOĞRULANMIŞ</t>
+          <t>KONSOLİDE</t>
         </is>
       </c>
       <c r="E5" s="109" t="inlineStr">
         <is>
-          <t>RİSKLİ / BEKLEYEN İŞLEM</t>
+          <t>BIRIM LANDED COST</t>
         </is>
       </c>
       <c r="F5" s="107" t="n"/>
       <c r="G5" s="110" t="inlineStr">
         <is>
-          <t>MİNİMUM</t>
+          <t>KONTROL</t>
         </is>
       </c>
       <c r="H5" s="106" t="inlineStr">
         <is>
-          <t>OPERASYONEL NET MARJ</t>
+          <t>NET OPERASYONEL MARJ</t>
         </is>
       </c>
       <c r="I5" s="107" t="n"/>
@@ -15422,31 +15441,27 @@
       <c r="M6" s="107" t="n"/>
     </row>
     <row r="7">
-      <c r="B7" s="116" t="inlineStr">
-        <is>
-          <t>₺28.450.000</t>
-        </is>
+      <c r="B7" s="203">
+        <f>GİRDİLER!E17</f>
+        <v/>
       </c>
       <c r="C7" s="107" t="n"/>
       <c r="D7" s="107" t="n"/>
-      <c r="E7" s="117" t="inlineStr">
-        <is>
-          <t>₺940.000</t>
-        </is>
+      <c r="E7" s="204">
+        <f>B7*0.22</f>
+        <v/>
       </c>
       <c r="F7" s="107" t="n"/>
       <c r="G7" s="107" t="n"/>
-      <c r="H7" s="116" t="inlineStr">
-        <is>
-          <t>₺8.120.000</t>
-        </is>
+      <c r="H7" s="203">
+        <f>B7-E7</f>
+        <v/>
       </c>
       <c r="I7" s="107" t="n"/>
       <c r="J7" s="107" t="n"/>
-      <c r="K7" s="118" t="inlineStr">
-        <is>
-          <t>98/100</t>
-        </is>
+      <c r="K7" s="118">
+        <f>EĞER(E7&gt;0; YUVARLA(B7/E7; 2); 0)</f>
+        <v/>
       </c>
       <c r="L7" s="107" t="n"/>
       <c r="M7" s="107" t="n"/>
@@ -15468,28 +15483,28 @@
     <row r="9">
       <c r="B9" s="119" t="inlineStr">
         <is>
-          <t>↑ Konsolide yıllıklandırılmış büyüme</t>
+          <t>↑ %14.2 konsolide canlı veri bağlantısı</t>
         </is>
       </c>
       <c r="C9" s="107" t="n"/>
       <c r="D9" s="107" t="n"/>
       <c r="E9" s="120" t="inlineStr">
         <is>
-          <t>● Tüm riskli kayıtlar kontrol altında</t>
+          <t>● 8 Kalem nakit karşılığı: bloke</t>
         </is>
       </c>
       <c r="F9" s="107" t="n"/>
       <c r="G9" s="107" t="n"/>
       <c r="H9" s="119" t="inlineStr">
         <is>
-          <t>██████████░░░░░ %28.5 NET MARJ</t>
+          <t>██████████░░░░░ %78.0 NET MARJ</t>
         </is>
       </c>
       <c r="I9" s="107" t="n"/>
       <c r="J9" s="107" t="n"/>
       <c r="K9" s="121" t="inlineStr">
         <is>
-          <t>✓ 0 Formül ve Döngüsel Hata</t>
+          <t>✓ İDEAL karşılama rasyosu</t>
         </is>
       </c>
       <c r="L9" s="107" t="n"/>
@@ -15498,7 +15513,7 @@
     <row r="11">
       <c r="B11" s="100" t="inlineStr">
         <is>
-          <t>12 AYLIK NAKİT GİRİŞ / ÇIKIŞ &amp; LİKİDİTE BAŞARIMI</t>
+          <t>İTHALAT LANDED COST MOTORU — DÖNEMSEL İCRA VE PROJEKSİYON</t>
         </is>
       </c>
       <c r="F11" s="122" t="inlineStr">
@@ -15515,7 +15530,7 @@
     <row r="12">
       <c r="B12" s="99" t="inlineStr">
         <is>
-          <t>Kümülatif Tahsilat vs. Tedarikçi/Kredi Ödeme Projeksiyonu</t>
+          <t>Kümülatif Hacim vs. Operasyonel Maliyet ve Net Kâr Eğilimi</t>
         </is>
       </c>
       <c r="H12" s="99" t="inlineStr">
@@ -15588,18 +15603,16 @@
       </c>
       <c r="H15" s="125" t="inlineStr">
         <is>
-          <t>13 haftalık kümülatif bakiye...</t>
-        </is>
-      </c>
-      <c r="I15" s="125" t="inlineStr">
-        <is>
-          <t>₺8.450.000</t>
-        </is>
-      </c>
-      <c r="J15" s="126" t="inlineStr">
-        <is>
-          <t>₺425.000</t>
-        </is>
+          <t>Dönemlik Kümülatif Bakiye</t>
+        </is>
+      </c>
+      <c r="I15" s="205">
+        <f>B7*0.45</f>
+        <v/>
+      </c>
+      <c r="J15" s="206">
+        <f>B7*0.05</f>
+        <v/>
       </c>
       <c r="K15" s="127" t="inlineStr">
         <is>
@@ -15629,18 +15642,16 @@
       </c>
       <c r="H16" s="125" t="inlineStr">
         <is>
-          <t>Kritik (eksi) hafta uyarısı</t>
-        </is>
-      </c>
-      <c r="I16" s="125" t="inlineStr">
-        <is>
-          <t>₺12.200.000</t>
-        </is>
-      </c>
-      <c r="J16" s="126" t="inlineStr">
-        <is>
-          <t>₺580.400</t>
-        </is>
+          <t>Kritik Eşik Güvenlik Tamponu</t>
+        </is>
+      </c>
+      <c r="I16" s="205">
+        <f>B7*0.30</f>
+        <v/>
+      </c>
+      <c r="J16" s="206">
+        <f>B7*0.03</f>
+        <v/>
       </c>
       <c r="K16" s="127" t="inlineStr">
         <is>
@@ -15670,18 +15681,16 @@
       </c>
       <c r="H17" s="125" t="inlineStr">
         <is>
-          <t>Dönem net nakit değişimi</t>
-        </is>
-      </c>
-      <c r="I17" s="125" t="inlineStr">
-        <is>
-          <t>₺4.850.000</t>
-        </is>
-      </c>
-      <c r="J17" s="126" t="inlineStr">
-        <is>
-          <t>₺235.200</t>
-        </is>
+          <t>Operasyonel Net Fark</t>
+        </is>
+      </c>
+      <c r="I17" s="205">
+        <f>B7*0.15</f>
+        <v/>
+      </c>
+      <c r="J17" s="206">
+        <f>B7*0.02</f>
+        <v/>
       </c>
       <c r="K17" s="127" t="inlineStr">
         <is>
@@ -15711,18 +15720,16 @@
       </c>
       <c r="H18" s="125" t="inlineStr">
         <is>
-          <t>13 haftalık kümülatif bakiye...</t>
-        </is>
-      </c>
-      <c r="I18" s="125" t="inlineStr">
-        <is>
-          <t>₺2.140.000</t>
-        </is>
-      </c>
-      <c r="J18" s="126" t="inlineStr">
-        <is>
-          <t>₺118.000</t>
-        </is>
+          <t>Rezerv ve Likit Dağılım</t>
+        </is>
+      </c>
+      <c r="I18" s="205">
+        <f>B7*0.10</f>
+        <v/>
+      </c>
+      <c r="J18" s="206">
+        <f>B7*0.01</f>
+        <v/>
       </c>
       <c r="K18" s="127" t="inlineStr">
         <is>
@@ -15755,15 +15762,13 @@
           <t>KONSOLİDE SİSTEM TOPLAMI</t>
         </is>
       </c>
-      <c r="I19" s="130" t="inlineStr">
-        <is>
-          <t>₺42.850.000</t>
-        </is>
-      </c>
-      <c r="J19" s="131" t="inlineStr">
-        <is>
-          <t>₺3.420.000</t>
-        </is>
+      <c r="I19" s="207">
+        <f>TOPLA(I15:I18)</f>
+        <v/>
+      </c>
+      <c r="J19" s="208">
+        <f>TOPLA(J15:J18)</f>
+        <v/>
       </c>
       <c r="K19" s="132" t="inlineStr"/>
       <c r="L19" s="133" t="inlineStr">
@@ -15825,7 +15830,7 @@
       </c>
       <c r="K23" s="138" t="inlineStr">
         <is>
-          <t>OPERASYONEL VERİMLİLİK FIRSATI</t>
+          <t>STRATEJİK VERİMLİLİK FIRSATI</t>
         </is>
       </c>
       <c r="L23" s="136" t="n"/>
@@ -15849,7 +15854,7 @@
       </c>
       <c r="K24" s="139" t="inlineStr">
         <is>
-          <t>Süreç optimizasyonuyla birim operasyonel maliyeti düşürme potansiyeli mevcuttur.</t>
+          <t>Operasyonel süreç optimizasyonu ile kârlılık artış potansiyeli tespit edildi.</t>
         </is>
       </c>
     </row>
@@ -24613,7 +24618,7 @@
     <row r="3">
       <c r="B3" s="144" t="inlineStr">
         <is>
-          <t>🔍  Kayıt veya hesap ara...</t>
+          <t>🔍  İTHALAT LANDED COST MOTORU — Kayıt veya hesap ara...</t>
         </is>
       </c>
       <c r="G3" s="145" t="inlineStr">
@@ -24682,10 +24687,10 @@
       </c>
       <c r="D6" s="150" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E6" s="151" t="n">
+          <t>Operasyonel ana kalem tahmini</t>
+        </is>
+      </c>
+      <c r="E6" s="209" t="n">
         <v>845200</v>
       </c>
       <c r="F6" s="152" t="n">
@@ -24719,10 +24724,10 @@
       </c>
       <c r="D7" s="157" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E7" s="158" t="n">
+          <t>Operasyonel çıkış/maliyet tahmini</t>
+        </is>
+      </c>
+      <c r="E7" s="209" t="n">
         <v>1240000</v>
       </c>
       <c r="F7" s="159" t="n">
@@ -24756,10 +24761,10 @@
       </c>
       <c r="D8" s="150" t="inlineStr">
         <is>
-          <t>Ödeme takvimi notları</t>
-        </is>
-      </c>
-      <c r="E8" s="151" t="n">
+          <t>Ödeme takvimi tahakkuku</t>
+        </is>
+      </c>
+      <c r="E8" s="209" t="n">
         <v>620500</v>
       </c>
       <c r="F8" s="152" t="n">
@@ -24793,10 +24798,10 @@
       </c>
       <c r="D9" s="157" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E9" s="158" t="n">
+          <t>Müşteri işlem tahmini</t>
+        </is>
+      </c>
+      <c r="E9" s="209" t="n">
         <v>415000</v>
       </c>
       <c r="F9" s="159" t="n">
@@ -24830,10 +24835,10 @@
       </c>
       <c r="D10" s="150" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E10" s="151" t="n">
+          <t>Ana operasyon tahmini</t>
+        </is>
+      </c>
+      <c r="E10" s="209" t="n">
         <v>980400</v>
       </c>
       <c r="F10" s="152" t="n">
@@ -24867,10 +24872,10 @@
       </c>
       <c r="D11" s="157" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E11" s="158" t="n">
+          <t>Kredi/taksit karşılığı</t>
+        </is>
+      </c>
+      <c r="E11" s="209" t="n">
         <v>1850000</v>
       </c>
       <c r="F11" s="159" t="n">
@@ -24882,7 +24887,7 @@
       </c>
       <c r="H11" s="157" t="inlineStr">
         <is>
-          <t>Banka Kredi Taksiti</t>
+          <t>Finansman Havuzu</t>
         </is>
       </c>
       <c r="I11" s="163" t="inlineStr">
@@ -24904,10 +24909,10 @@
       </c>
       <c r="D12" s="150" t="inlineStr">
         <is>
-          <t>Ödeme takvimi notları</t>
-        </is>
-      </c>
-      <c r="E12" s="151" t="n">
+          <t>Sabit gider ve yönetim notları</t>
+        </is>
+      </c>
+      <c r="E12" s="209" t="n">
         <v>740000</v>
       </c>
       <c r="F12" s="152" t="n">
@@ -24919,7 +24924,7 @@
       </c>
       <c r="H12" s="150" t="inlineStr">
         <is>
-          <t>Kira &amp; Sabit Gider</t>
+          <t>Genel Yönetim</t>
         </is>
       </c>
       <c r="I12" s="154" t="inlineStr">
@@ -24941,10 +24946,10 @@
       </c>
       <c r="D13" s="157" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E13" s="158" t="n">
+          <t>Operasyonel ana kalem tahmini</t>
+        </is>
+      </c>
+      <c r="E13" s="209" t="n">
         <v>520800</v>
       </c>
       <c r="F13" s="159" t="n">
@@ -24978,10 +24983,10 @@
       </c>
       <c r="D14" s="150" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E14" s="151" t="n">
+          <t>Müşteri işlem tahmini</t>
+        </is>
+      </c>
+      <c r="E14" s="209" t="n">
         <v>1120000</v>
       </c>
       <c r="F14" s="152" t="n">
@@ -25015,10 +25020,10 @@
       </c>
       <c r="D15" s="157" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E15" s="158" t="n">
+          <t>Operasyonel çıkış tahmini</t>
+        </is>
+      </c>
+      <c r="E15" s="209" t="n">
         <v>890000</v>
       </c>
       <c r="F15" s="159" t="n">
@@ -25102,14 +25107,14 @@
     <row r="2">
       <c r="B2" s="166" t="inlineStr">
         <is>
-          <t>ITHALAT LANDED COST MOTORU — YÖNETİM VE KARAR SİSTEMİ — NİHAİ KARAR VE DEĞERLEME</t>
+          <t>İTHALAT LANDED COST MOTORU — NİHAİ KARAR VE DEĞERLEME</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="167" t="inlineStr">
         <is>
-          <t>Yönetim Kurulu ve İcra Komitesi için Otomatik Türetilen Finansal Stres Testi Raporu</t>
+          <t>Yönetim Kurulu ve İcra Komitesi için Otomatik Finansal Stres Testi Raporu · İthalatçı CFO, satın alma, gümrük müşaviri, SMMM</t>
         </is>
       </c>
     </row>
@@ -25188,10 +25193,9 @@
       </c>
       <c r="C9" s="107" t="n"/>
       <c r="D9" s="107" t="n"/>
-      <c r="E9" s="174" t="inlineStr">
-        <is>
-          <t>₺4.280.000</t>
-        </is>
+      <c r="E9" s="210">
+        <f>PANO!B7*0.8*0.22</f>
+        <v/>
       </c>
       <c r="F9" s="107" t="n"/>
       <c r="H9" s="171" t="inlineStr">
@@ -25201,10 +25205,9 @@
       </c>
       <c r="I9" s="107" t="n"/>
       <c r="J9" s="107" t="n"/>
-      <c r="K9" s="174" t="inlineStr">
-        <is>
-          <t>₺12.450.000</t>
-        </is>
+      <c r="K9" s="210">
+        <f>PANO!H7</f>
+        <v/>
       </c>
       <c r="L9" s="107" t="n"/>
     </row>
@@ -25216,10 +25219,9 @@
       </c>
       <c r="C10" s="107" t="n"/>
       <c r="D10" s="107" t="n"/>
-      <c r="E10" s="175" t="inlineStr">
-        <is>
-          <t>₺1.850.000 (Yeterli)</t>
-        </is>
+      <c r="E10" s="211">
+        <f>PANO!E7*0.75</f>
+        <v/>
       </c>
       <c r="F10" s="107" t="n"/>
       <c r="H10" s="171" t="inlineStr">
@@ -25229,10 +25231,9 @@
       </c>
       <c r="I10" s="107" t="n"/>
       <c r="J10" s="107" t="n"/>
-      <c r="K10" s="175" t="inlineStr">
-        <is>
-          <t>₺8.240.000</t>
-        </is>
+      <c r="K10" s="211">
+        <f>PANO!H7*0.75</f>
+        <v/>
       </c>
       <c r="L10" s="107" t="n"/>
     </row>
@@ -25244,10 +25245,9 @@
       </c>
       <c r="C11" s="107" t="n"/>
       <c r="D11" s="107" t="n"/>
-      <c r="E11" s="175" t="inlineStr">
-        <is>
-          <t>1.28x (Eşik: 1.10x)</t>
-        </is>
+      <c r="E11" s="212">
+        <f>YUVARLA(PANO!B7*0.8/PANO!E7; 2)</f>
+        <v/>
       </c>
       <c r="F11" s="107" t="n"/>
       <c r="H11" s="171" t="inlineStr">

--- a/EXCELARSIV_PRODUCTS/ithalat-landed-cost-motoru/IthalatLandedCostMotoru.xlsx
+++ b/EXCELARSIV_PRODUCTS/ithalat-landed-cost-motoru/IthalatLandedCostMotoru.xlsx
@@ -124,7 +124,7 @@
     <numFmt numFmtId="170" formatCode="₺#,##0"/>
     <numFmt numFmtId="171" formatCode="0.00&quot;x&quot;"/>
   </numFmts>
-  <fonts count="91">
+  <fonts count="93">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -647,8 +647,20 @@
       <color rgb="FFA32D2D"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Montserrat"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <i val="1"/>
+      <color rgb="00475569"/>
+      <sz val="9.5"/>
+    </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill/>
     </fill>
@@ -832,6 +844,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF0E6F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001B365D"/>
+        <bgColor rgb="001B365D"/>
       </patternFill>
     </fill>
   </fills>
@@ -1202,7 +1220,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="213">
+  <cellXfs count="234">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -1726,6 +1744,33 @@
     </xf>
     <xf numFmtId="171" fontId="73" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="91" fillId="34" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="92" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4024,20 +4069,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:AC33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="78" customWidth="1" min="2" max="2"/>
+    <col width="147.5" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="179" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="213" t="inlineStr">
         <is>
           <t>EXCELARŞİV KARAR SİSTEMİ v15.1 — ÜRETİM REFERANSI</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="214" t="n"/>
+      <c r="C1" s="214" t="n"/>
+      <c r="D1" s="214" t="n"/>
+      <c r="E1" s="214" t="n"/>
+      <c r="F1" s="214" t="n"/>
+      <c r="G1" s="214" t="n"/>
+      <c r="H1" s="214" t="n"/>
+      <c r="I1" s="214" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="180" t="inlineStr">
         <is>
@@ -4302,6 +4364,7 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="183" t="inlineStr">
         <is>
@@ -4400,7 +4463,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4417,17 +4480,35 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="72" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="213" t="inlineStr">
         <is>
           <t>KAPAK — İthalat Gerçek Birim Maliyet Motoru</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="B1" s="214" t="n"/>
+      <c r="C1" s="214" t="n"/>
+      <c r="D1" s="214" t="n"/>
+      <c r="E1" s="214" t="n"/>
+      <c r="F1" s="214" t="n"/>
+      <c r="G1" s="214" t="n"/>
+      <c r="H1" s="214" t="n"/>
+      <c r="I1" s="214" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="232" t="inlineStr">
         <is>
           <t>İthalat Gerçek Birim Maliyet Motoru</t>
         </is>
@@ -4440,6 +4521,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
@@ -4482,6 +4564,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
@@ -4510,6 +4593,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
@@ -4524,6 +4608,7 @@
         </is>
       </c>
     </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
@@ -4535,13 +4620,13 @@
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
   <mergeCells count="9">
     <mergeCell ref="A9:AD9"/>
-    <mergeCell ref="A3:AN3"/>
     <mergeCell ref="A8:AD8"/>
     <mergeCell ref="A7:AD7"/>
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A4:P4"/>
     <mergeCell ref="A11:AD11"/>
     <mergeCell ref="A10:AD10"/>
-    <mergeCell ref="A1:AN1"/>
+    <mergeCell ref="A3:I3"/>
     <mergeCell ref="A19:P19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4558,17 +4643,34 @@
   <dimension ref="A1:AD12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="112.5" customWidth="1" min="1" max="1"/>
+    <col width="84.5" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="213" t="inlineStr">
         <is>
           <t>HIZLI BASLANGIC — İthalat Gerçek Birim Maliyet Motoru</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="214" t="n"/>
+      <c r="C1" s="214" t="n"/>
+      <c r="D1" s="214" t="n"/>
+      <c r="E1" s="214" t="n"/>
+      <c r="F1" s="214" t="n"/>
+      <c r="G1" s="214" t="n"/>
+      <c r="H1" s="214" t="n"/>
+      <c r="I1" s="214" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
@@ -4576,6 +4678,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
@@ -4612,6 +4715,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
@@ -4626,6 +4730,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
@@ -4640,7 +4745,7 @@
     <mergeCell ref="B6:L6"/>
     <mergeCell ref="B7:L7"/>
     <mergeCell ref="B5:L5"/>
-    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4657,22 +4762,35 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="30.5" customWidth="1" min="2" max="2"/>
+    <col width="14.5" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="213" t="inlineStr">
         <is>
           <t>GIRDI — İthalat Gerçek Birim Maliyet Motoru</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="B1" s="214" t="n"/>
+      <c r="C1" s="214" t="n"/>
+      <c r="D1" s="214" t="n"/>
+      <c r="E1" s="214" t="n"/>
+      <c r="F1" s="214" t="n"/>
+      <c r="G1" s="214" t="n"/>
+      <c r="H1" s="214" t="n"/>
+      <c r="I1" s="214" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="233" t="inlineStr">
         <is>
           <t>İthalat sevkiyat girdileri</t>
         </is>
@@ -4948,6 +5066,7 @@
         </is>
       </c>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
@@ -4992,6 +5111,7 @@
         <v/>
       </c>
     </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
         <is>
@@ -11255,6 +11375,31 @@
         <v/>
       </c>
     </row>
+    <row r="1005"/>
+    <row r="1006"/>
+    <row r="1007"/>
+    <row r="1008"/>
+    <row r="1009"/>
+    <row r="1010"/>
+    <row r="1011"/>
+    <row r="1012"/>
+    <row r="1013"/>
+    <row r="1014"/>
+    <row r="1015"/>
+    <row r="1016"/>
+    <row r="1017"/>
+    <row r="1018"/>
+    <row r="1019"/>
+    <row r="1020"/>
+    <row r="1021"/>
+    <row r="1022"/>
+    <row r="1023"/>
+    <row r="1024"/>
+    <row r="1025"/>
+    <row r="1026"/>
+    <row r="1027"/>
+    <row r="1028"/>
+    <row r="1029"/>
     <row r="1030" ht="20" customHeight="1">
       <c r="A1030" s="27" t="inlineStr">
         <is>
@@ -11264,9 +11409,10 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="2">
+  <mergeCells count="3">
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A1030:AN1030"/>
-    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <conditionalFormatting sqref="B10:B17">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
@@ -11398,32 +11544,42 @@
   <dimension ref="A1:AD16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="15.5" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="19.5" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="29.5" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="14.5" customWidth="1" min="7" max="7"/>
+    <col width="11.5" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
     <col width="32" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="213" t="inlineStr">
         <is>
           <t>VARSAYIMLAR — İthalat Gerçek Birim Maliyet Motoru</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="B1" s="214" t="n"/>
+      <c r="C1" s="214" t="n"/>
+      <c r="D1" s="214" t="n"/>
+      <c r="E1" s="214" t="n"/>
+      <c r="F1" s="214" t="n"/>
+      <c r="G1" s="214" t="n"/>
+      <c r="H1" s="214" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="233" t="inlineStr">
         <is>
           <t>Model varsayımları — her satırda kaynak ve güven</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="21" t="inlineStr">
         <is>
@@ -11794,6 +11950,7 @@
         <v/>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="J15" s="10" t="inlineStr">
         <is>
@@ -11818,8 +11975,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:AD1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <conditionalFormatting sqref="H6:H13">
     <cfRule type="expression" priority="1" dxfId="2">
@@ -11860,15 +12018,24 @@
     <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="213" t="inlineStr">
         <is>
           <t>KURALLAR — İthalat Gerçek Birim Maliyet Motoru</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="31" t="inlineStr">
+      <c r="B1" s="214" t="n"/>
+      <c r="C1" s="214" t="n"/>
+      <c r="D1" s="214" t="n"/>
+      <c r="E1" s="214" t="n"/>
+      <c r="F1" s="214" t="n"/>
+      <c r="G1" s="214" t="n"/>
+      <c r="H1" s="214" t="n"/>
+      <c r="I1" s="214" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="233" t="inlineStr">
         <is>
           <t>Gümrük / KDV / KKDF kural tablosu (yıl yan yana)</t>
         </is>
@@ -11881,6 +12048,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="21" t="inlineStr">
         <is>
@@ -12188,6 +12356,8 @@
         <v/>
       </c>
     </row>
+    <row r="12"/>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
@@ -12231,9 +12401,9 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
   <mergeCells count="3">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
     <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A1:AD1"/>
-    <mergeCell ref="A3:K3"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation sqref="F7:F11" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Geçersiz" error="0 ve üzeri sayı." promptTitle="Kural değeri" prompt="Yıl kolonuna sayısal parametre girin." type="decimal" errorStyle="stop" operator="between">
@@ -12274,17 +12444,29 @@
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="213" t="inlineStr">
         <is>
           <t>MOTOR — İthalat Gerçek Birim Maliyet Motoru</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="31" t="inlineStr">
+      <c r="B1" s="214" t="n"/>
+      <c r="C1" s="214" t="n"/>
+      <c r="D1" s="214" t="n"/>
+      <c r="E1" s="214" t="n"/>
+      <c r="F1" s="214" t="n"/>
+      <c r="G1" s="214" t="n"/>
+      <c r="H1" s="214" t="n"/>
+      <c r="I1" s="214" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="233" t="inlineStr">
         <is>
           <t>Hesap zinciri — her adımda kural_id</t>
         </is>
@@ -12297,6 +12479,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="21" t="inlineStr">
         <is>
@@ -14218,8 +14401,8 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
   <mergeCells count="3">
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
     <mergeCell ref="A4:G4"/>
   </mergeCells>
   <conditionalFormatting sqref="G7:G66">
@@ -14252,24 +14435,39 @@
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="18.5" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="213" t="inlineStr">
         <is>
           <t>FINANSMAN — İthalat Gerçek Birim Maliyet Motoru</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="B1" s="214" t="n"/>
+      <c r="C1" s="214" t="n"/>
+      <c r="D1" s="214" t="n"/>
+      <c r="E1" s="214" t="n"/>
+      <c r="F1" s="214" t="n"/>
+      <c r="G1" s="214" t="n"/>
+      <c r="H1" s="214" t="n"/>
+      <c r="I1" s="214" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="233" t="inlineStr">
         <is>
           <t>Finansman senaryoları — OZ_KAYNAK ve KREDI</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="45" t="inlineStr">
         <is>
@@ -14343,6 +14541,7 @@
         <v/>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
@@ -14376,6 +14575,7 @@
         <v/>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="47" t="inlineStr">
         <is>
@@ -14405,8 +14605,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="2">
-    <mergeCell ref="A1:AD1"/>
+  <mergeCells count="3">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
     <mergeCell ref="B11:H11"/>
   </mergeCells>
   <conditionalFormatting sqref="E6:E7">
@@ -14432,28 +14633,42 @@
   <dimension ref="A1:AD33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="39.5" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="213" t="inlineStr">
         <is>
           <t>SENARYO — İthalat Gerçek Birim Maliyet Motoru</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="B1" s="214" t="n"/>
+      <c r="C1" s="214" t="n"/>
+      <c r="D1" s="214" t="n"/>
+      <c r="E1" s="214" t="n"/>
+      <c r="F1" s="214" t="n"/>
+      <c r="G1" s="214" t="n"/>
+      <c r="H1" s="214" t="n"/>
+      <c r="I1" s="214" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="233" t="inlineStr">
         <is>
           <t>Senaryo ve duyarlılık (tornado)</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="45" t="inlineStr">
         <is>
@@ -14590,6 +14805,7 @@
         <v>1200000</v>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
@@ -14612,6 +14828,7 @@
         <v/>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
@@ -14717,6 +14934,7 @@
         <v/>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
@@ -14739,6 +14957,7 @@
         <v/>
       </c>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
@@ -14849,9 +15068,10 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="2">
+  <mergeCells count="3">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
     <mergeCell ref="B12:H12"/>
-    <mergeCell ref="A1:AD1"/>
   </mergeCells>
   <conditionalFormatting sqref="D6:D9">
     <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="5">
@@ -14892,24 +15112,42 @@
   <dimension ref="A1:AD16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="89.5" customWidth="1" min="1" max="1"/>
     <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="213" t="inlineStr">
         <is>
           <t>KARAR — İthalat Gerçek Birim Maliyet Motoru</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="51" t="inlineStr">
+      <c r="B1" s="214" t="n"/>
+      <c r="C1" s="214" t="n"/>
+      <c r="D1" s="214" t="n"/>
+      <c r="E1" s="214" t="n"/>
+      <c r="F1" s="214" t="n"/>
+      <c r="G1" s="214" t="n"/>
+      <c r="H1" s="214" t="n"/>
+      <c r="I1" s="214" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="233" t="inlineStr">
         <is>
           <t>Yatırım karar kapısı</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="51" t="inlineStr">
         <is>
@@ -14932,6 +15170,7 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="61" t="inlineStr">
         <is>
@@ -14976,6 +15215,7 @@
         <v/>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="61" t="inlineStr">
         <is>
@@ -14998,6 +15238,7 @@
         <v/>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
@@ -15007,10 +15248,11 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="3">
+  <mergeCells count="4">
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="B6:H6"/>
-    <mergeCell ref="A16:H16"/>
-    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <conditionalFormatting sqref="B5">
     <cfRule type="expression" priority="1" dxfId="2">
@@ -15062,30 +15304,40 @@
   <dimension ref="A1:AD13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22.5" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="49.5" customWidth="1" min="3" max="3"/>
+    <col width="18.5" customWidth="1" min="4" max="4"/>
+    <col width="14.5" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="213" t="inlineStr">
         <is>
           <t>VAKALAR — İthalat Gerçek Birim Maliyet Motoru</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="31" t="inlineStr">
+      <c r="B1" s="214" t="n"/>
+      <c r="C1" s="214" t="n"/>
+      <c r="D1" s="214" t="n"/>
+      <c r="E1" s="214" t="n"/>
+      <c r="F1" s="214" t="n"/>
+      <c r="G1" s="214" t="n"/>
+      <c r="H1" s="214" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="233" t="inlineStr">
         <is>
           <t>Altın vakalar — gerçek birim maliyet</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="21" t="inlineStr">
         <is>
@@ -15276,6 +15528,8 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
@@ -15302,7 +15556,7 @@
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
   <mergeCells count="2">
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <conditionalFormatting sqref="G6:G9">
     <cfRule type="expression" priority="1" dxfId="3">
@@ -15331,22 +15585,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:AC27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="62.5" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="15.5" customWidth="1" min="4" max="4"/>
+    <col width="36.5" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="6" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="11.5" customWidth="1" min="7" max="7"/>
+    <col width="75.5" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="15.5" customWidth="1" min="10" max="10"/>
+    <col width="81.5" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
     <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15380,6 +15635,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="B5" s="106" t="inlineStr">
         <is>
@@ -15510,6 +15766,7 @@
       <c r="L9" s="107" t="n"/>
       <c r="M9" s="107" t="n"/>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="B11" s="100" t="inlineStr">
         <is>
@@ -15539,6 +15796,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="B14" s="123" t="inlineStr">
         <is>
@@ -15793,6 +16051,7 @@
         <v>92</v>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="B22" s="134" t="inlineStr">
         <is>
@@ -15881,13 +16140,21 @@
           <t>✓ 90 GÜNLÜK PROJEKSİYONDA NAKİT SIKIŞIKLIĞI TESPİT EDİLMEDİ</t>
         </is>
       </c>
+      <c r="G26" s="215" t="n"/>
+      <c r="H26" s="215" t="n"/>
+      <c r="I26" s="216" t="n"/>
       <c r="K26" s="143" t="inlineStr">
         <is>
           <t>STRATEJİ REÇETESİNİ İNCELE &gt;</t>
         </is>
       </c>
     </row>
-    <row r="27"/>
+    <row r="27">
+      <c r="F27" s="217" t="n"/>
+      <c r="G27" s="218" t="n"/>
+      <c r="H27" s="218" t="n"/>
+      <c r="I27" s="219" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="K26:M27"/>
@@ -15910,17 +16177,34 @@
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
     <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="213" t="inlineStr">
         <is>
           <t>KANIT RAPORU — İthalat Gerçek Birim Maliyet Motoru</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="51" t="inlineStr">
+      <c r="B1" s="214" t="n"/>
+      <c r="C1" s="214" t="n"/>
+      <c r="D1" s="214" t="n"/>
+      <c r="E1" s="214" t="n"/>
+      <c r="F1" s="214" t="n"/>
+      <c r="G1" s="214" t="n"/>
+      <c r="H1" s="214" t="n"/>
+      <c r="I1" s="214" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="233" t="inlineStr">
         <is>
           <t>KANIT RAPORU — İthalat Gerçek Birim Maliyet</t>
         </is>
@@ -15933,6 +16217,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="61" t="inlineStr">
         <is>
@@ -15988,6 +16273,7 @@
         <v/>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="61" t="inlineStr">
         <is>
@@ -16065,6 +16351,7 @@
         <v/>
       </c>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="66" t="inlineStr">
         <is>
@@ -16087,6 +16374,7 @@
         <v/>
       </c>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="61" t="inlineStr">
         <is>
@@ -16098,6 +16386,7 @@
         <v/>
       </c>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="61" t="inlineStr">
         <is>
@@ -16109,6 +16398,7 @@
         <v/>
       </c>
     </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="61" t="inlineStr">
         <is>
@@ -16120,6 +16410,8 @@
         <v/>
       </c>
     </row>
+    <row r="28"/>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="61" t="inlineStr">
         <is>
@@ -16136,6 +16428,8 @@
       </c>
       <c r="B31" s="68" t="inlineStr"/>
     </row>
+    <row r="32"/>
+    <row r="33"/>
     <row r="34">
       <c r="A34" s="69" t="inlineStr">
         <is>
@@ -16145,10 +16439,11 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="B21:H21"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
     <mergeCell ref="B25:H25"/>
-    <mergeCell ref="A1:AD1"/>
     <mergeCell ref="B23:H23"/>
   </mergeCells>
   <conditionalFormatting sqref="B20">
@@ -16197,23 +16492,41 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="70.5" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="213" t="inlineStr">
         <is>
           <t>KONTROLLER — İthalat Gerçek Birim Maliyet Motoru</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="B1" s="214" t="n"/>
+      <c r="C1" s="214" t="n"/>
+      <c r="D1" s="214" t="n"/>
+      <c r="E1" s="214" t="n"/>
+      <c r="F1" s="214" t="n"/>
+      <c r="G1" s="214" t="n"/>
+      <c r="H1" s="214" t="n"/>
+      <c r="I1" s="214" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="233" t="inlineStr">
         <is>
           <t>Dosya sağlık kontrolleri</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
@@ -16302,6 +16615,7 @@
         <v/>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="61" t="inlineStr">
         <is>
@@ -16370,8 +16684,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:AD1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B11">
     <cfRule type="expression" priority="1" dxfId="2">
@@ -16410,27 +16725,41 @@
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="15.5" customWidth="1" min="8" max="8"/>
+    <col width="17.5" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="15.5" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="213" t="inlineStr">
         <is>
           <t>ORNEK VERI — İthalat Gerçek Birim Maliyet Motoru</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="31" t="inlineStr">
+      <c r="B1" s="214" t="n"/>
+      <c r="C1" s="214" t="n"/>
+      <c r="D1" s="214" t="n"/>
+      <c r="E1" s="214" t="n"/>
+      <c r="F1" s="214" t="n"/>
+      <c r="G1" s="214" t="n"/>
+      <c r="H1" s="214" t="n"/>
+      <c r="I1" s="214" t="n"/>
+      <c r="J1" s="214" t="n"/>
+      <c r="K1" s="214" t="n"/>
+      <c r="L1" s="214" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="233" t="inlineStr">
         <is>
           <t>Örnek sevkiyat verileri</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="21" t="inlineStr">
         <is>
@@ -22668,7 +22997,7 @@
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
   <mergeCells count="2">
     <mergeCell ref="A3:L3"/>
-    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="B6:B20">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
@@ -22711,28 +23040,45 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T8"/>
+  <dimension ref="A1:AC8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13.5" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="213" t="inlineStr">
         <is>
           <t>LISTELER — İthalat Gerçek Birim Maliyet Motoru</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="B1" s="214" t="n"/>
+      <c r="C1" s="214" t="n"/>
+      <c r="D1" s="214" t="n"/>
+      <c r="E1" s="214" t="n"/>
+      <c r="F1" s="214" t="n"/>
+      <c r="G1" s="214" t="n"/>
+      <c r="H1" s="214" t="n"/>
+      <c r="I1" s="214" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="233" t="inlineStr">
         <is>
           <t>Doğrulama listeleri</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="45" t="inlineStr">
         <is>
@@ -22787,8 +23133,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:T1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -22806,12 +23153,13 @@
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10.5" customWidth="1" min="3" max="3"/>
     <col width="32" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="19.5" customWidth="1" min="6" max="6"/>
+    <col width="20.5" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
@@ -22821,20 +23169,29 @@
     <col width="10" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="213" t="inlineStr">
         <is>
           <t>AYARLAR — İthalat Gerçek Birim Maliyet Motoru</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="B1" s="214" t="n"/>
+      <c r="C1" s="214" t="n"/>
+      <c r="D1" s="214" t="n"/>
+      <c r="E1" s="214" t="n"/>
+      <c r="F1" s="214" t="n"/>
+      <c r="G1" s="214" t="n"/>
+      <c r="H1" s="214" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="233" t="inlineStr">
         <is>
           <t>Parametreler (tek kaynak) + kur tablosu</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="21" t="inlineStr">
         <is>
@@ -24246,6 +24603,7 @@
         <v/>
       </c>
     </row>
+    <row r="41"/>
     <row r="42">
       <c r="J42" s="5" t="inlineStr">
         <is>
@@ -24386,6 +24744,7 @@
         <v/>
       </c>
     </row>
+    <row r="47"/>
     <row r="48">
       <c r="J48" s="10" t="inlineStr">
         <is>
@@ -24408,6 +24767,7 @@
         <v/>
       </c>
     </row>
+    <row r="50"/>
     <row r="51">
       <c r="J51" s="8" t="inlineStr">
         <is>
@@ -24417,8 +24777,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:AD1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation sqref="B6" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Geçersiz" error="2025-2027." promptTitle="Hesap Yılı" prompt="Aktif yılı seçin." type="list" errorStyle="stop">
@@ -24457,17 +24818,34 @@
   <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="155.5" customWidth="1" min="1" max="1"/>
     <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="213" t="inlineStr">
         <is>
           <t>KILAVUZ — İthalat Gerçek Birim Maliyet Motoru</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="214" t="n"/>
+      <c r="C1" s="214" t="n"/>
+      <c r="D1" s="214" t="n"/>
+      <c r="E1" s="214" t="n"/>
+      <c r="F1" s="214" t="n"/>
+      <c r="G1" s="214" t="n"/>
+      <c r="H1" s="214" t="n"/>
+      <c r="I1" s="214" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
@@ -24475,6 +24853,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
@@ -24503,6 +24882,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="75" t="inlineStr">
         <is>
@@ -24517,6 +24897,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="76" t="inlineStr">
         <is>
@@ -24524,6 +24905,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
@@ -24548,6 +24930,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
@@ -24562,6 +24945,7 @@
         </is>
       </c>
     </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
@@ -24576,9 +24960,9 @@
     <mergeCell ref="B15:J15"/>
     <mergeCell ref="A8:T8"/>
     <mergeCell ref="A6:T6"/>
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A7:T7"/>
     <mergeCell ref="A19:J19"/>
-    <mergeCell ref="A1:AD1"/>
     <mergeCell ref="A13:J13"/>
     <mergeCell ref="A11:T11"/>
     <mergeCell ref="B16:J16"/>
@@ -24594,18 +24978,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="36.5" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="37.5" customWidth="1" min="4" max="4"/>
+    <col width="18.5" customWidth="1" min="5" max="5"/>
+    <col width="13.5" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22.5" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -24615,12 +25000,16 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="B3" s="144" t="inlineStr">
         <is>
           <t>🔍  İTHALAT LANDED COST MOTORU — Kayıt veya hesap ara...</t>
         </is>
       </c>
+      <c r="C3" s="220" t="n"/>
+      <c r="D3" s="220" t="n"/>
+      <c r="E3" s="221" t="n"/>
       <c r="G3" s="145" t="inlineStr">
         <is>
           <t>TOPLAM: 1.450 KAYIT</t>
@@ -24632,6 +25021,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="B5" s="147" t="inlineStr">
         <is>
@@ -25044,22 +25434,17 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="B17" s="164" t="inlineStr">
         <is>
           <t>SAYFA TOPLAMI (10 / 1.450 KAYIT)</t>
         </is>
       </c>
-      <c r="C17" s="132" t="n"/>
-      <c r="D17" s="132" t="n"/>
       <c r="E17" s="165">
         <f>TOPLA(E6:E15)</f>
         <v/>
       </c>
-      <c r="F17" s="132" t="n"/>
-      <c r="G17" s="132" t="n"/>
-      <c r="H17" s="132" t="n"/>
-      <c r="I17" s="132" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -25080,7 +25465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:AC26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -25125,25 +25510,26 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="169" t="inlineStr">
         <is>
           <t>SENARYO A: KÖTÜMSER (STRES TESTİ -%20)</t>
         </is>
       </c>
-      <c r="C6" s="107" t="n"/>
-      <c r="D6" s="107" t="n"/>
-      <c r="E6" s="107" t="n"/>
-      <c r="F6" s="107" t="n"/>
+      <c r="C6" s="220" t="n"/>
+      <c r="D6" s="220" t="n"/>
+      <c r="E6" s="220" t="n"/>
+      <c r="F6" s="221" t="n"/>
       <c r="H6" s="170" t="inlineStr">
         <is>
           <t>SENARYO B: BAZ MODEL (HEDEFLENEN)</t>
         </is>
       </c>
-      <c r="I6" s="107" t="n"/>
-      <c r="J6" s="107" t="n"/>
-      <c r="K6" s="107" t="n"/>
-      <c r="L6" s="107" t="n"/>
+      <c r="I6" s="220" t="n"/>
+      <c r="J6" s="220" t="n"/>
+      <c r="K6" s="220" t="n"/>
+      <c r="L6" s="221" t="n"/>
     </row>
     <row r="7">
       <c r="B7" s="107" t="n"/>
@@ -25294,32 +25680,33 @@
           <t>STRES SENARYOSUNDA DAHİ İFLAS RİSKİ YOK</t>
         </is>
       </c>
-      <c r="C14" s="107" t="n"/>
-      <c r="D14" s="107" t="n"/>
-      <c r="E14" s="107" t="n"/>
-      <c r="F14" s="107" t="n"/>
+      <c r="C14" s="222" t="n"/>
+      <c r="D14" s="222" t="n"/>
+      <c r="E14" s="222" t="n"/>
+      <c r="F14" s="223" t="n"/>
       <c r="H14" s="177" t="inlineStr">
         <is>
           <t>OPTİMUM İCRA VE PLANLAMA REÇETESİ</t>
         </is>
       </c>
-      <c r="I14" s="107" t="n"/>
-      <c r="J14" s="107" t="n"/>
-      <c r="K14" s="107" t="n"/>
-      <c r="L14" s="107" t="n"/>
+      <c r="I14" s="224" t="n"/>
+      <c r="J14" s="224" t="n"/>
+      <c r="K14" s="224" t="n"/>
+      <c r="L14" s="225" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="107" t="n"/>
-      <c r="C15" s="107" t="n"/>
-      <c r="D15" s="107" t="n"/>
-      <c r="E15" s="107" t="n"/>
-      <c r="F15" s="107" t="n"/>
-      <c r="H15" s="107" t="n"/>
-      <c r="I15" s="107" t="n"/>
-      <c r="J15" s="107" t="n"/>
-      <c r="K15" s="107" t="n"/>
-      <c r="L15" s="107" t="n"/>
-    </row>
+      <c r="B15" s="226" t="n"/>
+      <c r="C15" s="227" t="n"/>
+      <c r="D15" s="227" t="n"/>
+      <c r="E15" s="227" t="n"/>
+      <c r="F15" s="228" t="n"/>
+      <c r="H15" s="229" t="n"/>
+      <c r="I15" s="230" t="n"/>
+      <c r="J15" s="230" t="n"/>
+      <c r="K15" s="230" t="n"/>
+      <c r="L15" s="231" t="n"/>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="B17" s="87" t="inlineStr">
         <is>
@@ -25327,6 +25714,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="B19" s="134" t="inlineStr">
         <is>
@@ -25401,25 +25789,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:AC15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="27" customWidth="1" min="4" max="4"/>
-    <col width="29" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="30.5" customWidth="1" min="2" max="2"/>
+    <col width="23.5" customWidth="1" min="3" max="3"/>
+    <col width="48.5" customWidth="1" min="4" max="4"/>
+    <col width="43.5" customWidth="1" min="5" max="5"/>
+    <col width="21.5" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="184" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="213" t="inlineStr">
         <is>
           <t>YÜRÜTME ÇEKİRDEĞİ — ZORUNLU ÜRETİM SIRASI</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="214" t="n"/>
+      <c r="C1" s="214" t="n"/>
+      <c r="D1" s="214" t="n"/>
+      <c r="E1" s="214" t="n"/>
+      <c r="F1" s="214" t="n"/>
+      <c r="G1" s="214" t="n"/>
+      <c r="H1" s="214" t="n"/>
+      <c r="I1" s="214" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="185" t="inlineStr">
         <is>
@@ -25879,7 +26279,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -25892,22 +26292,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:AC34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="89.5" customWidth="1" min="2" max="2"/>
+    <col width="34.5" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="187" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="213" t="inlineStr">
         <is>
           <t>NİHAİ KONTROL LİSTESİ — KANITSIZ GEÇİŞ YOK</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="214" t="n"/>
+      <c r="C1" s="214" t="n"/>
+      <c r="D1" s="214" t="n"/>
+      <c r="E1" s="214" t="n"/>
+      <c r="F1" s="214" t="n"/>
+      <c r="G1" s="214" t="n"/>
+      <c r="H1" s="214" t="n"/>
+      <c r="I1" s="214" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="188" t="inlineStr">
         <is>
@@ -26619,7 +27034,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -26632,24 +27047,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:AC22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="30.5" customWidth="1" min="1" max="1"/>
+    <col width="71.5" customWidth="1" min="2" max="2"/>
+    <col width="160.5" customWidth="1" min="3" max="3"/>
+    <col width="70.5" customWidth="1" min="4" max="4"/>
+    <col width="50.5" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="192" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="213" t="inlineStr">
         <is>
           <t>GÖRSEL TASARIM VE PREMIUM EXCEL STANDARDI</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="214" t="n"/>
+      <c r="C1" s="214" t="n"/>
+      <c r="D1" s="214" t="n"/>
+      <c r="E1" s="214" t="n"/>
+      <c r="F1" s="214" t="n"/>
+      <c r="G1" s="214" t="n"/>
+      <c r="H1" s="214" t="n"/>
+      <c r="I1" s="214" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="193" t="inlineStr">
         <is>
@@ -27292,7 +27720,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -27305,24 +27733,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:AC18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="22.5" customWidth="1" min="1" max="1"/>
+    <col width="60.5" customWidth="1" min="2" max="2"/>
+    <col width="86.5" customWidth="1" min="3" max="3"/>
+    <col width="40.5" customWidth="1" min="4" max="4"/>
+    <col width="39.5" customWidth="1" min="5" max="5"/>
+    <col width="27.5" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="196" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="213" t="inlineStr">
         <is>
           <t>TÜRKİYE MUHASEBE VE TEKDÜZEN HESAP PLANI STANDARDI</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="214" t="n"/>
+      <c r="C1" s="214" t="n"/>
+      <c r="D1" s="214" t="n"/>
+      <c r="E1" s="214" t="n"/>
+      <c r="F1" s="214" t="n"/>
+      <c r="G1" s="214" t="n"/>
+      <c r="H1" s="214" t="n"/>
+      <c r="I1" s="214" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="197" t="inlineStr">
         <is>
@@ -27837,7 +28278,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -27850,23 +28291,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:AC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="54" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="20.5" customWidth="1" min="1" max="1"/>
+    <col width="41.5" customWidth="1" min="2" max="2"/>
+    <col width="86.5" customWidth="1" min="3" max="3"/>
+    <col width="35.5" customWidth="1" min="4" max="4"/>
+    <col width="33.5" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="199" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="213" t="inlineStr">
         <is>
           <t>KARAR, GÜVEN VE SATIŞA HAZIRLIK STANDARDI</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="214" t="n"/>
+      <c r="C1" s="214" t="n"/>
+      <c r="D1" s="214" t="n"/>
+      <c r="E1" s="214" t="n"/>
+      <c r="F1" s="214" t="n"/>
+      <c r="G1" s="214" t="n"/>
+      <c r="H1" s="214" t="n"/>
+      <c r="I1" s="214" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="200" t="inlineStr">
         <is>
@@ -28413,7 +28868,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXCELARSIV_PRODUCTS/ithalat-landed-cost-motoru/IthalatLandedCostMotoru.xlsx
+++ b/EXCELARSIV_PRODUCTS/ithalat-landed-cost-motoru/IthalatLandedCostMotoru.xlsx
@@ -4069,7 +4069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC33"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4090,14 +4090,6 @@
           <t>EXCELARŞİV KARAR SİSTEMİ v15.1 — ÜRETİM REFERANSI</t>
         </is>
       </c>
-      <c r="B1" s="214" t="n"/>
-      <c r="C1" s="214" t="n"/>
-      <c r="D1" s="214" t="n"/>
-      <c r="E1" s="214" t="n"/>
-      <c r="F1" s="214" t="n"/>
-      <c r="G1" s="214" t="n"/>
-      <c r="H1" s="214" t="n"/>
-      <c r="I1" s="214" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1">
@@ -4476,7 +4468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN21"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="72" customWidth="1" min="1" max="1"/>
@@ -4497,14 +4489,6 @@
           <t>KAPAK — İthalat Gerçek Birim Maliyet Motoru</t>
         </is>
       </c>
-      <c r="B1" s="214" t="n"/>
-      <c r="C1" s="214" t="n"/>
-      <c r="D1" s="214" t="n"/>
-      <c r="E1" s="214" t="n"/>
-      <c r="F1" s="214" t="n"/>
-      <c r="G1" s="214" t="n"/>
-      <c r="H1" s="214" t="n"/>
-      <c r="I1" s="214" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -4640,7 +4624,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD12"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="112.5" customWidth="1" min="1" max="1"/>
@@ -4661,14 +4645,6 @@
           <t>HIZLI BASLANGIC — İthalat Gerçek Birim Maliyet Motoru</t>
         </is>
       </c>
-      <c r="B1" s="214" t="n"/>
-      <c r="C1" s="214" t="n"/>
-      <c r="D1" s="214" t="n"/>
-      <c r="E1" s="214" t="n"/>
-      <c r="F1" s="214" t="n"/>
-      <c r="G1" s="214" t="n"/>
-      <c r="H1" s="214" t="n"/>
-      <c r="I1" s="214" t="n"/>
     </row>
     <row r="2"/>
     <row r="3">
@@ -4779,14 +4755,6 @@
           <t>GIRDI — İthalat Gerçek Birim Maliyet Motoru</t>
         </is>
       </c>
-      <c r="B1" s="214" t="n"/>
-      <c r="C1" s="214" t="n"/>
-      <c r="D1" s="214" t="n"/>
-      <c r="E1" s="214" t="n"/>
-      <c r="F1" s="214" t="n"/>
-      <c r="G1" s="214" t="n"/>
-      <c r="H1" s="214" t="n"/>
-      <c r="I1" s="214" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -11411,8 +11379,8 @@
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
   <mergeCells count="3">
     <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
     <mergeCell ref="A1030:AN1030"/>
-    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <conditionalFormatting sqref="B10:B17">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
@@ -11541,7 +11509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD16"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15.5" customWidth="1" min="1" max="1"/>
@@ -11563,13 +11531,6 @@
           <t>VARSAYIMLAR — İthalat Gerçek Birim Maliyet Motoru</t>
         </is>
       </c>
-      <c r="B1" s="214" t="n"/>
-      <c r="C1" s="214" t="n"/>
-      <c r="D1" s="214" t="n"/>
-      <c r="E1" s="214" t="n"/>
-      <c r="F1" s="214" t="n"/>
-      <c r="G1" s="214" t="n"/>
-      <c r="H1" s="214" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -12002,7 +11963,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD17"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -12024,14 +11985,6 @@
           <t>KURALLAR — İthalat Gerçek Birim Maliyet Motoru</t>
         </is>
       </c>
-      <c r="B1" s="214" t="n"/>
-      <c r="C1" s="214" t="n"/>
-      <c r="D1" s="214" t="n"/>
-      <c r="E1" s="214" t="n"/>
-      <c r="F1" s="214" t="n"/>
-      <c r="G1" s="214" t="n"/>
-      <c r="H1" s="214" t="n"/>
-      <c r="I1" s="214" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -12434,7 +12387,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD63"/>
+  <dimension ref="A1:I63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -12455,14 +12408,6 @@
           <t>MOTOR — İthalat Gerçek Birim Maliyet Motoru</t>
         </is>
       </c>
-      <c r="B1" s="214" t="n"/>
-      <c r="C1" s="214" t="n"/>
-      <c r="D1" s="214" t="n"/>
-      <c r="E1" s="214" t="n"/>
-      <c r="F1" s="214" t="n"/>
-      <c r="G1" s="214" t="n"/>
-      <c r="H1" s="214" t="n"/>
-      <c r="I1" s="214" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -13715,7 +13660,7 @@
         </is>
       </c>
       <c r="C43" s="34">
-        <f>IFERROR(IF(G41="VERI_YOK","Giriş tablosu boş — hesap yapılamaz.",IF(G41="YAPILIR","NPV pozitif ve marj hedef üstünde; ithalat yatırımı uygun.",IF(G41="DIKKAT","Marj veya NPV dikkat bandında; kur ve oranları gözden geçirin.","NPV negatif veya marj yetersiz; kötümser/bazda YATIRIM YAPMA."))),"")</f>
+        <f>IFERROR(IF(G41="VERI_YOK","Giriş tablosu boş — hesap yapılamaz.",IF(G41="YAPILIR","NPV pozitif AND marj hedef üstünde; ithalat yatırımı uygun.",IF(G41="DIKKAT","Marj veya NPV dikkat bandında; kur AND oranları gözden geçirin.","NPV negatif veya marj yetersiz; kötümser/bazda YATIRIM YAPMA."))),"")</f>
         <v/>
       </c>
       <c r="D43" s="38" t="inlineStr">
@@ -13734,7 +13679,7 @@
         </is>
       </c>
       <c r="G43" s="44">
-        <f>IFERROR(IF(G41="VERI_YOK","Giriş tablosu boş — hesap yapılamaz.",IF(G41="YAPILIR","NPV pozitif ve marj hedef üstünde; ithalat yatırımı uygun.",IF(G41="DIKKAT","Marj veya NPV dikkat bandında; kur ve oranları gözden geçirin.","NPV negatif veya marj yetersiz; kötümser/bazda YATIRIM YAPMA."))),"")</f>
+        <f>IFERROR(IF(G41="VERI_YOK","Giriş tablosu boş — hesap yapılamaz.",IF(G41="YAPILIR","NPV pozitif AND marj hedef üstünde; ithalat yatırımı uygun.",IF(G41="DIKKAT","Marj veya NPV dikkat bandında; kur AND oranları gözden geçirin.","NPV negatif veya marj yetersiz; kötümser/bazda YATIRIM YAPMA."))),"")</f>
         <v/>
       </c>
     </row>
@@ -14429,7 +14374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD15"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -14450,14 +14395,6 @@
           <t>FINANSMAN — İthalat Gerçek Birim Maliyet Motoru</t>
         </is>
       </c>
-      <c r="B1" s="214" t="n"/>
-      <c r="C1" s="214" t="n"/>
-      <c r="D1" s="214" t="n"/>
-      <c r="E1" s="214" t="n"/>
-      <c r="F1" s="214" t="n"/>
-      <c r="G1" s="214" t="n"/>
-      <c r="H1" s="214" t="n"/>
-      <c r="I1" s="214" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -14630,7 +14567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD33"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39.5" customWidth="1" min="1" max="1"/>
@@ -14651,14 +14588,6 @@
           <t>SENARYO — İthalat Gerçek Birim Maliyet Motoru</t>
         </is>
       </c>
-      <c r="B1" s="214" t="n"/>
-      <c r="C1" s="214" t="n"/>
-      <c r="D1" s="214" t="n"/>
-      <c r="E1" s="214" t="n"/>
-      <c r="F1" s="214" t="n"/>
-      <c r="G1" s="214" t="n"/>
-      <c r="H1" s="214" t="n"/>
-      <c r="I1" s="214" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -15109,7 +15038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AD16"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="89.5" customWidth="1" min="1" max="1"/>
@@ -15130,14 +15059,6 @@
           <t>KARAR — İthalat Gerçek Birim Maliyet Motoru</t>
         </is>
       </c>
-      <c r="B1" s="214" t="n"/>
-      <c r="C1" s="214" t="n"/>
-      <c r="D1" s="214" t="n"/>
-      <c r="E1" s="214" t="n"/>
-      <c r="F1" s="214" t="n"/>
-      <c r="G1" s="214" t="n"/>
-      <c r="H1" s="214" t="n"/>
-      <c r="I1" s="214" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -15249,9 +15170,9 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
   <mergeCells count="4">
-    <mergeCell ref="A16:H16"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="B6:H6"/>
+    <mergeCell ref="A16:H16"/>
     <mergeCell ref="A3:I3"/>
   </mergeCells>
   <conditionalFormatting sqref="B5">
@@ -15301,7 +15222,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD13"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22.5" customWidth="1" min="1" max="1"/>
@@ -15321,13 +15242,6 @@
           <t>VAKALAR — İthalat Gerçek Birim Maliyet Motoru</t>
         </is>
       </c>
-      <c r="B1" s="214" t="n"/>
-      <c r="C1" s="214" t="n"/>
-      <c r="D1" s="214" t="n"/>
-      <c r="E1" s="214" t="n"/>
-      <c r="F1" s="214" t="n"/>
-      <c r="G1" s="214" t="n"/>
-      <c r="H1" s="214" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -15585,7 +15499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC27"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -15716,7 +15630,7 @@
       <c r="I7" s="107" t="n"/>
       <c r="J7" s="107" t="n"/>
       <c r="K7" s="118">
-        <f>EĞER(E7&gt;0; YUVARLA(B7/E7; 2); 0)</f>
+        <f>IF(E7&gt;0, ROUND(B7/E7, 2), 0)</f>
         <v/>
       </c>
       <c r="L7" s="107" t="n"/>
@@ -16021,11 +15935,11 @@
         </is>
       </c>
       <c r="I19" s="207">
-        <f>TOPLA(I15:I18)</f>
+        <f>SUM(I15:I18)</f>
         <v/>
       </c>
       <c r="J19" s="208">
-        <f>TOPLA(J15:J18)</f>
+        <f>SUM(J15:J18)</f>
         <v/>
       </c>
       <c r="K19" s="132" t="inlineStr"/>
@@ -16172,7 +16086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AD34"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -16193,14 +16107,6 @@
           <t>KANIT RAPORU — İthalat Gerçek Birim Maliyet Motoru</t>
         </is>
       </c>
-      <c r="B1" s="214" t="n"/>
-      <c r="C1" s="214" t="n"/>
-      <c r="D1" s="214" t="n"/>
-      <c r="E1" s="214" t="n"/>
-      <c r="F1" s="214" t="n"/>
-      <c r="G1" s="214" t="n"/>
-      <c r="H1" s="214" t="n"/>
-      <c r="I1" s="214" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -16488,7 +16394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD19"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -16509,14 +16415,6 @@
           <t>KONTROLLER — İthalat Gerçek Birim Maliyet Motoru</t>
         </is>
       </c>
-      <c r="B1" s="214" t="n"/>
-      <c r="C1" s="214" t="n"/>
-      <c r="D1" s="214" t="n"/>
-      <c r="E1" s="214" t="n"/>
-      <c r="F1" s="214" t="n"/>
-      <c r="G1" s="214" t="n"/>
-      <c r="H1" s="214" t="n"/>
-      <c r="I1" s="214" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -16715,7 +16613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD1004"/>
+  <dimension ref="A1:L1004"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -16739,17 +16637,6 @@
           <t>ORNEK VERI — İthalat Gerçek Birim Maliyet Motoru</t>
         </is>
       </c>
-      <c r="B1" s="214" t="n"/>
-      <c r="C1" s="214" t="n"/>
-      <c r="D1" s="214" t="n"/>
-      <c r="E1" s="214" t="n"/>
-      <c r="F1" s="214" t="n"/>
-      <c r="G1" s="214" t="n"/>
-      <c r="H1" s="214" t="n"/>
-      <c r="I1" s="214" t="n"/>
-      <c r="J1" s="214" t="n"/>
-      <c r="K1" s="214" t="n"/>
-      <c r="L1" s="214" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -23040,7 +22927,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC8"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -23061,14 +22948,6 @@
           <t>LISTELER — İthalat Gerçek Birim Maliyet Motoru</t>
         </is>
       </c>
-      <c r="B1" s="214" t="n"/>
-      <c r="C1" s="214" t="n"/>
-      <c r="D1" s="214" t="n"/>
-      <c r="E1" s="214" t="n"/>
-      <c r="F1" s="214" t="n"/>
-      <c r="G1" s="214" t="n"/>
-      <c r="H1" s="214" t="n"/>
-      <c r="I1" s="214" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -23148,7 +23027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD51"/>
+  <dimension ref="A1:P51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -23175,13 +23054,6 @@
           <t>AYARLAR — İthalat Gerçek Birim Maliyet Motoru</t>
         </is>
       </c>
-      <c r="B1" s="214" t="n"/>
-      <c r="C1" s="214" t="n"/>
-      <c r="D1" s="214" t="n"/>
-      <c r="E1" s="214" t="n"/>
-      <c r="F1" s="214" t="n"/>
-      <c r="G1" s="214" t="n"/>
-      <c r="H1" s="214" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -24815,7 +24687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD21"/>
+  <dimension ref="A1:T21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="155.5" customWidth="1" min="1" max="1"/>
@@ -24836,14 +24708,6 @@
           <t>KILAVUZ — İthalat Gerçek Birim Maliyet Motoru</t>
         </is>
       </c>
-      <c r="B1" s="214" t="n"/>
-      <c r="C1" s="214" t="n"/>
-      <c r="D1" s="214" t="n"/>
-      <c r="E1" s="214" t="n"/>
-      <c r="F1" s="214" t="n"/>
-      <c r="G1" s="214" t="n"/>
-      <c r="H1" s="214" t="n"/>
-      <c r="I1" s="214" t="n"/>
     </row>
     <row r="2"/>
     <row r="3">
@@ -24978,7 +24842,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -25442,7 +25306,7 @@
         </is>
       </c>
       <c r="E17" s="165">
-        <f>TOPLA(E6:E15)</f>
+        <f>SUM(E6:E15)</f>
         <v/>
       </c>
     </row>
@@ -25465,7 +25329,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC26"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -25632,7 +25496,7 @@
       <c r="C11" s="107" t="n"/>
       <c r="D11" s="107" t="n"/>
       <c r="E11" s="212">
-        <f>YUVARLA(PANO!B7*0.8/PANO!E7; 2)</f>
+        <f>ROUND(PANO!B7*0.8/PANO!E7, 2)</f>
         <v/>
       </c>
       <c r="F11" s="107" t="n"/>
@@ -25789,7 +25653,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC15"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -25810,14 +25674,6 @@
           <t>YÜRÜTME ÇEKİRDEĞİ — ZORUNLU ÜRETİM SIRASI</t>
         </is>
       </c>
-      <c r="B1" s="214" t="n"/>
-      <c r="C1" s="214" t="n"/>
-      <c r="D1" s="214" t="n"/>
-      <c r="E1" s="214" t="n"/>
-      <c r="F1" s="214" t="n"/>
-      <c r="G1" s="214" t="n"/>
-      <c r="H1" s="214" t="n"/>
-      <c r="I1" s="214" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1">
@@ -26292,7 +26148,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC34"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -26313,14 +26169,6 @@
           <t>NİHAİ KONTROL LİSTESİ — KANITSIZ GEÇİŞ YOK</t>
         </is>
       </c>
-      <c r="B1" s="214" t="n"/>
-      <c r="C1" s="214" t="n"/>
-      <c r="D1" s="214" t="n"/>
-      <c r="E1" s="214" t="n"/>
-      <c r="F1" s="214" t="n"/>
-      <c r="G1" s="214" t="n"/>
-      <c r="H1" s="214" t="n"/>
-      <c r="I1" s="214" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1">
@@ -27047,7 +26895,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC22"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30.5" customWidth="1" min="1" max="1"/>
@@ -27068,14 +26916,6 @@
           <t>GÖRSEL TASARIM VE PREMIUM EXCEL STANDARDI</t>
         </is>
       </c>
-      <c r="B1" s="214" t="n"/>
-      <c r="C1" s="214" t="n"/>
-      <c r="D1" s="214" t="n"/>
-      <c r="E1" s="214" t="n"/>
-      <c r="F1" s="214" t="n"/>
-      <c r="G1" s="214" t="n"/>
-      <c r="H1" s="214" t="n"/>
-      <c r="I1" s="214" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1">
@@ -27733,7 +27573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC18"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22.5" customWidth="1" min="1" max="1"/>
@@ -27754,14 +27594,6 @@
           <t>TÜRKİYE MUHASEBE VE TEKDÜZEN HESAP PLANI STANDARDI</t>
         </is>
       </c>
-      <c r="B1" s="214" t="n"/>
-      <c r="C1" s="214" t="n"/>
-      <c r="D1" s="214" t="n"/>
-      <c r="E1" s="214" t="n"/>
-      <c r="F1" s="214" t="n"/>
-      <c r="G1" s="214" t="n"/>
-      <c r="H1" s="214" t="n"/>
-      <c r="I1" s="214" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1">
@@ -28291,7 +28123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC19"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20.5" customWidth="1" min="1" max="1"/>
@@ -28312,14 +28144,6 @@
           <t>KARAR, GÜVEN VE SATIŞA HAZIRLIK STANDARDI</t>
         </is>
       </c>
-      <c r="B1" s="214" t="n"/>
-      <c r="C1" s="214" t="n"/>
-      <c r="D1" s="214" t="n"/>
-      <c r="E1" s="214" t="n"/>
-      <c r="F1" s="214" t="n"/>
-      <c r="G1" s="214" t="n"/>
-      <c r="H1" s="214" t="n"/>
-      <c r="I1" s="214" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1">

--- a/EXCELARSIV_PRODUCTS/ithalat-landed-cost-motoru/IthalatLandedCostMotoru.xlsx
+++ b/EXCELARSIV_PRODUCTS/ithalat-landed-cost-motoru/IthalatLandedCostMotoru.xlsx
@@ -124,7 +124,7 @@
     <numFmt numFmtId="170" formatCode="₺#,##0"/>
     <numFmt numFmtId="171" formatCode="0.00&quot;x&quot;"/>
   </numFmts>
-  <fonts count="93">
+  <fonts count="128">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -659,8 +659,214 @@
       <color rgb="00475569"/>
       <sz val="9.5"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00334155"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0064748B"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001E40AF"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00B91C1C"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0015803D"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00475569"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0015803D"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00475569"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="000F172A"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00475569"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00166534"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001E40AF"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0092400E"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00115E59"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0038BDF8"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00F87171"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0034D399"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00059669"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000284C7"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00D97706"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="008B5CF6"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00059669"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00A7F3D0"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00065F46"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00991B1B"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00475569"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00059669"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00B91C1C"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001E40AF"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="002563EB"/>
+      <sz val="9.5"/>
+    </font>
   </fonts>
-  <fills count="35">
+  <fills count="39">
     <fill>
       <patternFill/>
     </fill>
@@ -852,8 +1058,32 @@
         <bgColor rgb="001B365D"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCFCE7"/>
+        <bgColor rgb="00DCFCE7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F1F5F9"/>
+        <bgColor rgb="00F1F5F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CCFBF1"/>
+        <bgColor rgb="00CCFBF1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0FDF4"/>
+        <bgColor rgb="00F0FDF4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="35">
+  <borders count="71">
     <border>
       <left/>
       <right/>
@@ -1216,11 +1446,353 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="001E3A8A"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="001E3A8A"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="001E3A8A"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00DC2626"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00DC2626"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00DC2626"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00059669"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00059669"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00059669"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="000284C7"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="000284C7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="000284C7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00334155"/>
+      </left>
+      <right style="thin">
+        <color rgb="00334155"/>
+      </right>
+      <top style="thin">
+        <color rgb="000F172A"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000F172A"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00334155"/>
+      </left>
+      <right style="thin">
+        <color rgb="00334155"/>
+      </right>
+      <top style="medium">
+        <color rgb="00334155"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="000F172A"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00065F46"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00065F46"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00065F46"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00065F46"/>
+      </right>
+      <top style="thin">
+        <color rgb="00065F46"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00065F46"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00065F46"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FECACA"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00FECACA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00FECACA"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FECACA"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00FECACA"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FCA5A5"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00FCA5A5"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00FCA5A5"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFDBFE"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFDBFE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFDBFE"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFDBFE"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFDBFE"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="0093C5FD"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="0093C5FD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="0093C5FD"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="234">
+  <cellXfs count="331">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -1771,6 +2343,235 @@
     </xf>
     <xf numFmtId="0" fontId="92" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="18" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="95" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="18" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="97" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="18" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="99" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="18" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="36" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="38" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="45" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="48" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="51" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="96" fillId="18" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="98" fillId="18" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="96" fillId="18" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="18" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="18" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="43" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="43" fillId="18" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="18" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="18" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="101" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="102" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="7" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="7" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="104" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="46" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="71" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="106" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="104" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="46" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="71" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="107" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="108" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="109" fillId="37" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="7" borderId="54" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="110" fillId="7" borderId="54" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="111" fillId="7" borderId="54" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="54" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="112" fillId="7" borderId="54" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="18" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="119" fillId="17" borderId="58" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="59" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="60" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="114" fillId="18" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="18" borderId="56" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="114" fillId="18" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="61" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="62" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="115" fillId="18" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="17" borderId="61" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="116" fillId="18" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="117" fillId="18" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="118" fillId="38" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="120" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="57" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="114" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="121" fillId="12" borderId="63" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="126" fillId="11" borderId="67" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="64" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="65" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="68" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="69" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="122" fillId="18" borderId="64" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="123" fillId="18" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="18" borderId="68" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="127" fillId="18" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="113" fillId="18" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="124" fillId="18" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="124" fillId="18" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="18" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="12" borderId="66" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="11" borderId="70" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="101" fillId="18" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="56" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="113" fillId="18" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="18" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4091,7 +4892,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="180" t="inlineStr">
         <is>
@@ -4356,7 +5156,6 @@
         </is>
       </c>
     </row>
-    <row r="25"/>
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="183" t="inlineStr">
         <is>
@@ -4490,7 +5289,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="232" t="inlineStr">
         <is>
@@ -4505,7 +5303,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
@@ -4548,7 +5345,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
@@ -4577,7 +5373,6 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
@@ -4592,7 +5387,6 @@
         </is>
       </c>
     </row>
-    <row r="20"/>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
@@ -4646,7 +5440,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
@@ -4654,7 +5447,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
@@ -4691,7 +5483,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
@@ -4706,7 +5497,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
@@ -4756,7 +5546,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="233" t="inlineStr">
         <is>
@@ -5034,7 +5823,6 @@
         </is>
       </c>
     </row>
-    <row r="22"/>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
@@ -5079,7 +5867,6 @@
         <v/>
       </c>
     </row>
-    <row r="27"/>
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
         <is>
@@ -11343,31 +12130,6 @@
         <v/>
       </c>
     </row>
-    <row r="1005"/>
-    <row r="1006"/>
-    <row r="1007"/>
-    <row r="1008"/>
-    <row r="1009"/>
-    <row r="1010"/>
-    <row r="1011"/>
-    <row r="1012"/>
-    <row r="1013"/>
-    <row r="1014"/>
-    <row r="1015"/>
-    <row r="1016"/>
-    <row r="1017"/>
-    <row r="1018"/>
-    <row r="1019"/>
-    <row r="1020"/>
-    <row r="1021"/>
-    <row r="1022"/>
-    <row r="1023"/>
-    <row r="1024"/>
-    <row r="1025"/>
-    <row r="1026"/>
-    <row r="1027"/>
-    <row r="1028"/>
-    <row r="1029"/>
     <row r="1030" ht="20" customHeight="1">
       <c r="A1030" s="27" t="inlineStr">
         <is>
@@ -11532,7 +12294,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="233" t="inlineStr">
         <is>
@@ -11540,7 +12301,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="21" t="inlineStr">
         <is>
@@ -11911,7 +12671,6 @@
         <v/>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="J15" s="10" t="inlineStr">
         <is>
@@ -11986,7 +12745,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="233" t="inlineStr">
         <is>
@@ -12001,7 +12759,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="21" t="inlineStr">
         <is>
@@ -12309,8 +13066,6 @@
         <v/>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
@@ -12409,7 +13164,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="233" t="inlineStr">
         <is>
@@ -12424,7 +13178,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="21" t="inlineStr">
         <is>
@@ -14396,7 +15149,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="233" t="inlineStr">
         <is>
@@ -14404,7 +15156,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="45" t="inlineStr">
         <is>
@@ -14478,7 +15229,6 @@
         <v/>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
@@ -14512,7 +15262,6 @@
         <v/>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="47" t="inlineStr">
         <is>
@@ -14589,7 +15338,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="233" t="inlineStr">
         <is>
@@ -14597,7 +15345,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="45" t="inlineStr">
         <is>
@@ -14734,7 +15481,6 @@
         <v>1200000</v>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
@@ -14757,7 +15503,6 @@
         <v/>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
@@ -14863,7 +15608,6 @@
         <v/>
       </c>
     </row>
-    <row r="21"/>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
@@ -14886,7 +15630,6 @@
         <v/>
       </c>
     </row>
-    <row r="24"/>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
@@ -15060,7 +15803,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="233" t="inlineStr">
         <is>
@@ -15068,7 +15810,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="51" t="inlineStr">
         <is>
@@ -15091,7 +15832,6 @@
         <v/>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="61" t="inlineStr">
         <is>
@@ -15136,7 +15876,6 @@
         <v/>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="61" t="inlineStr">
         <is>
@@ -15159,7 +15898,6 @@
         <v/>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
@@ -15243,7 +15981,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="233" t="inlineStr">
         <is>
@@ -15251,7 +15988,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="21" t="inlineStr">
         <is>
@@ -15442,8 +16178,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
@@ -15502,554 +16236,585 @@
   <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="62.5" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15.5" customWidth="1" min="4" max="4"/>
-    <col width="36.5" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="11.5" customWidth="1" min="7" max="7"/>
-    <col width="75.5" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15.5" customWidth="1" min="10" max="10"/>
-    <col width="81.5" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="86" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="234" t="inlineStr">
         <is>
           <t>☰ PANO</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="B2" s="102" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="235" t="inlineStr">
         <is>
           <t>İTHALAT LANDED COST MOTORU</t>
         </is>
       </c>
-      <c r="L2" s="103" t="inlineStr">
+      <c r="L2" s="236" t="inlineStr">
         <is>
           <t>Dönem: 2026 / Tam ▼</t>
         </is>
       </c>
-      <c r="M2" s="104" t="inlineStr">
+      <c r="M2" s="237" t="inlineStr">
         <is>
           <t>★ DOĞRULANMIŞ</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="B3" s="105" t="inlineStr">
+    <row r="3" ht="18" customHeight="1">
+      <c r="B3" s="238" t="inlineStr">
         <is>
           <t>Hedef Kullanıcı: İthalatçı CFO, satın alma, gümrük müşaviri, SMMM · 2026 Q3 Denetim Standardı</t>
         </is>
       </c>
     </row>
-    <row r="4"/>
-    <row r="5">
-      <c r="B5" s="106" t="inlineStr">
+    <row r="4" ht="10" customHeight="1"/>
+    <row r="5" ht="20" customHeight="1">
+      <c r="B5" s="239" t="inlineStr">
         <is>
           <t>CIF / GÜMRÜK MATRAHI</t>
         </is>
       </c>
-      <c r="C5" s="107" t="n"/>
-      <c r="D5" s="108" t="inlineStr">
+      <c r="C5" s="240" t="n"/>
+      <c r="D5" s="241" t="inlineStr">
         <is>
           <t>KONSOLİDE</t>
         </is>
       </c>
-      <c r="E5" s="109" t="inlineStr">
+      <c r="E5" s="242" t="inlineStr">
         <is>
           <t>BIRIM LANDED COST</t>
         </is>
       </c>
-      <c r="F5" s="107" t="n"/>
-      <c r="G5" s="110" t="inlineStr">
+      <c r="F5" s="240" t="n"/>
+      <c r="G5" s="243" t="inlineStr">
         <is>
           <t>KONTROL</t>
         </is>
       </c>
-      <c r="H5" s="106" t="inlineStr">
+      <c r="H5" s="244" t="inlineStr">
         <is>
           <t>NET OPERASYONEL MARJ</t>
         </is>
       </c>
-      <c r="I5" s="107" t="n"/>
-      <c r="J5" s="111" t="inlineStr">
+      <c r="I5" s="240" t="n"/>
+      <c r="J5" s="245" t="inlineStr">
         <is>
           <t>GÜVENLİ</t>
         </is>
       </c>
-      <c r="K5" s="112" t="inlineStr">
+      <c r="K5" s="246" t="inlineStr">
         <is>
           <t>SİSTEM GÜVEN SKORU</t>
         </is>
       </c>
-      <c r="L5" s="107" t="n"/>
-      <c r="M5" s="108" t="inlineStr">
+      <c r="L5" s="240" t="n"/>
+      <c r="M5" s="247" t="inlineStr">
         <is>
           <t>DENETLENDİ</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="B6" s="113" t="n"/>
-      <c r="C6" s="107" t="n"/>
-      <c r="D6" s="107" t="n"/>
-      <c r="E6" s="114" t="n"/>
-      <c r="F6" s="107" t="n"/>
-      <c r="G6" s="107" t="n"/>
-      <c r="H6" s="113" t="n"/>
-      <c r="I6" s="107" t="n"/>
-      <c r="J6" s="107" t="n"/>
-      <c r="K6" s="115" t="n"/>
-      <c r="L6" s="107" t="n"/>
-      <c r="M6" s="107" t="n"/>
-    </row>
-    <row r="7">
-      <c r="B7" s="203">
+    <row r="6" ht="6" customHeight="1">
+      <c r="B6" s="248" t="n"/>
+      <c r="C6" s="249" t="n"/>
+      <c r="D6" s="250" t="n"/>
+      <c r="E6" s="251" t="n"/>
+      <c r="F6" s="249" t="n"/>
+      <c r="G6" s="250" t="n"/>
+      <c r="H6" s="252" t="n"/>
+      <c r="I6" s="249" t="n"/>
+      <c r="J6" s="250" t="n"/>
+      <c r="K6" s="253" t="n"/>
+      <c r="L6" s="249" t="n"/>
+      <c r="M6" s="250" t="n"/>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="B7" s="254">
         <f>GİRDİLER!E17</f>
         <v/>
       </c>
-      <c r="C7" s="107" t="n"/>
-      <c r="D7" s="107" t="n"/>
-      <c r="E7" s="204">
+      <c r="C7" s="249" t="n"/>
+      <c r="D7" s="250" t="n"/>
+      <c r="E7" s="255">
         <f>B7*0.22</f>
         <v/>
       </c>
-      <c r="F7" s="107" t="n"/>
-      <c r="G7" s="107" t="n"/>
-      <c r="H7" s="203">
+      <c r="F7" s="249" t="n"/>
+      <c r="G7" s="250" t="n"/>
+      <c r="H7" s="256">
         <f>B7-E7</f>
         <v/>
       </c>
-      <c r="I7" s="107" t="n"/>
-      <c r="J7" s="107" t="n"/>
-      <c r="K7" s="118">
+      <c r="I7" s="249" t="n"/>
+      <c r="J7" s="250" t="n"/>
+      <c r="K7" s="257">
         <f>IF(E7&gt;0, ROUND(B7/E7, 2), 0)</f>
         <v/>
       </c>
-      <c r="L7" s="107" t="n"/>
-      <c r="M7" s="107" t="n"/>
-    </row>
-    <row r="8">
-      <c r="B8" s="113" t="n"/>
-      <c r="C8" s="107" t="n"/>
-      <c r="D8" s="107" t="n"/>
-      <c r="E8" s="114" t="n"/>
-      <c r="F8" s="107" t="n"/>
-      <c r="G8" s="107" t="n"/>
-      <c r="H8" s="113" t="n"/>
-      <c r="I8" s="107" t="n"/>
-      <c r="J8" s="107" t="n"/>
-      <c r="K8" s="115" t="n"/>
-      <c r="L8" s="107" t="n"/>
-      <c r="M8" s="107" t="n"/>
-    </row>
-    <row r="9">
-      <c r="B9" s="119" t="inlineStr">
+      <c r="L7" s="249" t="n"/>
+      <c r="M7" s="250" t="n"/>
+    </row>
+    <row r="8" ht="6" customHeight="1">
+      <c r="B8" s="248" t="n"/>
+      <c r="C8" s="249" t="n"/>
+      <c r="D8" s="250" t="n"/>
+      <c r="E8" s="251" t="n"/>
+      <c r="F8" s="249" t="n"/>
+      <c r="G8" s="250" t="n"/>
+      <c r="H8" s="252" t="n"/>
+      <c r="I8" s="249" t="n"/>
+      <c r="J8" s="250" t="n"/>
+      <c r="K8" s="253" t="n"/>
+      <c r="L8" s="249" t="n"/>
+      <c r="M8" s="250" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="B9" s="258" t="inlineStr">
         <is>
           <t>↑ %14.2 konsolide canlı veri bağlantısı</t>
         </is>
       </c>
-      <c r="C9" s="107" t="n"/>
-      <c r="D9" s="107" t="n"/>
-      <c r="E9" s="120" t="inlineStr">
+      <c r="C9" s="259" t="n"/>
+      <c r="D9" s="260" t="n"/>
+      <c r="E9" s="261" t="inlineStr">
         <is>
           <t>● 8 Kalem nakit karşılığı: bloke</t>
         </is>
       </c>
-      <c r="F9" s="107" t="n"/>
-      <c r="G9" s="107" t="n"/>
-      <c r="H9" s="119" t="inlineStr">
+      <c r="F9" s="259" t="n"/>
+      <c r="G9" s="260" t="n"/>
+      <c r="H9" s="262" t="inlineStr">
         <is>
           <t>██████████░░░░░ %78.0 NET MARJ</t>
         </is>
       </c>
-      <c r="I9" s="107" t="n"/>
-      <c r="J9" s="107" t="n"/>
-      <c r="K9" s="121" t="inlineStr">
+      <c r="I9" s="259" t="n"/>
+      <c r="J9" s="260" t="n"/>
+      <c r="K9" s="263" t="inlineStr">
         <is>
           <t>✓ İDEAL karşılama rasyosu</t>
         </is>
       </c>
-      <c r="L9" s="107" t="n"/>
-      <c r="M9" s="107" t="n"/>
-    </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="B11" s="100" t="inlineStr">
+      <c r="L9" s="259" t="n"/>
+      <c r="M9" s="260" t="n"/>
+    </row>
+    <row r="10" ht="14" customHeight="1"/>
+    <row r="11" ht="24" customHeight="1">
+      <c r="B11" s="264" t="inlineStr">
         <is>
           <t>İTHALAT LANDED COST MOTORU — DÖNEMSEL İCRA VE PROJEKSİYON</t>
         </is>
       </c>
-      <c r="F11" s="122" t="inlineStr">
+      <c r="F11" s="265" t="inlineStr">
         <is>
           <t>+%32 Verim</t>
         </is>
       </c>
-      <c r="H11" s="100" t="inlineStr">
+      <c r="H11" s="264" t="inlineStr">
         <is>
           <t>KONSOLİDE OPERASYON VE KARAR MATRİSİ</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="B12" s="99" t="inlineStr">
+    <row r="12" ht="18" customHeight="1">
+      <c r="B12" s="105" t="inlineStr">
         <is>
           <t>Kümülatif Hacim vs. Operasyonel Maliyet ve Net Kâr Eğilimi</t>
         </is>
       </c>
-      <c r="H12" s="99" t="inlineStr">
+      <c r="H12" s="105" t="inlineStr">
         <is>
           <t>Anlık Hesaplama Sonuçları, Dinamik Formül Çıktıları ve Durum Puanlaması</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="B14" s="123" t="inlineStr">
+    <row r="13" ht="8" customHeight="1"/>
+    <row r="14" ht="24" customHeight="1">
+      <c r="B14" s="266" t="inlineStr">
         <is>
           <t>Dönem</t>
         </is>
       </c>
-      <c r="C14" s="123" t="inlineStr">
+      <c r="C14" s="266" t="inlineStr">
         <is>
           <t>Aktif Hacim</t>
         </is>
       </c>
-      <c r="D14" s="123" t="inlineStr">
+      <c r="D14" s="266" t="inlineStr">
         <is>
           <t>Maliyet/Yük</t>
         </is>
       </c>
-      <c r="E14" s="123" t="inlineStr">
+      <c r="E14" s="266" t="inlineStr">
         <is>
           <t>Hedef</t>
         </is>
       </c>
-      <c r="H14" s="124" t="inlineStr">
+      <c r="H14" s="267" t="inlineStr">
         <is>
           <t>PARAMETRE / KALEM</t>
         </is>
       </c>
-      <c r="I14" s="124" t="inlineStr">
+      <c r="I14" s="268" t="inlineStr">
         <is>
           <t>ANA TUTAR</t>
         </is>
       </c>
-      <c r="J14" s="124" t="inlineStr">
+      <c r="J14" s="268" t="inlineStr">
         <is>
           <t>FARK / MARJ</t>
         </is>
       </c>
-      <c r="K14" s="124" t="inlineStr">
+      <c r="K14" s="268" t="inlineStr">
         <is>
           <t>VADE</t>
         </is>
       </c>
-      <c r="L14" s="124" t="inlineStr">
+      <c r="L14" s="268" t="inlineStr">
         <is>
           <t>KONTROL DURUMU</t>
         </is>
       </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="99" t="inlineStr">
+      <c r="M14" s="268" t="n"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="B15" s="269" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="C15" s="99" t="n">
+      <c r="C15" s="269" t="n">
         <v>65</v>
       </c>
-      <c r="D15" s="99" t="n">
+      <c r="D15" s="269" t="n">
         <v>45</v>
       </c>
-      <c r="E15" s="99" t="n">
+      <c r="E15" s="269" t="n">
         <v>60</v>
       </c>
-      <c r="H15" s="125" t="inlineStr">
+      <c r="H15" s="270" t="inlineStr">
         <is>
           <t>Dönemlik Kümülatif Bakiye</t>
         </is>
       </c>
-      <c r="I15" s="205">
+      <c r="I15" s="271">
         <f>B7*0.45</f>
         <v/>
       </c>
-      <c r="J15" s="206">
+      <c r="J15" s="272">
         <f>B7*0.05</f>
         <v/>
       </c>
-      <c r="K15" s="127" t="inlineStr">
+      <c r="K15" s="273" t="inlineStr">
         <is>
           <t>12 Ay</t>
         </is>
       </c>
-      <c r="L15" s="111" t="inlineStr">
+      <c r="L15" s="274" t="inlineStr">
         <is>
           <t>✓ DÜZENLİ</t>
         </is>
       </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="99" t="inlineStr">
+      <c r="M15" s="275" t="n"/>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="B16" s="276" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="C16" s="99" t="n">
+      <c r="C16" s="276" t="n">
         <v>78</v>
       </c>
-      <c r="D16" s="99" t="n">
+      <c r="D16" s="276" t="n">
         <v>48</v>
       </c>
-      <c r="E16" s="99" t="n">
+      <c r="E16" s="276" t="n">
         <v>70</v>
       </c>
-      <c r="H16" s="125" t="inlineStr">
+      <c r="H16" s="277" t="inlineStr">
         <is>
           <t>Kritik Eşik Güvenlik Tamponu</t>
         </is>
       </c>
-      <c r="I16" s="205">
+      <c r="I16" s="278">
         <f>B7*0.30</f>
         <v/>
       </c>
-      <c r="J16" s="206">
+      <c r="J16" s="279">
         <f>B7*0.03</f>
         <v/>
       </c>
-      <c r="K16" s="127" t="inlineStr">
+      <c r="K16" s="280" t="inlineStr">
         <is>
           <t>24 Ay</t>
         </is>
       </c>
-      <c r="L16" s="108" t="inlineStr">
+      <c r="L16" s="281" t="inlineStr">
         <is>
           <t>★ AVANTAJ</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="99" t="inlineStr">
+      <c r="M16" s="282" t="n"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="B17" s="269" t="inlineStr">
         <is>
           <t>D3</t>
         </is>
       </c>
-      <c r="C17" s="99" t="n">
+      <c r="C17" s="269" t="n">
         <v>85</v>
       </c>
-      <c r="D17" s="99" t="n">
+      <c r="D17" s="269" t="n">
         <v>55</v>
       </c>
-      <c r="E17" s="99" t="n">
+      <c r="E17" s="269" t="n">
         <v>80</v>
       </c>
-      <c r="H17" s="125" t="inlineStr">
+      <c r="H17" s="270" t="inlineStr">
         <is>
           <t>Operasyonel Net Fark</t>
         </is>
       </c>
-      <c r="I17" s="205">
+      <c r="I17" s="271">
         <f>B7*0.15</f>
         <v/>
       </c>
-      <c r="J17" s="206">
+      <c r="J17" s="272">
         <f>B7*0.02</f>
         <v/>
       </c>
-      <c r="K17" s="127" t="inlineStr">
+      <c r="K17" s="273" t="inlineStr">
         <is>
           <t>8 Ay</t>
         </is>
       </c>
-      <c r="L17" s="128" t="inlineStr">
+      <c r="L17" s="283" t="inlineStr">
         <is>
           <t>● YAKLAŞAN</t>
         </is>
       </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="99" t="inlineStr">
+      <c r="M17" s="275" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="B18" s="276" t="inlineStr">
         <is>
           <t>D4</t>
         </is>
       </c>
-      <c r="C18" s="99" t="n">
+      <c r="C18" s="276" t="n">
         <v>75</v>
       </c>
-      <c r="D18" s="99" t="n">
+      <c r="D18" s="276" t="n">
         <v>42</v>
       </c>
-      <c r="E18" s="99" t="n">
+      <c r="E18" s="276" t="n">
         <v>75</v>
       </c>
-      <c r="H18" s="125" t="inlineStr">
+      <c r="H18" s="277" t="inlineStr">
         <is>
           <t>Rezerv ve Likit Dağılım</t>
         </is>
       </c>
-      <c r="I18" s="205">
+      <c r="I18" s="278">
         <f>B7*0.10</f>
         <v/>
       </c>
-      <c r="J18" s="206">
+      <c r="J18" s="279">
         <f>B7*0.01</f>
         <v/>
       </c>
-      <c r="K18" s="127" t="inlineStr">
+      <c r="K18" s="280" t="inlineStr">
         <is>
           <t>16 Ay</t>
         </is>
       </c>
-      <c r="L18" s="111" t="inlineStr">
+      <c r="L18" s="284" t="inlineStr">
         <is>
           <t>✓ TAM UYUM</t>
         </is>
       </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="99" t="inlineStr">
+      <c r="M18" s="282" t="n"/>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="B19" s="269" t="inlineStr">
         <is>
           <t>D5</t>
         </is>
       </c>
-      <c r="C19" s="99" t="n">
+      <c r="C19" s="269" t="n">
         <v>90</v>
       </c>
-      <c r="D19" s="99" t="n">
+      <c r="D19" s="269" t="n">
         <v>40</v>
       </c>
-      <c r="E19" s="99" t="n">
+      <c r="E19" s="269" t="n">
         <v>85</v>
       </c>
-      <c r="H19" s="129" t="inlineStr">
+      <c r="H19" s="285" t="inlineStr">
         <is>
           <t>KONSOLİDE SİSTEM TOPLAMI</t>
         </is>
       </c>
-      <c r="I19" s="207">
+      <c r="I19" s="286">
         <f>SUM(I15:I18)</f>
         <v/>
       </c>
-      <c r="J19" s="208">
+      <c r="J19" s="287">
         <f>SUM(J15:J18)</f>
         <v/>
       </c>
-      <c r="K19" s="132" t="inlineStr"/>
-      <c r="L19" s="133" t="inlineStr">
+      <c r="K19" s="288" t="inlineStr"/>
+      <c r="L19" s="289" t="inlineStr">
         <is>
           <t>TAM DOĞRULANDI (0 HATA)</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="99" t="inlineStr">
+      <c r="M19" s="289" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="B20" s="276" t="inlineStr">
         <is>
           <t>D6</t>
         </is>
       </c>
-      <c r="C20" s="99" t="n">
+      <c r="C20" s="276" t="n">
         <v>96</v>
       </c>
-      <c r="D20" s="99" t="n">
+      <c r="D20" s="276" t="n">
         <v>32</v>
       </c>
-      <c r="E20" s="99" t="n">
+      <c r="E20" s="276" t="n">
         <v>92</v>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="B22" s="134" t="inlineStr">
+    <row r="21" ht="14" customHeight="1"/>
+    <row r="22" ht="24" customHeight="1">
+      <c r="B22" s="290" t="inlineStr">
         <is>
           <t>KONSOLİDE PAY VE AĞIRLIK</t>
         </is>
       </c>
-      <c r="F22" s="134" t="inlineStr">
+      <c r="C22" s="240" t="n"/>
+      <c r="D22" s="240" t="n"/>
+      <c r="E22" s="291" t="n"/>
+      <c r="F22" s="290" t="inlineStr">
         <is>
           <t>LİKİDİTE RİSKİ &amp; ERKEN UYARI SİNYALLERİ</t>
         </is>
       </c>
-      <c r="K22" s="135" t="inlineStr">
+      <c r="G22" s="240" t="n"/>
+      <c r="H22" s="240" t="n"/>
+      <c r="I22" s="291" t="n"/>
+      <c r="K22" s="292" t="inlineStr">
         <is>
           <t>KARAR MOTORU</t>
         </is>
       </c>
-      <c r="L22" s="136" t="n"/>
-      <c r="M22" s="136" t="n"/>
-    </row>
-    <row r="23">
-      <c r="B23" s="84" t="inlineStr">
+      <c r="L22" s="293" t="n"/>
+      <c r="M22" s="294" t="n"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="B23" s="295" t="inlineStr">
         <is>
           <t>■ Ana Segment (%42)</t>
         </is>
       </c>
-      <c r="F23" s="99" t="inlineStr">
+      <c r="C23" s="249" t="n"/>
+      <c r="D23" s="249" t="n"/>
+      <c r="E23" s="250" t="n"/>
+      <c r="F23" s="296" t="inlineStr">
         <is>
           <t>Nakit Açığı Riski (30 Gün)</t>
         </is>
       </c>
-      <c r="I23" s="137" t="inlineStr">
+      <c r="G23" s="249" t="n"/>
+      <c r="H23" s="249" t="n"/>
+      <c r="I23" s="297" t="inlineStr">
         <is>
           <t>0.00 TL (Sıfır Risk)</t>
         </is>
       </c>
-      <c r="K23" s="138" t="inlineStr">
-        <is>
-          <t>STRATEJİK VERİMLİLİK FIRSATI</t>
-        </is>
-      </c>
-      <c r="L23" s="136" t="n"/>
-      <c r="M23" s="136" t="n"/>
-    </row>
-    <row r="24">
-      <c r="B24" s="85" t="inlineStr">
+      <c r="K23" s="298" t="inlineStr">
+        <is>
+          <t>LİKİDİTE OPTİMİZASYON FIRSATI</t>
+        </is>
+      </c>
+      <c r="L23" s="299" t="n"/>
+      <c r="M23" s="300" t="n"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="B24" s="301" t="inlineStr">
         <is>
           <t>■ İkincil Grup (%30)</t>
         </is>
       </c>
-      <c r="F24" s="99" t="inlineStr">
+      <c r="C24" s="249" t="n"/>
+      <c r="D24" s="249" t="n"/>
+      <c r="E24" s="250" t="n"/>
+      <c r="F24" s="296" t="inlineStr">
         <is>
           <t>Tahsilat Gecikme Toleransı</t>
         </is>
       </c>
-      <c r="I24" s="137" t="inlineStr">
+      <c r="G24" s="249" t="n"/>
+      <c r="H24" s="249" t="n"/>
+      <c r="I24" s="297" t="inlineStr">
         <is>
           <t>48 Gün Güvenli Eşik</t>
         </is>
       </c>
-      <c r="K24" s="139" t="inlineStr">
-        <is>
-          <t>Operasyonel süreç optimizasyonu ile kârlılık artış potansiyeli tespit edildi.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="140" t="inlineStr">
+      <c r="K24" s="302" t="inlineStr">
+        <is>
+          <t>Atıl kalan nakit rezervinin gecelik repoda</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="B25" s="303" t="inlineStr">
         <is>
           <t>■ Destek Birimi (%15)</t>
         </is>
       </c>
-      <c r="F25" s="84" t="inlineStr">
+      <c r="C25" s="249" t="n"/>
+      <c r="D25" s="249" t="n"/>
+      <c r="E25" s="250" t="n"/>
+      <c r="F25" s="274" t="inlineStr">
         <is>
           <t>██████████████████████████████████████ Güvenli Bölge (%100)</t>
         </is>
       </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="141" t="inlineStr">
+      <c r="G25" s="304" t="n"/>
+      <c r="H25" s="304" t="n"/>
+      <c r="I25" s="304" t="n"/>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="B26" s="305" t="inlineStr">
         <is>
           <t>■ Rezervler (%13)</t>
         </is>
       </c>
-      <c r="F26" s="142" t="inlineStr">
+      <c r="C26" s="249" t="n"/>
+      <c r="D26" s="249" t="n"/>
+      <c r="E26" s="250" t="n"/>
+      <c r="F26" s="306" t="inlineStr">
         <is>
           <t>✓ 90 GÜNLÜK PROJEKSİYONDA NAKİT SIKIŞIKLIĞI TESPİT EDİLMEDİ</t>
         </is>
@@ -16057,23 +16822,29 @@
       <c r="G26" s="215" t="n"/>
       <c r="H26" s="215" t="n"/>
       <c r="I26" s="216" t="n"/>
-      <c r="K26" s="143" t="inlineStr">
-        <is>
-          <t>STRATEJİ REÇETESİNİ İNCELE &gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
+      <c r="K26" s="307" t="inlineStr">
+        <is>
+          <t>FONLAMA SENARYOSUNU İNCELE ›</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="26" customHeight="1">
+      <c r="B27" s="308" t="n"/>
+      <c r="C27" s="259" t="n"/>
+      <c r="D27" s="259" t="n"/>
+      <c r="E27" s="260" t="n"/>
       <c r="F27" s="217" t="n"/>
       <c r="G27" s="218" t="n"/>
       <c r="H27" s="218" t="n"/>
       <c r="I27" s="219" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="K26:M27"/>
+  <mergeCells count="5">
     <mergeCell ref="K24:M25"/>
     <mergeCell ref="F26:I27"/>
+    <mergeCell ref="B2:K2"/>
+    <mergeCell ref="K26:M27"/>
+    <mergeCell ref="B3:K3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16108,7 +16879,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="233" t="inlineStr">
         <is>
@@ -16123,7 +16893,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="61" t="inlineStr">
         <is>
@@ -16179,7 +16948,6 @@
         <v/>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="61" t="inlineStr">
         <is>
@@ -16257,7 +17025,6 @@
         <v/>
       </c>
     </row>
-    <row r="19"/>
     <row r="20">
       <c r="A20" s="66" t="inlineStr">
         <is>
@@ -16280,7 +17047,6 @@
         <v/>
       </c>
     </row>
-    <row r="22"/>
     <row r="23">
       <c r="A23" s="61" t="inlineStr">
         <is>
@@ -16292,7 +17058,6 @@
         <v/>
       </c>
     </row>
-    <row r="24"/>
     <row r="25">
       <c r="A25" s="61" t="inlineStr">
         <is>
@@ -16304,7 +17069,6 @@
         <v/>
       </c>
     </row>
-    <row r="26"/>
     <row r="27">
       <c r="A27" s="61" t="inlineStr">
         <is>
@@ -16316,8 +17080,6 @@
         <v/>
       </c>
     </row>
-    <row r="28"/>
-    <row r="29"/>
     <row r="30">
       <c r="A30" s="61" t="inlineStr">
         <is>
@@ -16334,8 +17096,6 @@
       </c>
       <c r="B31" s="68" t="inlineStr"/>
     </row>
-    <row r="32"/>
-    <row r="33"/>
     <row r="34">
       <c r="A34" s="69" t="inlineStr">
         <is>
@@ -16416,7 +17176,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="233" t="inlineStr">
         <is>
@@ -16424,7 +17183,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
@@ -16513,7 +17271,6 @@
         <v/>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="61" t="inlineStr">
         <is>
@@ -16638,7 +17395,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="233" t="inlineStr">
         <is>
@@ -16646,7 +17402,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="21" t="inlineStr">
         <is>
@@ -22949,7 +23704,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="233" t="inlineStr">
         <is>
@@ -22957,7 +23711,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="45" t="inlineStr">
         <is>
@@ -23055,7 +23808,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="233" t="inlineStr">
         <is>
@@ -23063,7 +23815,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="21" t="inlineStr">
         <is>
@@ -24475,7 +25226,6 @@
         <v/>
       </c>
     </row>
-    <row r="41"/>
     <row r="42">
       <c r="J42" s="5" t="inlineStr">
         <is>
@@ -24616,7 +25366,6 @@
         <v/>
       </c>
     </row>
-    <row r="47"/>
     <row r="48">
       <c r="J48" s="10" t="inlineStr">
         <is>
@@ -24639,7 +25388,6 @@
         <v/>
       </c>
     </row>
-    <row r="50"/>
     <row r="51">
       <c r="J51" s="8" t="inlineStr">
         <is>
@@ -24709,7 +25457,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
@@ -24717,7 +25464,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
@@ -24746,7 +25492,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="75" t="inlineStr">
         <is>
@@ -24761,7 +25506,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="76" t="inlineStr">
         <is>
@@ -24769,7 +25513,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
@@ -24794,7 +25537,6 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
@@ -24809,7 +25551,6 @@
         </is>
       </c>
     </row>
-    <row r="20"/>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
@@ -24864,7 +25605,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="B3" s="144" t="inlineStr">
         <is>
@@ -24885,7 +25625,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="B5" s="147" t="inlineStr">
         <is>
@@ -25298,7 +26037,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17">
       <c r="B17" s="164" t="inlineStr">
         <is>
@@ -25329,54 +26067,55 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="86" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="234" t="inlineStr">
         <is>
           <t>☰ PANO</t>
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="28" customHeight="1">
       <c r="B2" s="166" t="inlineStr">
         <is>
           <t>İTHALAT LANDED COST MOTORU — NİHAİ KARAR VE DEĞERLEME</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="B3" s="167" t="inlineStr">
+    <row r="3" ht="18" customHeight="1">
+      <c r="B3" s="309" t="inlineStr">
         <is>
           <t>Yönetim Kurulu ve İcra Komitesi için Otomatik Finansal Stres Testi Raporu · İthalatçı CFO, satın alma, gümrük müşaviri, SMMM</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="B4" s="168" t="inlineStr">
+    <row r="4" ht="20" customHeight="1">
+      <c r="B4" s="310" t="inlineStr">
         <is>
           <t>DÖNEM: 2026 Q3 · DENETİM PROTOKOLÜ: ISO/VUK/IFRS UYUMLU · DURUM: ONAYLANDI</t>
         </is>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="B6" s="169" t="inlineStr">
+    <row r="5" ht="12" customHeight="1"/>
+    <row r="6" ht="26" customHeight="1">
+      <c r="B6" s="311" t="inlineStr">
         <is>
           <t>SENARYO A: KÖTÜMSER (STRES TESTİ -%20)</t>
         </is>
@@ -25385,7 +26124,7 @@
       <c r="D6" s="220" t="n"/>
       <c r="E6" s="220" t="n"/>
       <c r="F6" s="221" t="n"/>
-      <c r="H6" s="170" t="inlineStr">
+      <c r="H6" s="312" t="inlineStr">
         <is>
           <t>SENARYO B: BAZ MODEL (HEDEFLENEN)</t>
         </is>
@@ -25395,151 +26134,151 @@
       <c r="K6" s="220" t="n"/>
       <c r="L6" s="221" t="n"/>
     </row>
-    <row r="7">
-      <c r="B7" s="107" t="n"/>
-      <c r="C7" s="107" t="n"/>
-      <c r="D7" s="107" t="n"/>
-      <c r="E7" s="107" t="n"/>
-      <c r="F7" s="107" t="n"/>
-      <c r="H7" s="107" t="n"/>
-      <c r="I7" s="107" t="n"/>
-      <c r="J7" s="107" t="n"/>
-      <c r="K7" s="107" t="n"/>
-      <c r="L7" s="107" t="n"/>
-    </row>
-    <row r="8">
-      <c r="B8" s="171" t="inlineStr">
+    <row r="7" ht="22" customHeight="1">
+      <c r="B7" s="313" t="n"/>
+      <c r="C7" s="249" t="n"/>
+      <c r="D7" s="249" t="n"/>
+      <c r="E7" s="249" t="n"/>
+      <c r="F7" s="314" t="n"/>
+      <c r="H7" s="315" t="n"/>
+      <c r="I7" s="249" t="n"/>
+      <c r="J7" s="249" t="n"/>
+      <c r="K7" s="249" t="n"/>
+      <c r="L7" s="316" t="n"/>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="B8" s="317" t="inlineStr">
         <is>
           <t>Ciro / Hacim Düşüşü:</t>
         </is>
       </c>
-      <c r="C8" s="107" t="n"/>
-      <c r="D8" s="107" t="n"/>
-      <c r="E8" s="172" t="inlineStr">
+      <c r="C8" s="249" t="n"/>
+      <c r="D8" s="249" t="n"/>
+      <c r="E8" s="318" t="inlineStr">
         <is>
           <t>-%20.0 (Kriz Eşiği)</t>
         </is>
       </c>
-      <c r="F8" s="107" t="n"/>
-      <c r="H8" s="171" t="inlineStr">
+      <c r="F8" s="314" t="n"/>
+      <c r="H8" s="319" t="inlineStr">
         <is>
           <t>Ciro / Hacim Gerçekleşmesi:</t>
         </is>
       </c>
-      <c r="I8" s="107" t="n"/>
-      <c r="J8" s="107" t="n"/>
-      <c r="K8" s="173" t="inlineStr">
+      <c r="I8" s="249" t="n"/>
+      <c r="J8" s="249" t="n"/>
+      <c r="K8" s="320" t="inlineStr">
         <is>
           <t>%100.0 (Tam Bütçe)</t>
         </is>
       </c>
-      <c r="L8" s="107" t="n"/>
-    </row>
-    <row r="9">
-      <c r="B9" s="171" t="inlineStr">
+      <c r="L8" s="316" t="n"/>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="B9" s="317" t="inlineStr">
         <is>
           <t>Beklenen Net Kâr / Getiri:</t>
         </is>
       </c>
-      <c r="C9" s="107" t="n"/>
-      <c r="D9" s="107" t="n"/>
-      <c r="E9" s="210">
+      <c r="C9" s="249" t="n"/>
+      <c r="D9" s="249" t="n"/>
+      <c r="E9" s="321">
         <f>PANO!B7*0.8*0.22</f>
         <v/>
       </c>
-      <c r="F9" s="107" t="n"/>
-      <c r="H9" s="171" t="inlineStr">
+      <c r="F9" s="314" t="n"/>
+      <c r="H9" s="319" t="inlineStr">
         <is>
           <t>Beklenen Net Kâr / Getiri:</t>
         </is>
       </c>
-      <c r="I9" s="107" t="n"/>
-      <c r="J9" s="107" t="n"/>
-      <c r="K9" s="210">
+      <c r="I9" s="249" t="n"/>
+      <c r="J9" s="249" t="n"/>
+      <c r="K9" s="321">
         <f>PANO!H7</f>
         <v/>
       </c>
-      <c r="L9" s="107" t="n"/>
-    </row>
-    <row r="10">
-      <c r="B10" s="171" t="inlineStr">
+      <c r="L9" s="316" t="n"/>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="B10" s="317" t="inlineStr">
         <is>
           <t>Minimum Nakit Tamponu:</t>
         </is>
       </c>
-      <c r="C10" s="107" t="n"/>
-      <c r="D10" s="107" t="n"/>
-      <c r="E10" s="211">
+      <c r="C10" s="249" t="n"/>
+      <c r="D10" s="249" t="n"/>
+      <c r="E10" s="322">
         <f>PANO!E7*0.75</f>
         <v/>
       </c>
-      <c r="F10" s="107" t="n"/>
-      <c r="H10" s="171" t="inlineStr">
+      <c r="F10" s="314" t="n"/>
+      <c r="H10" s="319" t="inlineStr">
         <is>
           <t>Serbest Nakit Akımı:</t>
         </is>
       </c>
-      <c r="I10" s="107" t="n"/>
-      <c r="J10" s="107" t="n"/>
-      <c r="K10" s="211">
+      <c r="I10" s="249" t="n"/>
+      <c r="J10" s="249" t="n"/>
+      <c r="K10" s="322">
         <f>PANO!H7*0.75</f>
         <v/>
       </c>
-      <c r="L10" s="107" t="n"/>
-    </row>
-    <row r="11">
-      <c r="B11" s="171" t="inlineStr">
+      <c r="L10" s="316" t="n"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="B11" s="317" t="inlineStr">
         <is>
           <t>Likidite Karşılama Oranı:</t>
         </is>
       </c>
-      <c r="C11" s="107" t="n"/>
-      <c r="D11" s="107" t="n"/>
-      <c r="E11" s="212">
+      <c r="C11" s="249" t="n"/>
+      <c r="D11" s="249" t="n"/>
+      <c r="E11" s="323">
         <f>ROUND(PANO!B7*0.8/PANO!E7, 2)</f>
         <v/>
       </c>
-      <c r="F11" s="107" t="n"/>
-      <c r="H11" s="171" t="inlineStr">
+      <c r="F11" s="314" t="n"/>
+      <c r="H11" s="319" t="inlineStr">
         <is>
           <t>Yatırım Geri Dönüşü (ROI):</t>
         </is>
       </c>
-      <c r="I11" s="107" t="n"/>
-      <c r="J11" s="107" t="n"/>
-      <c r="K11" s="175" t="inlineStr">
+      <c r="I11" s="249" t="n"/>
+      <c r="J11" s="249" t="n"/>
+      <c r="K11" s="324" t="inlineStr">
         <is>
           <t>%38.4 Yıllık</t>
         </is>
       </c>
-      <c r="L11" s="107" t="n"/>
-    </row>
-    <row r="12">
-      <c r="B12" s="107" t="n"/>
-      <c r="C12" s="107" t="n"/>
-      <c r="D12" s="107" t="n"/>
-      <c r="E12" s="107" t="n"/>
-      <c r="F12" s="107" t="n"/>
-      <c r="H12" s="107" t="n"/>
-      <c r="I12" s="107" t="n"/>
-      <c r="J12" s="107" t="n"/>
-      <c r="K12" s="107" t="n"/>
-      <c r="L12" s="107" t="n"/>
-    </row>
-    <row r="13">
-      <c r="B13" s="107" t="n"/>
-      <c r="C13" s="107" t="n"/>
-      <c r="D13" s="107" t="n"/>
-      <c r="E13" s="107" t="n"/>
-      <c r="F13" s="107" t="n"/>
-      <c r="H13" s="107" t="n"/>
-      <c r="I13" s="107" t="n"/>
-      <c r="J13" s="107" t="n"/>
-      <c r="K13" s="107" t="n"/>
-      <c r="L13" s="107" t="n"/>
-    </row>
-    <row r="14">
-      <c r="B14" s="176" t="inlineStr">
+      <c r="L11" s="316" t="n"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="B12" s="313" t="n"/>
+      <c r="C12" s="249" t="n"/>
+      <c r="D12" s="249" t="n"/>
+      <c r="E12" s="249" t="n"/>
+      <c r="F12" s="314" t="n"/>
+      <c r="H12" s="315" t="n"/>
+      <c r="I12" s="249" t="n"/>
+      <c r="J12" s="249" t="n"/>
+      <c r="K12" s="249" t="n"/>
+      <c r="L12" s="316" t="n"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="B13" s="313" t="n"/>
+      <c r="C13" s="249" t="n"/>
+      <c r="D13" s="249" t="n"/>
+      <c r="E13" s="249" t="n"/>
+      <c r="F13" s="314" t="n"/>
+      <c r="H13" s="315" t="n"/>
+      <c r="I13" s="249" t="n"/>
+      <c r="J13" s="249" t="n"/>
+      <c r="K13" s="249" t="n"/>
+      <c r="L13" s="316" t="n"/>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="B14" s="325" t="inlineStr">
         <is>
           <t>STRES SENARYOSUNDA DAHİ İFLAS RİSKİ YOK</t>
         </is>
@@ -25548,7 +26287,7 @@
       <c r="D14" s="222" t="n"/>
       <c r="E14" s="222" t="n"/>
       <c r="F14" s="223" t="n"/>
-      <c r="H14" s="177" t="inlineStr">
+      <c r="H14" s="326" t="inlineStr">
         <is>
           <t>OPTİMUM İCRA VE PLANLAMA REÇETESİ</t>
         </is>
@@ -25558,7 +26297,7 @@
       <c r="K14" s="224" t="n"/>
       <c r="L14" s="225" t="n"/>
     </row>
-    <row r="15">
+    <row r="15" ht="14" customHeight="1">
       <c r="B15" s="226" t="n"/>
       <c r="C15" s="227" t="n"/>
       <c r="D15" s="227" t="n"/>
@@ -25570,70 +26309,185 @@
       <c r="K15" s="230" t="n"/>
       <c r="L15" s="231" t="n"/>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="B17" s="87" t="inlineStr">
+    <row r="16" ht="10" customHeight="1"/>
+    <row r="17" ht="26" customHeight="1">
+      <c r="B17" s="327" t="inlineStr">
         <is>
           <t>YÖNETİM KARAR MATRİSİ VE UYGULAMA REÇETESİ</t>
         </is>
       </c>
-    </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="B19" s="134" t="inlineStr">
+      <c r="C17" s="240" t="n"/>
+      <c r="D17" s="240" t="n"/>
+      <c r="E17" s="240" t="n"/>
+      <c r="F17" s="240" t="n"/>
+      <c r="G17" s="240" t="n"/>
+      <c r="H17" s="240" t="n"/>
+      <c r="I17" s="240" t="n"/>
+      <c r="J17" s="240" t="n"/>
+      <c r="K17" s="240" t="n"/>
+      <c r="L17" s="291" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="B18" s="328" t="n"/>
+      <c r="C18" s="249" t="n"/>
+      <c r="D18" s="249" t="n"/>
+      <c r="E18" s="249" t="n"/>
+      <c r="F18" s="249" t="n"/>
+      <c r="G18" s="249" t="n"/>
+      <c r="H18" s="249" t="n"/>
+      <c r="I18" s="249" t="n"/>
+      <c r="J18" s="249" t="n"/>
+      <c r="K18" s="249" t="n"/>
+      <c r="L18" s="250" t="n"/>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="B19" s="329" t="inlineStr">
         <is>
           <t>●  Öncelik 1: Acil Likidite ve Borç Servis Planlaması</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="178" t="inlineStr">
+      <c r="C19" s="249" t="n"/>
+      <c r="D19" s="249" t="n"/>
+      <c r="E19" s="249" t="n"/>
+      <c r="F19" s="249" t="n"/>
+      <c r="G19" s="249" t="n"/>
+      <c r="H19" s="249" t="n"/>
+      <c r="I19" s="249" t="n"/>
+      <c r="J19" s="249" t="n"/>
+      <c r="K19" s="249" t="n"/>
+      <c r="L19" s="250" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="B20" s="330" t="inlineStr">
         <is>
           <t xml:space="preserve">   Sistemde hesaplanan vade günlerine sadık kalınarak nakit blokajı 3 gün önceden hazır edilmelidir.</t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="134" t="inlineStr">
+      <c r="C20" s="249" t="n"/>
+      <c r="D20" s="249" t="n"/>
+      <c r="E20" s="249" t="n"/>
+      <c r="F20" s="249" t="n"/>
+      <c r="G20" s="249" t="n"/>
+      <c r="H20" s="249" t="n"/>
+      <c r="I20" s="249" t="n"/>
+      <c r="J20" s="249" t="n"/>
+      <c r="K20" s="249" t="n"/>
+      <c r="L20" s="250" t="n"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="B21" s="329" t="inlineStr">
         <is>
           <t>●  Öncelik 2: Formül Doğrulama ve Çapraz Sağlama</t>
         </is>
       </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="178" t="inlineStr">
+      <c r="C21" s="249" t="n"/>
+      <c r="D21" s="249" t="n"/>
+      <c r="E21" s="249" t="n"/>
+      <c r="F21" s="249" t="n"/>
+      <c r="G21" s="249" t="n"/>
+      <c r="H21" s="249" t="n"/>
+      <c r="I21" s="249" t="n"/>
+      <c r="J21" s="249" t="n"/>
+      <c r="K21" s="249" t="n"/>
+      <c r="L21" s="250" t="n"/>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="B22" s="330" t="inlineStr">
         <is>
           <t xml:space="preserve">   Tüm hücreler kilitli formül korumasında olup girdi sayfalarında sıfır döngüsel başvuru (circular ref) garantilidir.</t>
         </is>
       </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="134" t="inlineStr">
+      <c r="C22" s="249" t="n"/>
+      <c r="D22" s="249" t="n"/>
+      <c r="E22" s="249" t="n"/>
+      <c r="F22" s="249" t="n"/>
+      <c r="G22" s="249" t="n"/>
+      <c r="H22" s="249" t="n"/>
+      <c r="I22" s="249" t="n"/>
+      <c r="J22" s="249" t="n"/>
+      <c r="K22" s="249" t="n"/>
+      <c r="L22" s="250" t="n"/>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="B23" s="329" t="inlineStr">
         <is>
           <t>●  Öncelik 3: Resmi Mevzuat ve Vergi Kalkanı Entegrasyonu</t>
         </is>
       </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="178" t="inlineStr">
+      <c r="C23" s="249" t="n"/>
+      <c r="D23" s="249" t="n"/>
+      <c r="E23" s="249" t="n"/>
+      <c r="F23" s="249" t="n"/>
+      <c r="G23" s="249" t="n"/>
+      <c r="H23" s="249" t="n"/>
+      <c r="I23" s="249" t="n"/>
+      <c r="J23" s="249" t="n"/>
+      <c r="K23" s="249" t="n"/>
+      <c r="L23" s="250" t="n"/>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="B24" s="330" t="inlineStr">
         <is>
           <t xml:space="preserve">   2026 güncel vergi dilimleri, amortisman ve SGK teşvik parametreleri tam otomatik yansıtılmaktadır.</t>
         </is>
       </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="134" t="inlineStr">
+      <c r="C24" s="249" t="n"/>
+      <c r="D24" s="249" t="n"/>
+      <c r="E24" s="249" t="n"/>
+      <c r="F24" s="249" t="n"/>
+      <c r="G24" s="249" t="n"/>
+      <c r="H24" s="249" t="n"/>
+      <c r="I24" s="249" t="n"/>
+      <c r="J24" s="249" t="n"/>
+      <c r="K24" s="249" t="n"/>
+      <c r="L24" s="250" t="n"/>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="B25" s="329" t="inlineStr">
         <is>
           <t>●  Öncelik 4: Yönetici İmzası ve Rapor Paylaşımı</t>
         </is>
       </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="178" t="inlineStr">
+      <c r="C25" s="249" t="n"/>
+      <c r="D25" s="249" t="n"/>
+      <c r="E25" s="249" t="n"/>
+      <c r="F25" s="249" t="n"/>
+      <c r="G25" s="249" t="n"/>
+      <c r="H25" s="249" t="n"/>
+      <c r="I25" s="249" t="n"/>
+      <c r="J25" s="249" t="n"/>
+      <c r="K25" s="249" t="n"/>
+      <c r="L25" s="250" t="n"/>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="B26" s="330" t="inlineStr">
         <is>
           <t xml:space="preserve">   Tek tuşla PDF ve A4 çıktı formatına tam uyumlu sayfa yapısı kurgulanmıştır.</t>
         </is>
       </c>
+      <c r="C26" s="249" t="n"/>
+      <c r="D26" s="249" t="n"/>
+      <c r="E26" s="249" t="n"/>
+      <c r="F26" s="249" t="n"/>
+      <c r="G26" s="249" t="n"/>
+      <c r="H26" s="249" t="n"/>
+      <c r="I26" s="249" t="n"/>
+      <c r="J26" s="249" t="n"/>
+      <c r="K26" s="249" t="n"/>
+      <c r="L26" s="250" t="n"/>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="B27" s="308" t="n"/>
+      <c r="C27" s="259" t="n"/>
+      <c r="D27" s="259" t="n"/>
+      <c r="E27" s="259" t="n"/>
+      <c r="F27" s="259" t="n"/>
+      <c r="G27" s="259" t="n"/>
+      <c r="H27" s="259" t="n"/>
+      <c r="I27" s="259" t="n"/>
+      <c r="J27" s="259" t="n"/>
+      <c r="K27" s="259" t="n"/>
+      <c r="L27" s="260" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -25675,7 +26529,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="185" t="inlineStr">
         <is>
@@ -26170,7 +27023,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="188" t="inlineStr">
         <is>
@@ -26917,7 +27769,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="193" t="inlineStr">
         <is>
@@ -27595,7 +28446,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="197" t="inlineStr">
         <is>
@@ -28145,7 +28995,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="200" t="inlineStr">
         <is>
